--- a/J_e_all_my.xlsx
+++ b/J_e_all_my.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1000"/>
+  <dimension ref="A1:H885"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6437,7 +6437,7 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>Приду снова.</t>
         </is>
       </c>
     </row>
@@ -6465,7 +6465,7 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>обычно</t>
+          <t>обычно, норма, не странно, стандартно</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
@@ -6475,7 +6475,7 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>Это обычный магазин., Обычно так не делают</t>
         </is>
       </c>
     </row>
@@ -8968,12 +8968,12 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>そのほこ</t>
+          <t>そのほか</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>кроме того</t>
+          <t>другое / прочее / помимо этого (как категория)</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
@@ -8983,7 +8983,7 @@
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>Купила овощи, фрукты и всякое другое.</t>
         </is>
       </c>
     </row>
@@ -10037,7 +10037,7 @@
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>очень, довольно-таки, достаточно, вполне, значительно</t>
+          <t>очень, довольно-таки, достаточно, вполне, нейтрально</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
@@ -10531,7 +10531,7 @@
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>однако</t>
+          <t>однако (мягкое, живое)</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
@@ -16877,7 +16877,7 @@
       </c>
       <c r="F433" t="inlineStr">
         <is>
-          <t>обычно</t>
+          <t>в повседневной жизни, обычно (в быту)</t>
         </is>
       </c>
       <c r="G433" t="inlineStr">
@@ -16887,7 +16887,7 @@
       </c>
       <c r="H433" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>Обычно (в жизни) я пью кофе</t>
         </is>
       </c>
     </row>
@@ -21247,7 +21247,7 @@
       </c>
       <c r="F548" t="inlineStr">
         <is>
-          <t>прямо, все время, гораздо</t>
+          <t>непрерывно / долго / всё время</t>
         </is>
       </c>
       <c r="G548" t="inlineStr">
@@ -21257,7 +21257,7 @@
       </c>
       <c r="H548" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>Я всё время ждала.</t>
         </is>
       </c>
     </row>
@@ -21665,7 +21665,7 @@
       </c>
       <c r="F559" t="inlineStr">
         <is>
-          <t>настолько, как</t>
+          <t>настолько, как (часто с отрицанием не так уж)</t>
         </is>
       </c>
       <c r="G559" t="inlineStr">
@@ -21675,7 +21675,7 @@
       </c>
       <c r="H559" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>Не так уж сложно.</t>
         </is>
       </c>
     </row>
@@ -21817,7 +21817,7 @@
       </c>
       <c r="F563" t="inlineStr">
         <is>
-          <t>таким образом</t>
+          <t>таким образом (описание процесса)</t>
         </is>
       </c>
       <c r="G563" t="inlineStr">
@@ -21827,7 +21827,7 @@
       </c>
       <c r="H563" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>Таким образом решают задачу.</t>
         </is>
       </c>
     </row>
@@ -21893,7 +21893,7 @@
       </c>
       <c r="F565" t="inlineStr">
         <is>
-          <t>крепко, твердо, прочно, надежно</t>
+          <t>надежно, как следует, надёжно, внимательно</t>
         </is>
       </c>
       <c r="G565" t="inlineStr">
@@ -21903,7 +21903,7 @@
       </c>
       <c r="H565" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>Учись как следует.</t>
         </is>
       </c>
     </row>
@@ -21969,7 +21969,7 @@
       </c>
       <c r="F567" t="inlineStr">
         <is>
-          <t>почти что</t>
+          <t>почти, почти все / почти не</t>
         </is>
       </c>
       <c r="G567" t="inlineStr">
@@ -21979,7 +21979,7 @@
       </c>
       <c r="H567" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>почти все люди, почти не ем</t>
         </is>
       </c>
     </row>
@@ -24021,7 +24021,7 @@
       </c>
       <c r="F621" t="inlineStr">
         <is>
-          <t>очень, порядочно, вполне</t>
+          <t>очень, вполне, эмоционально, с оттенком удивления</t>
         </is>
       </c>
       <c r="G621" t="inlineStr">
@@ -24183,7 +24183,7 @@
       </c>
       <c r="H625" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>Я люблю рыбу, особенно лосось.</t>
         </is>
       </c>
     </row>
@@ -24667,7 +24667,7 @@
       </c>
       <c r="F638" t="inlineStr">
         <is>
-          <t>в конце концов</t>
+          <t>в конце концов, в итоге</t>
         </is>
       </c>
       <c r="G638" t="inlineStr">
@@ -24743,7 +24743,7 @@
       </c>
       <c r="F640" t="inlineStr">
         <is>
-          <t>немного спустя, долгое время</t>
+          <t>какое то время (может много а может мало)</t>
         </is>
       </c>
       <c r="G640" t="inlineStr">
@@ -24753,7 +24753,7 @@
       </c>
       <c r="H640" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>отдохну какое-то время</t>
         </is>
       </c>
     </row>
@@ -26491,7 +26491,7 @@
       </c>
       <c r="F686" t="inlineStr">
         <is>
-          <t>редко</t>
+          <t>редко, нейтральное и может быть без отрицания</t>
         </is>
       </c>
       <c r="G686" t="inlineStr">
@@ -26529,7 +26529,7 @@
       </c>
       <c r="F687" t="inlineStr">
         <is>
-          <t>редко</t>
+          <t>редко, разговорное + эмоциональное + обычно с отрицанием</t>
         </is>
       </c>
       <c r="G687" t="inlineStr">
@@ -27669,7 +27669,7 @@
       </c>
       <c r="F717" t="inlineStr">
         <is>
-          <t>и(союз)</t>
+          <t>и(союз) официально, для доков, объявлений</t>
         </is>
       </c>
       <c r="G717" t="inlineStr">
@@ -28657,7 +28657,7 @@
       </c>
       <c r="F743" t="inlineStr">
         <is>
-          <t>обязательно, непременно</t>
+          <t>обязательно, (если можешь, очень прошу)</t>
         </is>
       </c>
       <c r="G743" t="inlineStr">
@@ -30329,7 +30329,7 @@
       </c>
       <c r="F787" t="inlineStr">
         <is>
-          <t>точно</t>
+          <t>идеально подходит, точно (по размеру/время)</t>
         </is>
       </c>
       <c r="G787" t="inlineStr">
@@ -30339,7 +30339,7 @@
       </c>
       <c r="H787" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>Эта одежда мне идеально подходит.</t>
         </is>
       </c>
     </row>
@@ -32571,7 +32571,7 @@
       </c>
       <c r="F846" t="inlineStr">
         <is>
-          <t>точно</t>
+          <t>точно, точно по факту</t>
         </is>
       </c>
       <c r="G846" t="inlineStr">
@@ -32581,7 +32581,7 @@
       </c>
       <c r="H846" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>Точно измерять время</t>
         </is>
       </c>
     </row>
@@ -32799,7 +32799,7 @@
       </c>
       <c r="F852" t="inlineStr">
         <is>
-          <t>снова, ещё</t>
+          <t>ещё больше, к тому же, дополнительно</t>
         </is>
       </c>
       <c r="G852" t="inlineStr">
@@ -32809,7 +32809,7 @@
       </c>
       <c r="H852" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>Цена высокая, и к тому же вкус плохой.</t>
         </is>
       </c>
     </row>
@@ -32913,7 +32913,7 @@
       </c>
       <c r="F855" t="inlineStr">
         <is>
-          <t>однако, но</t>
+          <t>однако, но (книжное, жесткое)</t>
         </is>
       </c>
       <c r="G855" t="inlineStr">
@@ -33878,14 +33878,32 @@
       </c>
     </row>
     <row r="881">
-      <c r="A881" t="inlineStr"/>
+      <c r="A881" t="n">
+        <v>40</v>
+      </c>
       <c r="B881" t="n">
         <v>892</v>
       </c>
-      <c r="C881" t="inlineStr"/>
-      <c r="D881" t="inlineStr"/>
-      <c r="E881" t="inlineStr"/>
-      <c r="F881" t="inlineStr"/>
+      <c r="C881" t="inlineStr">
+        <is>
+          <t>慣</t>
+        </is>
+      </c>
+      <c r="D881" t="inlineStr">
+        <is>
+          <t>カン</t>
+        </is>
+      </c>
+      <c r="E881" t="inlineStr">
+        <is>
+          <t>な.れる、な.らす</t>
+        </is>
+      </c>
+      <c r="F881" t="inlineStr">
+        <is>
+          <t>привыкать, адаптироваться</t>
+        </is>
+      </c>
       <c r="G881" t="inlineStr">
         <is>
           <t>Сущ</t>
@@ -33956,1846 +33974,6 @@
         </is>
       </c>
       <c r="H885" t="inlineStr"/>
-    </row>
-    <row r="886">
-      <c r="A886" t="inlineStr"/>
-      <c r="B886" t="n">
-        <v>897</v>
-      </c>
-      <c r="C886" t="inlineStr"/>
-      <c r="D886" t="inlineStr"/>
-      <c r="E886" t="inlineStr"/>
-      <c r="F886" t="inlineStr"/>
-      <c r="G886" t="inlineStr">
-        <is>
-          <t>Сущ</t>
-        </is>
-      </c>
-      <c r="H886" t="inlineStr"/>
-    </row>
-    <row r="887">
-      <c r="A887" t="inlineStr"/>
-      <c r="B887" t="n">
-        <v>898</v>
-      </c>
-      <c r="C887" t="inlineStr"/>
-      <c r="D887" t="inlineStr"/>
-      <c r="E887" t="inlineStr"/>
-      <c r="F887" t="inlineStr"/>
-      <c r="G887" t="inlineStr">
-        <is>
-          <t>Сущ</t>
-        </is>
-      </c>
-      <c r="H887" t="inlineStr"/>
-    </row>
-    <row r="888">
-      <c r="A888" t="inlineStr"/>
-      <c r="B888" t="n">
-        <v>899</v>
-      </c>
-      <c r="C888" t="inlineStr"/>
-      <c r="D888" t="inlineStr"/>
-      <c r="E888" t="inlineStr"/>
-      <c r="F888" t="inlineStr"/>
-      <c r="G888" t="inlineStr">
-        <is>
-          <t>Сущ</t>
-        </is>
-      </c>
-      <c r="H888" t="inlineStr"/>
-    </row>
-    <row r="889">
-      <c r="A889" t="inlineStr"/>
-      <c r="B889" t="n">
-        <v>900</v>
-      </c>
-      <c r="C889" t="inlineStr"/>
-      <c r="D889" t="inlineStr"/>
-      <c r="E889" t="inlineStr"/>
-      <c r="F889" t="inlineStr"/>
-      <c r="G889" t="inlineStr">
-        <is>
-          <t>Сущ</t>
-        </is>
-      </c>
-      <c r="H889" t="inlineStr"/>
-    </row>
-    <row r="890">
-      <c r="A890" t="inlineStr"/>
-      <c r="B890" t="n">
-        <v>901</v>
-      </c>
-      <c r="C890" t="inlineStr"/>
-      <c r="D890" t="inlineStr"/>
-      <c r="E890" t="inlineStr"/>
-      <c r="F890" t="inlineStr"/>
-      <c r="G890" t="inlineStr">
-        <is>
-          <t>Сущ</t>
-        </is>
-      </c>
-      <c r="H890" t="inlineStr"/>
-    </row>
-    <row r="891">
-      <c r="A891" t="inlineStr"/>
-      <c r="B891" t="n">
-        <v>902</v>
-      </c>
-      <c r="C891" t="inlineStr"/>
-      <c r="D891" t="inlineStr"/>
-      <c r="E891" t="inlineStr"/>
-      <c r="F891" t="inlineStr"/>
-      <c r="G891" t="inlineStr">
-        <is>
-          <t>Сущ</t>
-        </is>
-      </c>
-      <c r="H891" t="inlineStr"/>
-    </row>
-    <row r="892">
-      <c r="A892" t="inlineStr"/>
-      <c r="B892" t="n">
-        <v>903</v>
-      </c>
-      <c r="C892" t="inlineStr"/>
-      <c r="D892" t="inlineStr"/>
-      <c r="E892" t="inlineStr"/>
-      <c r="F892" t="inlineStr"/>
-      <c r="G892" t="inlineStr">
-        <is>
-          <t>Сущ</t>
-        </is>
-      </c>
-      <c r="H892" t="inlineStr"/>
-    </row>
-    <row r="893">
-      <c r="A893" t="inlineStr"/>
-      <c r="B893" t="n">
-        <v>904</v>
-      </c>
-      <c r="C893" t="inlineStr"/>
-      <c r="D893" t="inlineStr"/>
-      <c r="E893" t="inlineStr"/>
-      <c r="F893" t="inlineStr"/>
-      <c r="G893" t="inlineStr">
-        <is>
-          <t>Сущ</t>
-        </is>
-      </c>
-      <c r="H893" t="inlineStr"/>
-    </row>
-    <row r="894">
-      <c r="A894" t="inlineStr"/>
-      <c r="B894" t="n">
-        <v>905</v>
-      </c>
-      <c r="C894" t="inlineStr"/>
-      <c r="D894" t="inlineStr"/>
-      <c r="E894" t="inlineStr"/>
-      <c r="F894" t="inlineStr"/>
-      <c r="G894" t="inlineStr">
-        <is>
-          <t>Сущ</t>
-        </is>
-      </c>
-      <c r="H894" t="inlineStr"/>
-    </row>
-    <row r="895">
-      <c r="A895" t="inlineStr"/>
-      <c r="B895" t="n">
-        <v>906</v>
-      </c>
-      <c r="C895" t="inlineStr"/>
-      <c r="D895" t="inlineStr"/>
-      <c r="E895" t="inlineStr"/>
-      <c r="F895" t="inlineStr"/>
-      <c r="G895" t="inlineStr">
-        <is>
-          <t>Сущ</t>
-        </is>
-      </c>
-      <c r="H895" t="inlineStr"/>
-    </row>
-    <row r="896">
-      <c r="A896" t="inlineStr"/>
-      <c r="B896" t="n">
-        <v>907</v>
-      </c>
-      <c r="C896" t="inlineStr"/>
-      <c r="D896" t="inlineStr"/>
-      <c r="E896" t="inlineStr"/>
-      <c r="F896" t="inlineStr"/>
-      <c r="G896" t="inlineStr">
-        <is>
-          <t>Сущ</t>
-        </is>
-      </c>
-      <c r="H896" t="inlineStr"/>
-    </row>
-    <row r="897">
-      <c r="A897" t="inlineStr"/>
-      <c r="B897" t="n">
-        <v>908</v>
-      </c>
-      <c r="C897" t="inlineStr"/>
-      <c r="D897" t="inlineStr"/>
-      <c r="E897" t="inlineStr"/>
-      <c r="F897" t="inlineStr"/>
-      <c r="G897" t="inlineStr">
-        <is>
-          <t>Сущ</t>
-        </is>
-      </c>
-      <c r="H897" t="inlineStr"/>
-    </row>
-    <row r="898">
-      <c r="A898" t="inlineStr"/>
-      <c r="B898" t="n">
-        <v>909</v>
-      </c>
-      <c r="C898" t="inlineStr"/>
-      <c r="D898" t="inlineStr"/>
-      <c r="E898" t="inlineStr"/>
-      <c r="F898" t="inlineStr"/>
-      <c r="G898" t="inlineStr">
-        <is>
-          <t>Сущ</t>
-        </is>
-      </c>
-      <c r="H898" t="inlineStr"/>
-    </row>
-    <row r="899">
-      <c r="A899" t="inlineStr"/>
-      <c r="B899" t="n">
-        <v>910</v>
-      </c>
-      <c r="C899" t="inlineStr"/>
-      <c r="D899" t="inlineStr"/>
-      <c r="E899" t="inlineStr"/>
-      <c r="F899" t="inlineStr"/>
-      <c r="G899" t="inlineStr">
-        <is>
-          <t>Сущ</t>
-        </is>
-      </c>
-      <c r="H899" t="inlineStr"/>
-    </row>
-    <row r="900">
-      <c r="A900" t="inlineStr"/>
-      <c r="B900" t="n">
-        <v>911</v>
-      </c>
-      <c r="C900" t="inlineStr"/>
-      <c r="D900" t="inlineStr"/>
-      <c r="E900" t="inlineStr"/>
-      <c r="F900" t="inlineStr"/>
-      <c r="G900" t="inlineStr">
-        <is>
-          <t>Сущ</t>
-        </is>
-      </c>
-      <c r="H900" t="inlineStr"/>
-    </row>
-    <row r="901">
-      <c r="A901" t="inlineStr"/>
-      <c r="B901" t="n">
-        <v>912</v>
-      </c>
-      <c r="C901" t="inlineStr"/>
-      <c r="D901" t="inlineStr"/>
-      <c r="E901" t="inlineStr"/>
-      <c r="F901" t="inlineStr"/>
-      <c r="G901" t="inlineStr">
-        <is>
-          <t>Сущ</t>
-        </is>
-      </c>
-      <c r="H901" t="inlineStr"/>
-    </row>
-    <row r="902">
-      <c r="A902" t="inlineStr"/>
-      <c r="B902" t="n">
-        <v>913</v>
-      </c>
-      <c r="C902" t="inlineStr"/>
-      <c r="D902" t="inlineStr"/>
-      <c r="E902" t="inlineStr"/>
-      <c r="F902" t="inlineStr"/>
-      <c r="G902" t="inlineStr">
-        <is>
-          <t>Сущ</t>
-        </is>
-      </c>
-      <c r="H902" t="inlineStr"/>
-    </row>
-    <row r="903">
-      <c r="A903" t="inlineStr"/>
-      <c r="B903" t="n">
-        <v>914</v>
-      </c>
-      <c r="C903" t="inlineStr"/>
-      <c r="D903" t="inlineStr"/>
-      <c r="E903" t="inlineStr"/>
-      <c r="F903" t="inlineStr"/>
-      <c r="G903" t="inlineStr">
-        <is>
-          <t>Сущ</t>
-        </is>
-      </c>
-      <c r="H903" t="inlineStr"/>
-    </row>
-    <row r="904">
-      <c r="A904" t="inlineStr"/>
-      <c r="B904" t="n">
-        <v>915</v>
-      </c>
-      <c r="C904" t="inlineStr"/>
-      <c r="D904" t="inlineStr"/>
-      <c r="E904" t="inlineStr"/>
-      <c r="F904" t="inlineStr"/>
-      <c r="G904" t="inlineStr">
-        <is>
-          <t>Сущ</t>
-        </is>
-      </c>
-      <c r="H904" t="inlineStr"/>
-    </row>
-    <row r="905">
-      <c r="A905" t="inlineStr"/>
-      <c r="B905" t="n">
-        <v>916</v>
-      </c>
-      <c r="C905" t="inlineStr"/>
-      <c r="D905" t="inlineStr"/>
-      <c r="E905" t="inlineStr"/>
-      <c r="F905" t="inlineStr"/>
-      <c r="G905" t="inlineStr">
-        <is>
-          <t>Сущ</t>
-        </is>
-      </c>
-      <c r="H905" t="inlineStr"/>
-    </row>
-    <row r="906">
-      <c r="A906" t="inlineStr"/>
-      <c r="B906" t="n">
-        <v>917</v>
-      </c>
-      <c r="C906" t="inlineStr"/>
-      <c r="D906" t="inlineStr"/>
-      <c r="E906" t="inlineStr"/>
-      <c r="F906" t="inlineStr"/>
-      <c r="G906" t="inlineStr">
-        <is>
-          <t>Сущ</t>
-        </is>
-      </c>
-      <c r="H906" t="inlineStr"/>
-    </row>
-    <row r="907">
-      <c r="A907" t="inlineStr"/>
-      <c r="B907" t="n">
-        <v>918</v>
-      </c>
-      <c r="C907" t="inlineStr"/>
-      <c r="D907" t="inlineStr"/>
-      <c r="E907" t="inlineStr"/>
-      <c r="F907" t="inlineStr"/>
-      <c r="G907" t="inlineStr">
-        <is>
-          <t>Сущ</t>
-        </is>
-      </c>
-      <c r="H907" t="inlineStr"/>
-    </row>
-    <row r="908">
-      <c r="A908" t="inlineStr"/>
-      <c r="B908" t="n">
-        <v>919</v>
-      </c>
-      <c r="C908" t="inlineStr"/>
-      <c r="D908" t="inlineStr"/>
-      <c r="E908" t="inlineStr"/>
-      <c r="F908" t="inlineStr"/>
-      <c r="G908" t="inlineStr">
-        <is>
-          <t>Сущ</t>
-        </is>
-      </c>
-      <c r="H908" t="inlineStr"/>
-    </row>
-    <row r="909">
-      <c r="A909" t="inlineStr"/>
-      <c r="B909" t="n">
-        <v>920</v>
-      </c>
-      <c r="C909" t="inlineStr"/>
-      <c r="D909" t="inlineStr"/>
-      <c r="E909" t="inlineStr"/>
-      <c r="F909" t="inlineStr"/>
-      <c r="G909" t="inlineStr">
-        <is>
-          <t>Сущ</t>
-        </is>
-      </c>
-      <c r="H909" t="inlineStr"/>
-    </row>
-    <row r="910">
-      <c r="A910" t="inlineStr"/>
-      <c r="B910" t="n">
-        <v>921</v>
-      </c>
-      <c r="C910" t="inlineStr"/>
-      <c r="D910" t="inlineStr"/>
-      <c r="E910" t="inlineStr"/>
-      <c r="F910" t="inlineStr"/>
-      <c r="G910" t="inlineStr">
-        <is>
-          <t>Сущ</t>
-        </is>
-      </c>
-      <c r="H910" t="inlineStr"/>
-    </row>
-    <row r="911">
-      <c r="A911" t="inlineStr"/>
-      <c r="B911" t="n">
-        <v>922</v>
-      </c>
-      <c r="C911" t="inlineStr"/>
-      <c r="D911" t="inlineStr"/>
-      <c r="E911" t="inlineStr"/>
-      <c r="F911" t="inlineStr"/>
-      <c r="G911" t="inlineStr">
-        <is>
-          <t>Сущ</t>
-        </is>
-      </c>
-      <c r="H911" t="inlineStr"/>
-    </row>
-    <row r="912">
-      <c r="A912" t="inlineStr"/>
-      <c r="B912" t="n">
-        <v>923</v>
-      </c>
-      <c r="C912" t="inlineStr"/>
-      <c r="D912" t="inlineStr"/>
-      <c r="E912" t="inlineStr"/>
-      <c r="F912" t="inlineStr"/>
-      <c r="G912" t="inlineStr">
-        <is>
-          <t>Сущ</t>
-        </is>
-      </c>
-      <c r="H912" t="inlineStr"/>
-    </row>
-    <row r="913">
-      <c r="A913" t="inlineStr"/>
-      <c r="B913" t="n">
-        <v>924</v>
-      </c>
-      <c r="C913" t="inlineStr"/>
-      <c r="D913" t="inlineStr"/>
-      <c r="E913" t="inlineStr"/>
-      <c r="F913" t="inlineStr"/>
-      <c r="G913" t="inlineStr">
-        <is>
-          <t>Сущ</t>
-        </is>
-      </c>
-      <c r="H913" t="inlineStr"/>
-    </row>
-    <row r="914">
-      <c r="A914" t="inlineStr"/>
-      <c r="B914" t="n">
-        <v>925</v>
-      </c>
-      <c r="C914" t="inlineStr"/>
-      <c r="D914" t="inlineStr"/>
-      <c r="E914" t="inlineStr"/>
-      <c r="F914" t="inlineStr"/>
-      <c r="G914" t="inlineStr">
-        <is>
-          <t>Сущ</t>
-        </is>
-      </c>
-      <c r="H914" t="inlineStr"/>
-    </row>
-    <row r="915">
-      <c r="A915" t="inlineStr"/>
-      <c r="B915" t="n">
-        <v>926</v>
-      </c>
-      <c r="C915" t="inlineStr"/>
-      <c r="D915" t="inlineStr"/>
-      <c r="E915" t="inlineStr"/>
-      <c r="F915" t="inlineStr"/>
-      <c r="G915" t="inlineStr">
-        <is>
-          <t>Сущ</t>
-        </is>
-      </c>
-      <c r="H915" t="inlineStr"/>
-    </row>
-    <row r="916">
-      <c r="A916" t="inlineStr"/>
-      <c r="B916" t="n">
-        <v>927</v>
-      </c>
-      <c r="C916" t="inlineStr"/>
-      <c r="D916" t="inlineStr"/>
-      <c r="E916" t="inlineStr"/>
-      <c r="F916" t="inlineStr"/>
-      <c r="G916" t="inlineStr">
-        <is>
-          <t>Сущ</t>
-        </is>
-      </c>
-      <c r="H916" t="inlineStr"/>
-    </row>
-    <row r="917">
-      <c r="A917" t="inlineStr"/>
-      <c r="B917" t="n">
-        <v>928</v>
-      </c>
-      <c r="C917" t="inlineStr"/>
-      <c r="D917" t="inlineStr"/>
-      <c r="E917" t="inlineStr"/>
-      <c r="F917" t="inlineStr"/>
-      <c r="G917" t="inlineStr">
-        <is>
-          <t>Сущ</t>
-        </is>
-      </c>
-      <c r="H917" t="inlineStr"/>
-    </row>
-    <row r="918">
-      <c r="A918" t="inlineStr"/>
-      <c r="B918" t="n">
-        <v>929</v>
-      </c>
-      <c r="C918" t="inlineStr"/>
-      <c r="D918" t="inlineStr"/>
-      <c r="E918" t="inlineStr"/>
-      <c r="F918" t="inlineStr"/>
-      <c r="G918" t="inlineStr">
-        <is>
-          <t>Сущ</t>
-        </is>
-      </c>
-      <c r="H918" t="inlineStr"/>
-    </row>
-    <row r="919">
-      <c r="A919" t="inlineStr"/>
-      <c r="B919" t="n">
-        <v>930</v>
-      </c>
-      <c r="C919" t="inlineStr"/>
-      <c r="D919" t="inlineStr"/>
-      <c r="E919" t="inlineStr"/>
-      <c r="F919" t="inlineStr"/>
-      <c r="G919" t="inlineStr">
-        <is>
-          <t>Сущ</t>
-        </is>
-      </c>
-      <c r="H919" t="inlineStr"/>
-    </row>
-    <row r="920">
-      <c r="A920" t="inlineStr"/>
-      <c r="B920" t="n">
-        <v>931</v>
-      </c>
-      <c r="C920" t="inlineStr"/>
-      <c r="D920" t="inlineStr"/>
-      <c r="E920" t="inlineStr"/>
-      <c r="F920" t="inlineStr"/>
-      <c r="G920" t="inlineStr">
-        <is>
-          <t>Сущ</t>
-        </is>
-      </c>
-      <c r="H920" t="inlineStr"/>
-    </row>
-    <row r="921">
-      <c r="A921" t="inlineStr"/>
-      <c r="B921" t="n">
-        <v>932</v>
-      </c>
-      <c r="C921" t="inlineStr"/>
-      <c r="D921" t="inlineStr"/>
-      <c r="E921" t="inlineStr"/>
-      <c r="F921" t="inlineStr"/>
-      <c r="G921" t="inlineStr">
-        <is>
-          <t>Сущ</t>
-        </is>
-      </c>
-      <c r="H921" t="inlineStr"/>
-    </row>
-    <row r="922">
-      <c r="A922" t="inlineStr"/>
-      <c r="B922" t="n">
-        <v>933</v>
-      </c>
-      <c r="C922" t="inlineStr"/>
-      <c r="D922" t="inlineStr"/>
-      <c r="E922" t="inlineStr"/>
-      <c r="F922" t="inlineStr"/>
-      <c r="G922" t="inlineStr">
-        <is>
-          <t>Сущ</t>
-        </is>
-      </c>
-      <c r="H922" t="inlineStr"/>
-    </row>
-    <row r="923">
-      <c r="A923" t="inlineStr"/>
-      <c r="B923" t="n">
-        <v>934</v>
-      </c>
-      <c r="C923" t="inlineStr"/>
-      <c r="D923" t="inlineStr"/>
-      <c r="E923" t="inlineStr"/>
-      <c r="F923" t="inlineStr"/>
-      <c r="G923" t="inlineStr">
-        <is>
-          <t>Сущ</t>
-        </is>
-      </c>
-      <c r="H923" t="inlineStr"/>
-    </row>
-    <row r="924">
-      <c r="A924" t="inlineStr"/>
-      <c r="B924" t="n">
-        <v>935</v>
-      </c>
-      <c r="C924" t="inlineStr"/>
-      <c r="D924" t="inlineStr"/>
-      <c r="E924" t="inlineStr"/>
-      <c r="F924" t="inlineStr"/>
-      <c r="G924" t="inlineStr">
-        <is>
-          <t>Сущ</t>
-        </is>
-      </c>
-      <c r="H924" t="inlineStr"/>
-    </row>
-    <row r="925">
-      <c r="A925" t="inlineStr"/>
-      <c r="B925" t="n">
-        <v>936</v>
-      </c>
-      <c r="C925" t="inlineStr"/>
-      <c r="D925" t="inlineStr"/>
-      <c r="E925" t="inlineStr"/>
-      <c r="F925" t="inlineStr"/>
-      <c r="G925" t="inlineStr">
-        <is>
-          <t>Сущ</t>
-        </is>
-      </c>
-      <c r="H925" t="inlineStr"/>
-    </row>
-    <row r="926">
-      <c r="A926" t="inlineStr"/>
-      <c r="B926" t="n">
-        <v>937</v>
-      </c>
-      <c r="C926" t="inlineStr"/>
-      <c r="D926" t="inlineStr"/>
-      <c r="E926" t="inlineStr"/>
-      <c r="F926" t="inlineStr"/>
-      <c r="G926" t="inlineStr">
-        <is>
-          <t>Сущ</t>
-        </is>
-      </c>
-      <c r="H926" t="inlineStr"/>
-    </row>
-    <row r="927">
-      <c r="A927" t="inlineStr"/>
-      <c r="B927" t="n">
-        <v>938</v>
-      </c>
-      <c r="C927" t="inlineStr"/>
-      <c r="D927" t="inlineStr"/>
-      <c r="E927" t="inlineStr"/>
-      <c r="F927" t="inlineStr"/>
-      <c r="G927" t="inlineStr">
-        <is>
-          <t>Сущ</t>
-        </is>
-      </c>
-      <c r="H927" t="inlineStr"/>
-    </row>
-    <row r="928">
-      <c r="A928" t="inlineStr"/>
-      <c r="B928" t="n">
-        <v>939</v>
-      </c>
-      <c r="C928" t="inlineStr"/>
-      <c r="D928" t="inlineStr"/>
-      <c r="E928" t="inlineStr"/>
-      <c r="F928" t="inlineStr"/>
-      <c r="G928" t="inlineStr">
-        <is>
-          <t>Сущ</t>
-        </is>
-      </c>
-      <c r="H928" t="inlineStr"/>
-    </row>
-    <row r="929">
-      <c r="A929" t="inlineStr"/>
-      <c r="B929" t="n">
-        <v>940</v>
-      </c>
-      <c r="C929" t="inlineStr"/>
-      <c r="D929" t="inlineStr"/>
-      <c r="E929" t="inlineStr"/>
-      <c r="F929" t="inlineStr"/>
-      <c r="G929" t="inlineStr">
-        <is>
-          <t>Сущ</t>
-        </is>
-      </c>
-      <c r="H929" t="inlineStr"/>
-    </row>
-    <row r="930">
-      <c r="A930" t="inlineStr"/>
-      <c r="B930" t="n">
-        <v>941</v>
-      </c>
-      <c r="C930" t="inlineStr"/>
-      <c r="D930" t="inlineStr"/>
-      <c r="E930" t="inlineStr"/>
-      <c r="F930" t="inlineStr"/>
-      <c r="G930" t="inlineStr">
-        <is>
-          <t>Сущ</t>
-        </is>
-      </c>
-      <c r="H930" t="inlineStr"/>
-    </row>
-    <row r="931">
-      <c r="A931" t="inlineStr"/>
-      <c r="B931" t="n">
-        <v>942</v>
-      </c>
-      <c r="C931" t="inlineStr"/>
-      <c r="D931" t="inlineStr"/>
-      <c r="E931" t="inlineStr"/>
-      <c r="F931" t="inlineStr"/>
-      <c r="G931" t="inlineStr">
-        <is>
-          <t>Сущ</t>
-        </is>
-      </c>
-      <c r="H931" t="inlineStr"/>
-    </row>
-    <row r="932">
-      <c r="A932" t="inlineStr"/>
-      <c r="B932" t="n">
-        <v>943</v>
-      </c>
-      <c r="C932" t="inlineStr"/>
-      <c r="D932" t="inlineStr"/>
-      <c r="E932" t="inlineStr"/>
-      <c r="F932" t="inlineStr"/>
-      <c r="G932" t="inlineStr">
-        <is>
-          <t>Сущ</t>
-        </is>
-      </c>
-      <c r="H932" t="inlineStr"/>
-    </row>
-    <row r="933">
-      <c r="A933" t="inlineStr"/>
-      <c r="B933" t="n">
-        <v>944</v>
-      </c>
-      <c r="C933" t="inlineStr"/>
-      <c r="D933" t="inlineStr"/>
-      <c r="E933" t="inlineStr"/>
-      <c r="F933" t="inlineStr"/>
-      <c r="G933" t="inlineStr">
-        <is>
-          <t>Сущ</t>
-        </is>
-      </c>
-      <c r="H933" t="inlineStr"/>
-    </row>
-    <row r="934">
-      <c r="A934" t="inlineStr"/>
-      <c r="B934" t="n">
-        <v>945</v>
-      </c>
-      <c r="C934" t="inlineStr"/>
-      <c r="D934" t="inlineStr"/>
-      <c r="E934" t="inlineStr"/>
-      <c r="F934" t="inlineStr"/>
-      <c r="G934" t="inlineStr">
-        <is>
-          <t>Сущ</t>
-        </is>
-      </c>
-      <c r="H934" t="inlineStr"/>
-    </row>
-    <row r="935">
-      <c r="A935" t="inlineStr"/>
-      <c r="B935" t="n">
-        <v>946</v>
-      </c>
-      <c r="C935" t="inlineStr"/>
-      <c r="D935" t="inlineStr"/>
-      <c r="E935" t="inlineStr"/>
-      <c r="F935" t="inlineStr"/>
-      <c r="G935" t="inlineStr">
-        <is>
-          <t>Сущ</t>
-        </is>
-      </c>
-      <c r="H935" t="inlineStr"/>
-    </row>
-    <row r="936">
-      <c r="A936" t="inlineStr"/>
-      <c r="B936" t="n">
-        <v>947</v>
-      </c>
-      <c r="C936" t="inlineStr"/>
-      <c r="D936" t="inlineStr"/>
-      <c r="E936" t="inlineStr"/>
-      <c r="F936" t="inlineStr"/>
-      <c r="G936" t="inlineStr">
-        <is>
-          <t>Сущ</t>
-        </is>
-      </c>
-      <c r="H936" t="inlineStr"/>
-    </row>
-    <row r="937">
-      <c r="A937" t="inlineStr"/>
-      <c r="B937" t="n">
-        <v>948</v>
-      </c>
-      <c r="C937" t="inlineStr"/>
-      <c r="D937" t="inlineStr"/>
-      <c r="E937" t="inlineStr"/>
-      <c r="F937" t="inlineStr"/>
-      <c r="G937" t="inlineStr">
-        <is>
-          <t>Сущ</t>
-        </is>
-      </c>
-      <c r="H937" t="inlineStr"/>
-    </row>
-    <row r="938">
-      <c r="A938" t="inlineStr"/>
-      <c r="B938" t="n">
-        <v>949</v>
-      </c>
-      <c r="C938" t="inlineStr"/>
-      <c r="D938" t="inlineStr"/>
-      <c r="E938" t="inlineStr"/>
-      <c r="F938" t="inlineStr"/>
-      <c r="G938" t="inlineStr">
-        <is>
-          <t>Сущ</t>
-        </is>
-      </c>
-      <c r="H938" t="inlineStr"/>
-    </row>
-    <row r="939">
-      <c r="A939" t="inlineStr"/>
-      <c r="B939" t="n">
-        <v>950</v>
-      </c>
-      <c r="C939" t="inlineStr"/>
-      <c r="D939" t="inlineStr"/>
-      <c r="E939" t="inlineStr"/>
-      <c r="F939" t="inlineStr"/>
-      <c r="G939" t="inlineStr">
-        <is>
-          <t>Сущ</t>
-        </is>
-      </c>
-      <c r="H939" t="inlineStr"/>
-    </row>
-    <row r="940">
-      <c r="A940" t="inlineStr"/>
-      <c r="B940" t="n">
-        <v>951</v>
-      </c>
-      <c r="C940" t="inlineStr"/>
-      <c r="D940" t="inlineStr"/>
-      <c r="E940" t="inlineStr"/>
-      <c r="F940" t="inlineStr"/>
-      <c r="G940" t="inlineStr">
-        <is>
-          <t>Сущ</t>
-        </is>
-      </c>
-      <c r="H940" t="inlineStr"/>
-    </row>
-    <row r="941">
-      <c r="A941" t="inlineStr"/>
-      <c r="B941" t="n">
-        <v>952</v>
-      </c>
-      <c r="C941" t="inlineStr"/>
-      <c r="D941" t="inlineStr"/>
-      <c r="E941" t="inlineStr"/>
-      <c r="F941" t="inlineStr"/>
-      <c r="G941" t="inlineStr">
-        <is>
-          <t>Сущ</t>
-        </is>
-      </c>
-      <c r="H941" t="inlineStr"/>
-    </row>
-    <row r="942">
-      <c r="A942" t="inlineStr"/>
-      <c r="B942" t="n">
-        <v>953</v>
-      </c>
-      <c r="C942" t="inlineStr"/>
-      <c r="D942" t="inlineStr"/>
-      <c r="E942" t="inlineStr"/>
-      <c r="F942" t="inlineStr"/>
-      <c r="G942" t="inlineStr">
-        <is>
-          <t>Сущ</t>
-        </is>
-      </c>
-      <c r="H942" t="inlineStr"/>
-    </row>
-    <row r="943">
-      <c r="A943" t="inlineStr"/>
-      <c r="B943" t="n">
-        <v>954</v>
-      </c>
-      <c r="C943" t="inlineStr"/>
-      <c r="D943" t="inlineStr"/>
-      <c r="E943" t="inlineStr"/>
-      <c r="F943" t="inlineStr"/>
-      <c r="G943" t="inlineStr">
-        <is>
-          <t>Сущ</t>
-        </is>
-      </c>
-      <c r="H943" t="inlineStr"/>
-    </row>
-    <row r="944">
-      <c r="A944" t="inlineStr"/>
-      <c r="B944" t="n">
-        <v>955</v>
-      </c>
-      <c r="C944" t="inlineStr"/>
-      <c r="D944" t="inlineStr"/>
-      <c r="E944" t="inlineStr"/>
-      <c r="F944" t="inlineStr"/>
-      <c r="G944" t="inlineStr">
-        <is>
-          <t>Сущ</t>
-        </is>
-      </c>
-      <c r="H944" t="inlineStr"/>
-    </row>
-    <row r="945">
-      <c r="A945" t="inlineStr"/>
-      <c r="B945" t="n">
-        <v>956</v>
-      </c>
-      <c r="C945" t="inlineStr"/>
-      <c r="D945" t="inlineStr"/>
-      <c r="E945" t="inlineStr"/>
-      <c r="F945" t="inlineStr"/>
-      <c r="G945" t="inlineStr">
-        <is>
-          <t>Сущ</t>
-        </is>
-      </c>
-      <c r="H945" t="inlineStr"/>
-    </row>
-    <row r="946">
-      <c r="A946" t="inlineStr"/>
-      <c r="B946" t="n">
-        <v>957</v>
-      </c>
-      <c r="C946" t="inlineStr"/>
-      <c r="D946" t="inlineStr"/>
-      <c r="E946" t="inlineStr"/>
-      <c r="F946" t="inlineStr"/>
-      <c r="G946" t="inlineStr">
-        <is>
-          <t>Сущ</t>
-        </is>
-      </c>
-      <c r="H946" t="inlineStr"/>
-    </row>
-    <row r="947">
-      <c r="A947" t="inlineStr"/>
-      <c r="B947" t="n">
-        <v>958</v>
-      </c>
-      <c r="C947" t="inlineStr"/>
-      <c r="D947" t="inlineStr"/>
-      <c r="E947" t="inlineStr"/>
-      <c r="F947" t="inlineStr"/>
-      <c r="G947" t="inlineStr">
-        <is>
-          <t>Сущ</t>
-        </is>
-      </c>
-      <c r="H947" t="inlineStr"/>
-    </row>
-    <row r="948">
-      <c r="A948" t="inlineStr"/>
-      <c r="B948" t="n">
-        <v>959</v>
-      </c>
-      <c r="C948" t="inlineStr"/>
-      <c r="D948" t="inlineStr"/>
-      <c r="E948" t="inlineStr"/>
-      <c r="F948" t="inlineStr"/>
-      <c r="G948" t="inlineStr">
-        <is>
-          <t>Сущ</t>
-        </is>
-      </c>
-      <c r="H948" t="inlineStr"/>
-    </row>
-    <row r="949">
-      <c r="A949" t="inlineStr"/>
-      <c r="B949" t="n">
-        <v>960</v>
-      </c>
-      <c r="C949" t="inlineStr"/>
-      <c r="D949" t="inlineStr"/>
-      <c r="E949" t="inlineStr"/>
-      <c r="F949" t="inlineStr"/>
-      <c r="G949" t="inlineStr">
-        <is>
-          <t>Сущ</t>
-        </is>
-      </c>
-      <c r="H949" t="inlineStr"/>
-    </row>
-    <row r="950">
-      <c r="A950" t="inlineStr"/>
-      <c r="B950" t="n">
-        <v>961</v>
-      </c>
-      <c r="C950" t="inlineStr"/>
-      <c r="D950" t="inlineStr"/>
-      <c r="E950" t="inlineStr"/>
-      <c r="F950" t="inlineStr"/>
-      <c r="G950" t="inlineStr">
-        <is>
-          <t>Сущ</t>
-        </is>
-      </c>
-      <c r="H950" t="inlineStr"/>
-    </row>
-    <row r="951">
-      <c r="A951" t="inlineStr"/>
-      <c r="B951" t="n">
-        <v>962</v>
-      </c>
-      <c r="C951" t="inlineStr"/>
-      <c r="D951" t="inlineStr"/>
-      <c r="E951" t="inlineStr"/>
-      <c r="F951" t="inlineStr"/>
-      <c r="G951" t="inlineStr">
-        <is>
-          <t>Сущ</t>
-        </is>
-      </c>
-      <c r="H951" t="inlineStr"/>
-    </row>
-    <row r="952">
-      <c r="A952" t="inlineStr"/>
-      <c r="B952" t="n">
-        <v>963</v>
-      </c>
-      <c r="C952" t="inlineStr"/>
-      <c r="D952" t="inlineStr"/>
-      <c r="E952" t="inlineStr"/>
-      <c r="F952" t="inlineStr"/>
-      <c r="G952" t="inlineStr">
-        <is>
-          <t>Сущ</t>
-        </is>
-      </c>
-      <c r="H952" t="inlineStr"/>
-    </row>
-    <row r="953">
-      <c r="A953" t="inlineStr"/>
-      <c r="B953" t="n">
-        <v>964</v>
-      </c>
-      <c r="C953" t="inlineStr"/>
-      <c r="D953" t="inlineStr"/>
-      <c r="E953" t="inlineStr"/>
-      <c r="F953" t="inlineStr"/>
-      <c r="G953" t="inlineStr">
-        <is>
-          <t>Сущ</t>
-        </is>
-      </c>
-      <c r="H953" t="inlineStr"/>
-    </row>
-    <row r="954">
-      <c r="A954" t="inlineStr"/>
-      <c r="B954" t="n">
-        <v>965</v>
-      </c>
-      <c r="C954" t="inlineStr"/>
-      <c r="D954" t="inlineStr"/>
-      <c r="E954" t="inlineStr"/>
-      <c r="F954" t="inlineStr"/>
-      <c r="G954" t="inlineStr">
-        <is>
-          <t>Сущ</t>
-        </is>
-      </c>
-      <c r="H954" t="inlineStr"/>
-    </row>
-    <row r="955">
-      <c r="A955" t="inlineStr"/>
-      <c r="B955" t="n">
-        <v>966</v>
-      </c>
-      <c r="C955" t="inlineStr"/>
-      <c r="D955" t="inlineStr"/>
-      <c r="E955" t="inlineStr"/>
-      <c r="F955" t="inlineStr"/>
-      <c r="G955" t="inlineStr">
-        <is>
-          <t>Сущ</t>
-        </is>
-      </c>
-      <c r="H955" t="inlineStr"/>
-    </row>
-    <row r="956">
-      <c r="A956" t="inlineStr"/>
-      <c r="B956" t="n">
-        <v>967</v>
-      </c>
-      <c r="C956" t="inlineStr"/>
-      <c r="D956" t="inlineStr"/>
-      <c r="E956" t="inlineStr"/>
-      <c r="F956" t="inlineStr"/>
-      <c r="G956" t="inlineStr">
-        <is>
-          <t>Сущ</t>
-        </is>
-      </c>
-      <c r="H956" t="inlineStr"/>
-    </row>
-    <row r="957">
-      <c r="A957" t="inlineStr"/>
-      <c r="B957" t="n">
-        <v>968</v>
-      </c>
-      <c r="C957" t="inlineStr"/>
-      <c r="D957" t="inlineStr"/>
-      <c r="E957" t="inlineStr"/>
-      <c r="F957" t="inlineStr"/>
-      <c r="G957" t="inlineStr">
-        <is>
-          <t>Сущ</t>
-        </is>
-      </c>
-      <c r="H957" t="inlineStr"/>
-    </row>
-    <row r="958">
-      <c r="A958" t="inlineStr"/>
-      <c r="B958" t="n">
-        <v>969</v>
-      </c>
-      <c r="C958" t="inlineStr"/>
-      <c r="D958" t="inlineStr"/>
-      <c r="E958" t="inlineStr"/>
-      <c r="F958" t="inlineStr"/>
-      <c r="G958" t="inlineStr">
-        <is>
-          <t>Сущ</t>
-        </is>
-      </c>
-      <c r="H958" t="inlineStr"/>
-    </row>
-    <row r="959">
-      <c r="A959" t="inlineStr"/>
-      <c r="B959" t="n">
-        <v>970</v>
-      </c>
-      <c r="C959" t="inlineStr"/>
-      <c r="D959" t="inlineStr"/>
-      <c r="E959" t="inlineStr"/>
-      <c r="F959" t="inlineStr"/>
-      <c r="G959" t="inlineStr">
-        <is>
-          <t>Сущ</t>
-        </is>
-      </c>
-      <c r="H959" t="inlineStr"/>
-    </row>
-    <row r="960">
-      <c r="A960" t="inlineStr"/>
-      <c r="B960" t="n">
-        <v>971</v>
-      </c>
-      <c r="C960" t="inlineStr"/>
-      <c r="D960" t="inlineStr"/>
-      <c r="E960" t="inlineStr"/>
-      <c r="F960" t="inlineStr"/>
-      <c r="G960" t="inlineStr">
-        <is>
-          <t>Сущ</t>
-        </is>
-      </c>
-      <c r="H960" t="inlineStr"/>
-    </row>
-    <row r="961">
-      <c r="A961" t="inlineStr"/>
-      <c r="B961" t="n">
-        <v>972</v>
-      </c>
-      <c r="C961" t="inlineStr"/>
-      <c r="D961" t="inlineStr"/>
-      <c r="E961" t="inlineStr"/>
-      <c r="F961" t="inlineStr"/>
-      <c r="G961" t="inlineStr">
-        <is>
-          <t>Сущ</t>
-        </is>
-      </c>
-      <c r="H961" t="inlineStr"/>
-    </row>
-    <row r="962">
-      <c r="A962" t="inlineStr"/>
-      <c r="B962" t="n">
-        <v>973</v>
-      </c>
-      <c r="C962" t="inlineStr"/>
-      <c r="D962" t="inlineStr"/>
-      <c r="E962" t="inlineStr"/>
-      <c r="F962" t="inlineStr"/>
-      <c r="G962" t="inlineStr">
-        <is>
-          <t>Сущ</t>
-        </is>
-      </c>
-      <c r="H962" t="inlineStr"/>
-    </row>
-    <row r="963">
-      <c r="A963" t="inlineStr"/>
-      <c r="B963" t="n">
-        <v>974</v>
-      </c>
-      <c r="C963" t="inlineStr"/>
-      <c r="D963" t="inlineStr"/>
-      <c r="E963" t="inlineStr"/>
-      <c r="F963" t="inlineStr"/>
-      <c r="G963" t="inlineStr">
-        <is>
-          <t>Сущ</t>
-        </is>
-      </c>
-      <c r="H963" t="inlineStr"/>
-    </row>
-    <row r="964">
-      <c r="A964" t="inlineStr"/>
-      <c r="B964" t="n">
-        <v>975</v>
-      </c>
-      <c r="C964" t="inlineStr"/>
-      <c r="D964" t="inlineStr"/>
-      <c r="E964" t="inlineStr"/>
-      <c r="F964" t="inlineStr"/>
-      <c r="G964" t="inlineStr">
-        <is>
-          <t>Сущ</t>
-        </is>
-      </c>
-      <c r="H964" t="inlineStr"/>
-    </row>
-    <row r="965">
-      <c r="A965" t="inlineStr"/>
-      <c r="B965" t="n">
-        <v>976</v>
-      </c>
-      <c r="C965" t="inlineStr"/>
-      <c r="D965" t="inlineStr"/>
-      <c r="E965" t="inlineStr"/>
-      <c r="F965" t="inlineStr"/>
-      <c r="G965" t="inlineStr">
-        <is>
-          <t>Сущ</t>
-        </is>
-      </c>
-      <c r="H965" t="inlineStr"/>
-    </row>
-    <row r="966">
-      <c r="A966" t="inlineStr"/>
-      <c r="B966" t="n">
-        <v>977</v>
-      </c>
-      <c r="C966" t="inlineStr"/>
-      <c r="D966" t="inlineStr"/>
-      <c r="E966" t="inlineStr"/>
-      <c r="F966" t="inlineStr"/>
-      <c r="G966" t="inlineStr">
-        <is>
-          <t>Сущ</t>
-        </is>
-      </c>
-      <c r="H966" t="inlineStr"/>
-    </row>
-    <row r="967">
-      <c r="A967" t="inlineStr"/>
-      <c r="B967" t="n">
-        <v>978</v>
-      </c>
-      <c r="C967" t="inlineStr"/>
-      <c r="D967" t="inlineStr"/>
-      <c r="E967" t="inlineStr"/>
-      <c r="F967" t="inlineStr"/>
-      <c r="G967" t="inlineStr">
-        <is>
-          <t>Сущ</t>
-        </is>
-      </c>
-      <c r="H967" t="inlineStr"/>
-    </row>
-    <row r="968">
-      <c r="A968" t="inlineStr"/>
-      <c r="B968" t="n">
-        <v>979</v>
-      </c>
-      <c r="C968" t="inlineStr"/>
-      <c r="D968" t="inlineStr"/>
-      <c r="E968" t="inlineStr"/>
-      <c r="F968" t="inlineStr"/>
-      <c r="G968" t="inlineStr">
-        <is>
-          <t>Сущ</t>
-        </is>
-      </c>
-      <c r="H968" t="inlineStr"/>
-    </row>
-    <row r="969">
-      <c r="A969" t="inlineStr"/>
-      <c r="B969" t="n">
-        <v>980</v>
-      </c>
-      <c r="C969" t="inlineStr"/>
-      <c r="D969" t="inlineStr"/>
-      <c r="E969" t="inlineStr"/>
-      <c r="F969" t="inlineStr"/>
-      <c r="G969" t="inlineStr">
-        <is>
-          <t>Сущ</t>
-        </is>
-      </c>
-      <c r="H969" t="inlineStr"/>
-    </row>
-    <row r="970">
-      <c r="A970" t="inlineStr"/>
-      <c r="B970" t="n">
-        <v>981</v>
-      </c>
-      <c r="C970" t="inlineStr"/>
-      <c r="D970" t="inlineStr"/>
-      <c r="E970" t="inlineStr"/>
-      <c r="F970" t="inlineStr"/>
-      <c r="G970" t="inlineStr">
-        <is>
-          <t>Сущ</t>
-        </is>
-      </c>
-      <c r="H970" t="inlineStr"/>
-    </row>
-    <row r="971">
-      <c r="A971" t="inlineStr"/>
-      <c r="B971" t="n">
-        <v>982</v>
-      </c>
-      <c r="C971" t="inlineStr"/>
-      <c r="D971" t="inlineStr"/>
-      <c r="E971" t="inlineStr"/>
-      <c r="F971" t="inlineStr"/>
-      <c r="G971" t="inlineStr">
-        <is>
-          <t>Сущ</t>
-        </is>
-      </c>
-      <c r="H971" t="inlineStr"/>
-    </row>
-    <row r="972">
-      <c r="A972" t="inlineStr"/>
-      <c r="B972" t="n">
-        <v>983</v>
-      </c>
-      <c r="C972" t="inlineStr"/>
-      <c r="D972" t="inlineStr"/>
-      <c r="E972" t="inlineStr"/>
-      <c r="F972" t="inlineStr"/>
-      <c r="G972" t="inlineStr">
-        <is>
-          <t>Сущ</t>
-        </is>
-      </c>
-      <c r="H972" t="inlineStr"/>
-    </row>
-    <row r="973">
-      <c r="A973" t="inlineStr"/>
-      <c r="B973" t="n">
-        <v>984</v>
-      </c>
-      <c r="C973" t="inlineStr"/>
-      <c r="D973" t="inlineStr"/>
-      <c r="E973" t="inlineStr"/>
-      <c r="F973" t="inlineStr"/>
-      <c r="G973" t="inlineStr">
-        <is>
-          <t>Сущ</t>
-        </is>
-      </c>
-      <c r="H973" t="inlineStr"/>
-    </row>
-    <row r="974">
-      <c r="A974" t="inlineStr"/>
-      <c r="B974" t="n">
-        <v>985</v>
-      </c>
-      <c r="C974" t="inlineStr"/>
-      <c r="D974" t="inlineStr"/>
-      <c r="E974" t="inlineStr"/>
-      <c r="F974" t="inlineStr"/>
-      <c r="G974" t="inlineStr">
-        <is>
-          <t>Сущ</t>
-        </is>
-      </c>
-      <c r="H974" t="inlineStr"/>
-    </row>
-    <row r="975">
-      <c r="A975" t="inlineStr"/>
-      <c r="B975" t="n">
-        <v>986</v>
-      </c>
-      <c r="C975" t="inlineStr"/>
-      <c r="D975" t="inlineStr"/>
-      <c r="E975" t="inlineStr"/>
-      <c r="F975" t="inlineStr"/>
-      <c r="G975" t="inlineStr">
-        <is>
-          <t>Сущ</t>
-        </is>
-      </c>
-      <c r="H975" t="inlineStr"/>
-    </row>
-    <row r="976">
-      <c r="A976" t="inlineStr"/>
-      <c r="B976" t="n">
-        <v>987</v>
-      </c>
-      <c r="C976" t="inlineStr"/>
-      <c r="D976" t="inlineStr"/>
-      <c r="E976" t="inlineStr"/>
-      <c r="F976" t="inlineStr"/>
-      <c r="G976" t="inlineStr">
-        <is>
-          <t>Сущ</t>
-        </is>
-      </c>
-      <c r="H976" t="inlineStr"/>
-    </row>
-    <row r="977">
-      <c r="A977" t="inlineStr"/>
-      <c r="B977" t="n">
-        <v>988</v>
-      </c>
-      <c r="C977" t="inlineStr"/>
-      <c r="D977" t="inlineStr"/>
-      <c r="E977" t="inlineStr"/>
-      <c r="F977" t="inlineStr"/>
-      <c r="G977" t="inlineStr">
-        <is>
-          <t>Сущ</t>
-        </is>
-      </c>
-      <c r="H977" t="inlineStr"/>
-    </row>
-    <row r="978">
-      <c r="A978" t="inlineStr"/>
-      <c r="B978" t="n">
-        <v>989</v>
-      </c>
-      <c r="C978" t="inlineStr"/>
-      <c r="D978" t="inlineStr"/>
-      <c r="E978" t="inlineStr"/>
-      <c r="F978" t="inlineStr"/>
-      <c r="G978" t="inlineStr">
-        <is>
-          <t>Сущ</t>
-        </is>
-      </c>
-      <c r="H978" t="inlineStr"/>
-    </row>
-    <row r="979">
-      <c r="A979" t="inlineStr"/>
-      <c r="B979" t="n">
-        <v>990</v>
-      </c>
-      <c r="C979" t="inlineStr"/>
-      <c r="D979" t="inlineStr"/>
-      <c r="E979" t="inlineStr"/>
-      <c r="F979" t="inlineStr"/>
-      <c r="G979" t="inlineStr">
-        <is>
-          <t>Сущ</t>
-        </is>
-      </c>
-      <c r="H979" t="inlineStr"/>
-    </row>
-    <row r="980">
-      <c r="A980" t="inlineStr"/>
-      <c r="B980" t="n">
-        <v>991</v>
-      </c>
-      <c r="C980" t="inlineStr"/>
-      <c r="D980" t="inlineStr"/>
-      <c r="E980" t="inlineStr"/>
-      <c r="F980" t="inlineStr"/>
-      <c r="G980" t="inlineStr">
-        <is>
-          <t>Сущ</t>
-        </is>
-      </c>
-      <c r="H980" t="inlineStr"/>
-    </row>
-    <row r="981">
-      <c r="A981" t="inlineStr"/>
-      <c r="B981" t="n">
-        <v>992</v>
-      </c>
-      <c r="C981" t="inlineStr"/>
-      <c r="D981" t="inlineStr"/>
-      <c r="E981" t="inlineStr"/>
-      <c r="F981" t="inlineStr"/>
-      <c r="G981" t="inlineStr">
-        <is>
-          <t>Сущ</t>
-        </is>
-      </c>
-      <c r="H981" t="inlineStr"/>
-    </row>
-    <row r="982">
-      <c r="A982" t="inlineStr"/>
-      <c r="B982" t="n">
-        <v>993</v>
-      </c>
-      <c r="C982" t="inlineStr"/>
-      <c r="D982" t="inlineStr"/>
-      <c r="E982" t="inlineStr"/>
-      <c r="F982" t="inlineStr"/>
-      <c r="G982" t="inlineStr">
-        <is>
-          <t>Сущ</t>
-        </is>
-      </c>
-      <c r="H982" t="inlineStr"/>
-    </row>
-    <row r="983">
-      <c r="A983" t="inlineStr"/>
-      <c r="B983" t="n">
-        <v>994</v>
-      </c>
-      <c r="C983" t="inlineStr"/>
-      <c r="D983" t="inlineStr"/>
-      <c r="E983" t="inlineStr"/>
-      <c r="F983" t="inlineStr"/>
-      <c r="G983" t="inlineStr">
-        <is>
-          <t>Сущ</t>
-        </is>
-      </c>
-      <c r="H983" t="inlineStr"/>
-    </row>
-    <row r="984">
-      <c r="A984" t="inlineStr"/>
-      <c r="B984" t="n">
-        <v>995</v>
-      </c>
-      <c r="C984" t="inlineStr"/>
-      <c r="D984" t="inlineStr"/>
-      <c r="E984" t="inlineStr"/>
-      <c r="F984" t="inlineStr"/>
-      <c r="G984" t="inlineStr">
-        <is>
-          <t>Сущ</t>
-        </is>
-      </c>
-      <c r="H984" t="inlineStr"/>
-    </row>
-    <row r="985">
-      <c r="A985" t="inlineStr"/>
-      <c r="B985" t="n">
-        <v>996</v>
-      </c>
-      <c r="C985" t="inlineStr"/>
-      <c r="D985" t="inlineStr"/>
-      <c r="E985" t="inlineStr"/>
-      <c r="F985" t="inlineStr"/>
-      <c r="G985" t="inlineStr">
-        <is>
-          <t>Сущ</t>
-        </is>
-      </c>
-      <c r="H985" t="inlineStr"/>
-    </row>
-    <row r="986">
-      <c r="A986" t="inlineStr"/>
-      <c r="B986" t="n">
-        <v>997</v>
-      </c>
-      <c r="C986" t="inlineStr"/>
-      <c r="D986" t="inlineStr"/>
-      <c r="E986" t="inlineStr"/>
-      <c r="F986" t="inlineStr"/>
-      <c r="G986" t="inlineStr">
-        <is>
-          <t>Сущ</t>
-        </is>
-      </c>
-      <c r="H986" t="inlineStr"/>
-    </row>
-    <row r="987">
-      <c r="A987" t="inlineStr"/>
-      <c r="B987" t="n">
-        <v>998</v>
-      </c>
-      <c r="C987" t="inlineStr"/>
-      <c r="D987" t="inlineStr"/>
-      <c r="E987" t="inlineStr"/>
-      <c r="F987" t="inlineStr"/>
-      <c r="G987" t="inlineStr">
-        <is>
-          <t>Сущ</t>
-        </is>
-      </c>
-      <c r="H987" t="inlineStr"/>
-    </row>
-    <row r="988">
-      <c r="A988" t="inlineStr"/>
-      <c r="B988" t="n">
-        <v>999</v>
-      </c>
-      <c r="C988" t="inlineStr"/>
-      <c r="D988" t="inlineStr"/>
-      <c r="E988" t="inlineStr"/>
-      <c r="F988" t="inlineStr"/>
-      <c r="G988" t="inlineStr">
-        <is>
-          <t>Сущ</t>
-        </is>
-      </c>
-      <c r="H988" t="inlineStr"/>
-    </row>
-    <row r="989">
-      <c r="A989" t="inlineStr"/>
-      <c r="B989" t="n">
-        <v>1000</v>
-      </c>
-      <c r="C989" t="inlineStr"/>
-      <c r="D989" t="inlineStr"/>
-      <c r="E989" t="inlineStr"/>
-      <c r="F989" t="inlineStr"/>
-      <c r="G989" t="inlineStr">
-        <is>
-          <t>Сущ</t>
-        </is>
-      </c>
-      <c r="H989" t="inlineStr"/>
-    </row>
-    <row r="990">
-      <c r="A990" t="inlineStr"/>
-      <c r="B990" t="n">
-        <v>1001</v>
-      </c>
-      <c r="C990" t="inlineStr"/>
-      <c r="D990" t="inlineStr"/>
-      <c r="E990" t="inlineStr"/>
-      <c r="F990" t="inlineStr"/>
-      <c r="G990" t="inlineStr">
-        <is>
-          <t>Сущ</t>
-        </is>
-      </c>
-      <c r="H990" t="inlineStr"/>
-    </row>
-    <row r="991">
-      <c r="A991" t="inlineStr"/>
-      <c r="B991" t="n">
-        <v>1002</v>
-      </c>
-      <c r="C991" t="inlineStr"/>
-      <c r="D991" t="inlineStr"/>
-      <c r="E991" t="inlineStr"/>
-      <c r="F991" t="inlineStr"/>
-      <c r="G991" t="inlineStr">
-        <is>
-          <t>Сущ</t>
-        </is>
-      </c>
-      <c r="H991" t="inlineStr"/>
-    </row>
-    <row r="992">
-      <c r="A992" t="inlineStr"/>
-      <c r="B992" t="n">
-        <v>1003</v>
-      </c>
-      <c r="C992" t="inlineStr"/>
-      <c r="D992" t="inlineStr"/>
-      <c r="E992" t="inlineStr"/>
-      <c r="F992" t="inlineStr"/>
-      <c r="G992" t="inlineStr">
-        <is>
-          <t>Сущ</t>
-        </is>
-      </c>
-      <c r="H992" t="inlineStr"/>
-    </row>
-    <row r="993">
-      <c r="A993" t="inlineStr"/>
-      <c r="B993" t="n">
-        <v>1004</v>
-      </c>
-      <c r="C993" t="inlineStr"/>
-      <c r="D993" t="inlineStr"/>
-      <c r="E993" t="inlineStr"/>
-      <c r="F993" t="inlineStr"/>
-      <c r="G993" t="inlineStr">
-        <is>
-          <t>Сущ</t>
-        </is>
-      </c>
-      <c r="H993" t="inlineStr"/>
-    </row>
-    <row r="994">
-      <c r="A994" t="inlineStr"/>
-      <c r="B994" t="n">
-        <v>1005</v>
-      </c>
-      <c r="C994" t="inlineStr"/>
-      <c r="D994" t="inlineStr"/>
-      <c r="E994" t="inlineStr"/>
-      <c r="F994" t="inlineStr"/>
-      <c r="G994" t="inlineStr">
-        <is>
-          <t>Сущ</t>
-        </is>
-      </c>
-      <c r="H994" t="inlineStr"/>
-    </row>
-    <row r="995">
-      <c r="A995" t="inlineStr"/>
-      <c r="B995" t="n">
-        <v>1006</v>
-      </c>
-      <c r="C995" t="inlineStr"/>
-      <c r="D995" t="inlineStr"/>
-      <c r="E995" t="inlineStr"/>
-      <c r="F995" t="inlineStr"/>
-      <c r="G995" t="inlineStr">
-        <is>
-          <t>Сущ</t>
-        </is>
-      </c>
-      <c r="H995" t="inlineStr"/>
-    </row>
-    <row r="996">
-      <c r="A996" t="inlineStr"/>
-      <c r="B996" t="n">
-        <v>1007</v>
-      </c>
-      <c r="C996" t="inlineStr"/>
-      <c r="D996" t="inlineStr"/>
-      <c r="E996" t="inlineStr"/>
-      <c r="F996" t="inlineStr"/>
-      <c r="G996" t="inlineStr">
-        <is>
-          <t>Сущ</t>
-        </is>
-      </c>
-      <c r="H996" t="inlineStr"/>
-    </row>
-    <row r="997">
-      <c r="A997" t="inlineStr"/>
-      <c r="B997" t="n">
-        <v>1008</v>
-      </c>
-      <c r="C997" t="inlineStr"/>
-      <c r="D997" t="inlineStr"/>
-      <c r="E997" t="inlineStr"/>
-      <c r="F997" t="inlineStr"/>
-      <c r="G997" t="inlineStr">
-        <is>
-          <t>Сущ</t>
-        </is>
-      </c>
-      <c r="H997" t="inlineStr"/>
-    </row>
-    <row r="998">
-      <c r="A998" t="inlineStr"/>
-      <c r="B998" t="n">
-        <v>1009</v>
-      </c>
-      <c r="C998" t="inlineStr"/>
-      <c r="D998" t="inlineStr"/>
-      <c r="E998" t="inlineStr"/>
-      <c r="F998" t="inlineStr"/>
-      <c r="G998" t="inlineStr">
-        <is>
-          <t>Сущ</t>
-        </is>
-      </c>
-      <c r="H998" t="inlineStr"/>
-    </row>
-    <row r="999">
-      <c r="A999" t="inlineStr"/>
-      <c r="B999" t="n">
-        <v>1010</v>
-      </c>
-      <c r="C999" t="inlineStr"/>
-      <c r="D999" t="inlineStr"/>
-      <c r="E999" t="inlineStr"/>
-      <c r="F999" t="inlineStr"/>
-      <c r="G999" t="inlineStr">
-        <is>
-          <t>Сущ</t>
-        </is>
-      </c>
-      <c r="H999" t="inlineStr"/>
-    </row>
-    <row r="1000">
-      <c r="A1000" t="inlineStr"/>
-      <c r="B1000" t="n">
-        <v>1011</v>
-      </c>
-      <c r="C1000" t="inlineStr"/>
-      <c r="D1000" t="inlineStr"/>
-      <c r="E1000" t="inlineStr"/>
-      <c r="F1000" t="inlineStr"/>
-      <c r="G1000" t="inlineStr">
-        <is>
-          <t>Сущ</t>
-        </is>
-      </c>
-      <c r="H1000" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -35808,7 +33986,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1001"/>
+  <dimension ref="A1:E459"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -46258,22 +44436,50 @@
       </c>
     </row>
     <row r="455">
-      <c r="A455" t="inlineStr"/>
+      <c r="A455" t="n">
+        <v>40</v>
+      </c>
       <c r="B455" t="n">
         <v>454</v>
       </c>
-      <c r="C455" t="inlineStr"/>
-      <c r="D455" t="inlineStr"/>
-      <c r="E455" t="inlineStr"/>
+      <c r="C455" t="inlineStr">
+        <is>
+          <t>関心</t>
+        </is>
+      </c>
+      <c r="D455" t="inlineStr">
+        <is>
+          <t>かんしん</t>
+        </is>
+      </c>
+      <c r="E455" t="inlineStr">
+        <is>
+          <t>интерес как внимание / обеспокоенность / внимание к теме</t>
+        </is>
+      </c>
     </row>
     <row r="456">
-      <c r="A456" t="inlineStr"/>
+      <c r="A456" t="n">
+        <v>40</v>
+      </c>
       <c r="B456" t="n">
         <v>455</v>
       </c>
-      <c r="C456" t="inlineStr"/>
-      <c r="D456" t="inlineStr"/>
-      <c r="E456" t="inlineStr"/>
+      <c r="C456" t="inlineStr">
+        <is>
+          <t>興味</t>
+        </is>
+      </c>
+      <c r="D456" t="inlineStr">
+        <is>
+          <t>きょうみ</t>
+        </is>
+      </c>
+      <c r="E456" t="inlineStr">
+        <is>
+          <t>личный интерес</t>
+        </is>
+      </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr"/>
@@ -46301,4884 +44507,6 @@
       <c r="C459" t="inlineStr"/>
       <c r="D459" t="inlineStr"/>
       <c r="E459" t="inlineStr"/>
-    </row>
-    <row r="460">
-      <c r="A460" t="inlineStr"/>
-      <c r="B460" t="n">
-        <v>459</v>
-      </c>
-      <c r="C460" t="inlineStr"/>
-      <c r="D460" t="inlineStr"/>
-      <c r="E460" t="inlineStr"/>
-    </row>
-    <row r="461">
-      <c r="A461" t="inlineStr"/>
-      <c r="B461" t="n">
-        <v>460</v>
-      </c>
-      <c r="C461" t="inlineStr"/>
-      <c r="D461" t="inlineStr"/>
-      <c r="E461" t="inlineStr"/>
-    </row>
-    <row r="462">
-      <c r="A462" t="inlineStr"/>
-      <c r="B462" t="n">
-        <v>461</v>
-      </c>
-      <c r="C462" t="inlineStr"/>
-      <c r="D462" t="inlineStr"/>
-      <c r="E462" t="inlineStr"/>
-    </row>
-    <row r="463">
-      <c r="A463" t="inlineStr"/>
-      <c r="B463" t="n">
-        <v>462</v>
-      </c>
-      <c r="C463" t="inlineStr"/>
-      <c r="D463" t="inlineStr"/>
-      <c r="E463" t="inlineStr"/>
-    </row>
-    <row r="464">
-      <c r="A464" t="inlineStr"/>
-      <c r="B464" t="n">
-        <v>463</v>
-      </c>
-      <c r="C464" t="inlineStr"/>
-      <c r="D464" t="inlineStr"/>
-      <c r="E464" t="inlineStr"/>
-    </row>
-    <row r="465">
-      <c r="A465" t="inlineStr"/>
-      <c r="B465" t="n">
-        <v>464</v>
-      </c>
-      <c r="C465" t="inlineStr"/>
-      <c r="D465" t="inlineStr"/>
-      <c r="E465" t="inlineStr"/>
-    </row>
-    <row r="466">
-      <c r="A466" t="inlineStr"/>
-      <c r="B466" t="n">
-        <v>465</v>
-      </c>
-      <c r="C466" t="inlineStr"/>
-      <c r="D466" t="inlineStr"/>
-      <c r="E466" t="inlineStr"/>
-    </row>
-    <row r="467">
-      <c r="A467" t="inlineStr"/>
-      <c r="B467" t="n">
-        <v>466</v>
-      </c>
-      <c r="C467" t="inlineStr"/>
-      <c r="D467" t="inlineStr"/>
-      <c r="E467" t="inlineStr"/>
-    </row>
-    <row r="468">
-      <c r="A468" t="inlineStr"/>
-      <c r="B468" t="n">
-        <v>467</v>
-      </c>
-      <c r="C468" t="inlineStr"/>
-      <c r="D468" t="inlineStr"/>
-      <c r="E468" t="inlineStr"/>
-    </row>
-    <row r="469">
-      <c r="A469" t="inlineStr"/>
-      <c r="B469" t="n">
-        <v>468</v>
-      </c>
-      <c r="C469" t="inlineStr"/>
-      <c r="D469" t="inlineStr"/>
-      <c r="E469" t="inlineStr"/>
-    </row>
-    <row r="470">
-      <c r="A470" t="inlineStr"/>
-      <c r="B470" t="n">
-        <v>469</v>
-      </c>
-      <c r="C470" t="inlineStr"/>
-      <c r="D470" t="inlineStr"/>
-      <c r="E470" t="inlineStr"/>
-    </row>
-    <row r="471">
-      <c r="A471" t="inlineStr"/>
-      <c r="B471" t="n">
-        <v>470</v>
-      </c>
-      <c r="C471" t="inlineStr"/>
-      <c r="D471" t="inlineStr"/>
-      <c r="E471" t="inlineStr"/>
-    </row>
-    <row r="472">
-      <c r="A472" t="inlineStr"/>
-      <c r="B472" t="n">
-        <v>471</v>
-      </c>
-      <c r="C472" t="inlineStr"/>
-      <c r="D472" t="inlineStr"/>
-      <c r="E472" t="inlineStr"/>
-    </row>
-    <row r="473">
-      <c r="A473" t="inlineStr"/>
-      <c r="B473" t="n">
-        <v>472</v>
-      </c>
-      <c r="C473" t="inlineStr"/>
-      <c r="D473" t="inlineStr"/>
-      <c r="E473" t="inlineStr"/>
-    </row>
-    <row r="474">
-      <c r="A474" t="inlineStr"/>
-      <c r="B474" t="n">
-        <v>473</v>
-      </c>
-      <c r="C474" t="inlineStr"/>
-      <c r="D474" t="inlineStr"/>
-      <c r="E474" t="inlineStr"/>
-    </row>
-    <row r="475">
-      <c r="A475" t="inlineStr"/>
-      <c r="B475" t="n">
-        <v>474</v>
-      </c>
-      <c r="C475" t="inlineStr"/>
-      <c r="D475" t="inlineStr"/>
-      <c r="E475" t="inlineStr"/>
-    </row>
-    <row r="476">
-      <c r="A476" t="inlineStr"/>
-      <c r="B476" t="n">
-        <v>475</v>
-      </c>
-      <c r="C476" t="inlineStr"/>
-      <c r="D476" t="inlineStr"/>
-      <c r="E476" t="inlineStr"/>
-    </row>
-    <row r="477">
-      <c r="A477" t="inlineStr"/>
-      <c r="B477" t="n">
-        <v>476</v>
-      </c>
-      <c r="C477" t="inlineStr"/>
-      <c r="D477" t="inlineStr"/>
-      <c r="E477" t="inlineStr"/>
-    </row>
-    <row r="478">
-      <c r="A478" t="inlineStr"/>
-      <c r="B478" t="n">
-        <v>477</v>
-      </c>
-      <c r="C478" t="inlineStr"/>
-      <c r="D478" t="inlineStr"/>
-      <c r="E478" t="inlineStr"/>
-    </row>
-    <row r="479">
-      <c r="A479" t="inlineStr"/>
-      <c r="B479" t="n">
-        <v>478</v>
-      </c>
-      <c r="C479" t="inlineStr"/>
-      <c r="D479" t="inlineStr"/>
-      <c r="E479" t="inlineStr"/>
-    </row>
-    <row r="480">
-      <c r="A480" t="inlineStr"/>
-      <c r="B480" t="n">
-        <v>479</v>
-      </c>
-      <c r="C480" t="inlineStr"/>
-      <c r="D480" t="inlineStr"/>
-      <c r="E480" t="inlineStr"/>
-    </row>
-    <row r="481">
-      <c r="A481" t="inlineStr"/>
-      <c r="B481" t="n">
-        <v>480</v>
-      </c>
-      <c r="C481" t="inlineStr"/>
-      <c r="D481" t="inlineStr"/>
-      <c r="E481" t="inlineStr"/>
-    </row>
-    <row r="482">
-      <c r="A482" t="inlineStr"/>
-      <c r="B482" t="n">
-        <v>481</v>
-      </c>
-      <c r="C482" t="inlineStr"/>
-      <c r="D482" t="inlineStr"/>
-      <c r="E482" t="inlineStr"/>
-    </row>
-    <row r="483">
-      <c r="A483" t="inlineStr"/>
-      <c r="B483" t="n">
-        <v>482</v>
-      </c>
-      <c r="C483" t="inlineStr"/>
-      <c r="D483" t="inlineStr"/>
-      <c r="E483" t="inlineStr"/>
-    </row>
-    <row r="484">
-      <c r="A484" t="inlineStr"/>
-      <c r="B484" t="n">
-        <v>483</v>
-      </c>
-      <c r="C484" t="inlineStr"/>
-      <c r="D484" t="inlineStr"/>
-      <c r="E484" t="inlineStr"/>
-    </row>
-    <row r="485">
-      <c r="A485" t="inlineStr"/>
-      <c r="B485" t="n">
-        <v>484</v>
-      </c>
-      <c r="C485" t="inlineStr"/>
-      <c r="D485" t="inlineStr"/>
-      <c r="E485" t="inlineStr"/>
-    </row>
-    <row r="486">
-      <c r="A486" t="inlineStr"/>
-      <c r="B486" t="n">
-        <v>485</v>
-      </c>
-      <c r="C486" t="inlineStr"/>
-      <c r="D486" t="inlineStr"/>
-      <c r="E486" t="inlineStr"/>
-    </row>
-    <row r="487">
-      <c r="A487" t="inlineStr"/>
-      <c r="B487" t="n">
-        <v>486</v>
-      </c>
-      <c r="C487" t="inlineStr"/>
-      <c r="D487" t="inlineStr"/>
-      <c r="E487" t="inlineStr"/>
-    </row>
-    <row r="488">
-      <c r="A488" t="inlineStr"/>
-      <c r="B488" t="n">
-        <v>487</v>
-      </c>
-      <c r="C488" t="inlineStr"/>
-      <c r="D488" t="inlineStr"/>
-      <c r="E488" t="inlineStr"/>
-    </row>
-    <row r="489">
-      <c r="A489" t="inlineStr"/>
-      <c r="B489" t="n">
-        <v>488</v>
-      </c>
-      <c r="C489" t="inlineStr"/>
-      <c r="D489" t="inlineStr"/>
-      <c r="E489" t="inlineStr"/>
-    </row>
-    <row r="490">
-      <c r="A490" t="inlineStr"/>
-      <c r="B490" t="n">
-        <v>489</v>
-      </c>
-      <c r="C490" t="inlineStr"/>
-      <c r="D490" t="inlineStr"/>
-      <c r="E490" t="inlineStr"/>
-    </row>
-    <row r="491">
-      <c r="A491" t="inlineStr"/>
-      <c r="B491" t="n">
-        <v>490</v>
-      </c>
-      <c r="C491" t="inlineStr"/>
-      <c r="D491" t="inlineStr"/>
-      <c r="E491" t="inlineStr"/>
-    </row>
-    <row r="492">
-      <c r="A492" t="inlineStr"/>
-      <c r="B492" t="n">
-        <v>491</v>
-      </c>
-      <c r="C492" t="inlineStr"/>
-      <c r="D492" t="inlineStr"/>
-      <c r="E492" t="inlineStr"/>
-    </row>
-    <row r="493">
-      <c r="A493" t="inlineStr"/>
-      <c r="B493" t="n">
-        <v>492</v>
-      </c>
-      <c r="C493" t="inlineStr"/>
-      <c r="D493" t="inlineStr"/>
-      <c r="E493" t="inlineStr"/>
-    </row>
-    <row r="494">
-      <c r="A494" t="inlineStr"/>
-      <c r="B494" t="n">
-        <v>493</v>
-      </c>
-      <c r="C494" t="inlineStr"/>
-      <c r="D494" t="inlineStr"/>
-      <c r="E494" t="inlineStr"/>
-    </row>
-    <row r="495">
-      <c r="A495" t="inlineStr"/>
-      <c r="B495" t="n">
-        <v>494</v>
-      </c>
-      <c r="C495" t="inlineStr"/>
-      <c r="D495" t="inlineStr"/>
-      <c r="E495" t="inlineStr"/>
-    </row>
-    <row r="496">
-      <c r="A496" t="inlineStr"/>
-      <c r="B496" t="n">
-        <v>495</v>
-      </c>
-      <c r="C496" t="inlineStr"/>
-      <c r="D496" t="inlineStr"/>
-      <c r="E496" t="inlineStr"/>
-    </row>
-    <row r="497">
-      <c r="A497" t="inlineStr"/>
-      <c r="B497" t="n">
-        <v>496</v>
-      </c>
-      <c r="C497" t="inlineStr"/>
-      <c r="D497" t="inlineStr"/>
-      <c r="E497" t="inlineStr"/>
-    </row>
-    <row r="498">
-      <c r="A498" t="inlineStr"/>
-      <c r="B498" t="n">
-        <v>497</v>
-      </c>
-      <c r="C498" t="inlineStr"/>
-      <c r="D498" t="inlineStr"/>
-      <c r="E498" t="inlineStr"/>
-    </row>
-    <row r="499">
-      <c r="A499" t="inlineStr"/>
-      <c r="B499" t="n">
-        <v>498</v>
-      </c>
-      <c r="C499" t="inlineStr"/>
-      <c r="D499" t="inlineStr"/>
-      <c r="E499" t="inlineStr"/>
-    </row>
-    <row r="500">
-      <c r="A500" t="inlineStr"/>
-      <c r="B500" t="n">
-        <v>499</v>
-      </c>
-      <c r="C500" t="inlineStr"/>
-      <c r="D500" t="inlineStr"/>
-      <c r="E500" t="inlineStr"/>
-    </row>
-    <row r="501">
-      <c r="A501" t="inlineStr"/>
-      <c r="B501" t="n">
-        <v>500</v>
-      </c>
-      <c r="C501" t="inlineStr"/>
-      <c r="D501" t="inlineStr"/>
-      <c r="E501" t="inlineStr"/>
-    </row>
-    <row r="502">
-      <c r="A502" t="inlineStr"/>
-      <c r="B502" t="n">
-        <v>501</v>
-      </c>
-      <c r="C502" t="inlineStr"/>
-      <c r="D502" t="inlineStr"/>
-      <c r="E502" t="inlineStr"/>
-    </row>
-    <row r="503">
-      <c r="A503" t="inlineStr"/>
-      <c r="B503" t="n">
-        <v>502</v>
-      </c>
-      <c r="C503" t="inlineStr"/>
-      <c r="D503" t="inlineStr"/>
-      <c r="E503" t="inlineStr"/>
-    </row>
-    <row r="504">
-      <c r="A504" t="inlineStr"/>
-      <c r="B504" t="n">
-        <v>503</v>
-      </c>
-      <c r="C504" t="inlineStr"/>
-      <c r="D504" t="inlineStr"/>
-      <c r="E504" t="inlineStr"/>
-    </row>
-    <row r="505">
-      <c r="A505" t="inlineStr"/>
-      <c r="B505" t="n">
-        <v>504</v>
-      </c>
-      <c r="C505" t="inlineStr"/>
-      <c r="D505" t="inlineStr"/>
-      <c r="E505" t="inlineStr"/>
-    </row>
-    <row r="506">
-      <c r="A506" t="inlineStr"/>
-      <c r="B506" t="n">
-        <v>505</v>
-      </c>
-      <c r="C506" t="inlineStr"/>
-      <c r="D506" t="inlineStr"/>
-      <c r="E506" t="inlineStr"/>
-    </row>
-    <row r="507">
-      <c r="A507" t="inlineStr"/>
-      <c r="B507" t="n">
-        <v>506</v>
-      </c>
-      <c r="C507" t="inlineStr"/>
-      <c r="D507" t="inlineStr"/>
-      <c r="E507" t="inlineStr"/>
-    </row>
-    <row r="508">
-      <c r="A508" t="inlineStr"/>
-      <c r="B508" t="n">
-        <v>507</v>
-      </c>
-      <c r="C508" t="inlineStr"/>
-      <c r="D508" t="inlineStr"/>
-      <c r="E508" t="inlineStr"/>
-    </row>
-    <row r="509">
-      <c r="A509" t="inlineStr"/>
-      <c r="B509" t="n">
-        <v>508</v>
-      </c>
-      <c r="C509" t="inlineStr"/>
-      <c r="D509" t="inlineStr"/>
-      <c r="E509" t="inlineStr"/>
-    </row>
-    <row r="510">
-      <c r="A510" t="inlineStr"/>
-      <c r="B510" t="n">
-        <v>509</v>
-      </c>
-      <c r="C510" t="inlineStr"/>
-      <c r="D510" t="inlineStr"/>
-      <c r="E510" t="inlineStr"/>
-    </row>
-    <row r="511">
-      <c r="A511" t="inlineStr"/>
-      <c r="B511" t="n">
-        <v>510</v>
-      </c>
-      <c r="C511" t="inlineStr"/>
-      <c r="D511" t="inlineStr"/>
-      <c r="E511" t="inlineStr"/>
-    </row>
-    <row r="512">
-      <c r="A512" t="inlineStr"/>
-      <c r="B512" t="n">
-        <v>511</v>
-      </c>
-      <c r="C512" t="inlineStr"/>
-      <c r="D512" t="inlineStr"/>
-      <c r="E512" t="inlineStr"/>
-    </row>
-    <row r="513">
-      <c r="A513" t="inlineStr"/>
-      <c r="B513" t="n">
-        <v>512</v>
-      </c>
-      <c r="C513" t="inlineStr"/>
-      <c r="D513" t="inlineStr"/>
-      <c r="E513" t="inlineStr"/>
-    </row>
-    <row r="514">
-      <c r="A514" t="inlineStr"/>
-      <c r="B514" t="n">
-        <v>513</v>
-      </c>
-      <c r="C514" t="inlineStr"/>
-      <c r="D514" t="inlineStr"/>
-      <c r="E514" t="inlineStr"/>
-    </row>
-    <row r="515">
-      <c r="A515" t="inlineStr"/>
-      <c r="B515" t="n">
-        <v>514</v>
-      </c>
-      <c r="C515" t="inlineStr"/>
-      <c r="D515" t="inlineStr"/>
-      <c r="E515" t="inlineStr"/>
-    </row>
-    <row r="516">
-      <c r="A516" t="inlineStr"/>
-      <c r="B516" t="n">
-        <v>515</v>
-      </c>
-      <c r="C516" t="inlineStr"/>
-      <c r="D516" t="inlineStr"/>
-      <c r="E516" t="inlineStr"/>
-    </row>
-    <row r="517">
-      <c r="A517" t="inlineStr"/>
-      <c r="B517" t="n">
-        <v>516</v>
-      </c>
-      <c r="C517" t="inlineStr"/>
-      <c r="D517" t="inlineStr"/>
-      <c r="E517" t="inlineStr"/>
-    </row>
-    <row r="518">
-      <c r="A518" t="inlineStr"/>
-      <c r="B518" t="n">
-        <v>517</v>
-      </c>
-      <c r="C518" t="inlineStr"/>
-      <c r="D518" t="inlineStr"/>
-      <c r="E518" t="inlineStr"/>
-    </row>
-    <row r="519">
-      <c r="A519" t="inlineStr"/>
-      <c r="B519" t="n">
-        <v>518</v>
-      </c>
-      <c r="C519" t="inlineStr"/>
-      <c r="D519" t="inlineStr"/>
-      <c r="E519" t="inlineStr"/>
-    </row>
-    <row r="520">
-      <c r="A520" t="inlineStr"/>
-      <c r="B520" t="n">
-        <v>519</v>
-      </c>
-      <c r="C520" t="inlineStr"/>
-      <c r="D520" t="inlineStr"/>
-      <c r="E520" t="inlineStr"/>
-    </row>
-    <row r="521">
-      <c r="A521" t="inlineStr"/>
-      <c r="B521" t="n">
-        <v>520</v>
-      </c>
-      <c r="C521" t="inlineStr"/>
-      <c r="D521" t="inlineStr"/>
-      <c r="E521" t="inlineStr"/>
-    </row>
-    <row r="522">
-      <c r="A522" t="inlineStr"/>
-      <c r="B522" t="n">
-        <v>521</v>
-      </c>
-      <c r="C522" t="inlineStr"/>
-      <c r="D522" t="inlineStr"/>
-      <c r="E522" t="inlineStr"/>
-    </row>
-    <row r="523">
-      <c r="A523" t="inlineStr"/>
-      <c r="B523" t="n">
-        <v>522</v>
-      </c>
-      <c r="C523" t="inlineStr"/>
-      <c r="D523" t="inlineStr"/>
-      <c r="E523" t="inlineStr"/>
-    </row>
-    <row r="524">
-      <c r="A524" t="inlineStr"/>
-      <c r="B524" t="n">
-        <v>523</v>
-      </c>
-      <c r="C524" t="inlineStr"/>
-      <c r="D524" t="inlineStr"/>
-      <c r="E524" t="inlineStr"/>
-    </row>
-    <row r="525">
-      <c r="A525" t="inlineStr"/>
-      <c r="B525" t="n">
-        <v>524</v>
-      </c>
-      <c r="C525" t="inlineStr"/>
-      <c r="D525" t="inlineStr"/>
-      <c r="E525" t="inlineStr"/>
-    </row>
-    <row r="526">
-      <c r="A526" t="inlineStr"/>
-      <c r="B526" t="n">
-        <v>525</v>
-      </c>
-      <c r="C526" t="inlineStr"/>
-      <c r="D526" t="inlineStr"/>
-      <c r="E526" t="inlineStr"/>
-    </row>
-    <row r="527">
-      <c r="A527" t="inlineStr"/>
-      <c r="B527" t="n">
-        <v>526</v>
-      </c>
-      <c r="C527" t="inlineStr"/>
-      <c r="D527" t="inlineStr"/>
-      <c r="E527" t="inlineStr"/>
-    </row>
-    <row r="528">
-      <c r="A528" t="inlineStr"/>
-      <c r="B528" t="n">
-        <v>527</v>
-      </c>
-      <c r="C528" t="inlineStr"/>
-      <c r="D528" t="inlineStr"/>
-      <c r="E528" t="inlineStr"/>
-    </row>
-    <row r="529">
-      <c r="A529" t="inlineStr"/>
-      <c r="B529" t="n">
-        <v>528</v>
-      </c>
-      <c r="C529" t="inlineStr"/>
-      <c r="D529" t="inlineStr"/>
-      <c r="E529" t="inlineStr"/>
-    </row>
-    <row r="530">
-      <c r="A530" t="inlineStr"/>
-      <c r="B530" t="n">
-        <v>529</v>
-      </c>
-      <c r="C530" t="inlineStr"/>
-      <c r="D530" t="inlineStr"/>
-      <c r="E530" t="inlineStr"/>
-    </row>
-    <row r="531">
-      <c r="A531" t="inlineStr"/>
-      <c r="B531" t="n">
-        <v>530</v>
-      </c>
-      <c r="C531" t="inlineStr"/>
-      <c r="D531" t="inlineStr"/>
-      <c r="E531" t="inlineStr"/>
-    </row>
-    <row r="532">
-      <c r="A532" t="inlineStr"/>
-      <c r="B532" t="n">
-        <v>531</v>
-      </c>
-      <c r="C532" t="inlineStr"/>
-      <c r="D532" t="inlineStr"/>
-      <c r="E532" t="inlineStr"/>
-    </row>
-    <row r="533">
-      <c r="A533" t="inlineStr"/>
-      <c r="B533" t="n">
-        <v>532</v>
-      </c>
-      <c r="C533" t="inlineStr"/>
-      <c r="D533" t="inlineStr"/>
-      <c r="E533" t="inlineStr"/>
-    </row>
-    <row r="534">
-      <c r="A534" t="inlineStr"/>
-      <c r="B534" t="n">
-        <v>533</v>
-      </c>
-      <c r="C534" t="inlineStr"/>
-      <c r="D534" t="inlineStr"/>
-      <c r="E534" t="inlineStr"/>
-    </row>
-    <row r="535">
-      <c r="A535" t="inlineStr"/>
-      <c r="B535" t="n">
-        <v>534</v>
-      </c>
-      <c r="C535" t="inlineStr"/>
-      <c r="D535" t="inlineStr"/>
-      <c r="E535" t="inlineStr"/>
-    </row>
-    <row r="536">
-      <c r="A536" t="inlineStr"/>
-      <c r="B536" t="n">
-        <v>535</v>
-      </c>
-      <c r="C536" t="inlineStr"/>
-      <c r="D536" t="inlineStr"/>
-      <c r="E536" t="inlineStr"/>
-    </row>
-    <row r="537">
-      <c r="A537" t="inlineStr"/>
-      <c r="B537" t="n">
-        <v>536</v>
-      </c>
-      <c r="C537" t="inlineStr"/>
-      <c r="D537" t="inlineStr"/>
-      <c r="E537" t="inlineStr"/>
-    </row>
-    <row r="538">
-      <c r="A538" t="inlineStr"/>
-      <c r="B538" t="n">
-        <v>537</v>
-      </c>
-      <c r="C538" t="inlineStr"/>
-      <c r="D538" t="inlineStr"/>
-      <c r="E538" t="inlineStr"/>
-    </row>
-    <row r="539">
-      <c r="A539" t="inlineStr"/>
-      <c r="B539" t="n">
-        <v>538</v>
-      </c>
-      <c r="C539" t="inlineStr"/>
-      <c r="D539" t="inlineStr"/>
-      <c r="E539" t="inlineStr"/>
-    </row>
-    <row r="540">
-      <c r="A540" t="inlineStr"/>
-      <c r="B540" t="n">
-        <v>539</v>
-      </c>
-      <c r="C540" t="inlineStr"/>
-      <c r="D540" t="inlineStr"/>
-      <c r="E540" t="inlineStr"/>
-    </row>
-    <row r="541">
-      <c r="A541" t="inlineStr"/>
-      <c r="B541" t="n">
-        <v>540</v>
-      </c>
-      <c r="C541" t="inlineStr"/>
-      <c r="D541" t="inlineStr"/>
-      <c r="E541" t="inlineStr"/>
-    </row>
-    <row r="542">
-      <c r="A542" t="inlineStr"/>
-      <c r="B542" t="n">
-        <v>541</v>
-      </c>
-      <c r="C542" t="inlineStr"/>
-      <c r="D542" t="inlineStr"/>
-      <c r="E542" t="inlineStr"/>
-    </row>
-    <row r="543">
-      <c r="A543" t="inlineStr"/>
-      <c r="B543" t="n">
-        <v>542</v>
-      </c>
-      <c r="C543" t="inlineStr"/>
-      <c r="D543" t="inlineStr"/>
-      <c r="E543" t="inlineStr"/>
-    </row>
-    <row r="544">
-      <c r="A544" t="inlineStr"/>
-      <c r="B544" t="n">
-        <v>543</v>
-      </c>
-      <c r="C544" t="inlineStr"/>
-      <c r="D544" t="inlineStr"/>
-      <c r="E544" t="inlineStr"/>
-    </row>
-    <row r="545">
-      <c r="A545" t="inlineStr"/>
-      <c r="B545" t="n">
-        <v>544</v>
-      </c>
-      <c r="C545" t="inlineStr"/>
-      <c r="D545" t="inlineStr"/>
-      <c r="E545" t="inlineStr"/>
-    </row>
-    <row r="546">
-      <c r="A546" t="inlineStr"/>
-      <c r="B546" t="n">
-        <v>545</v>
-      </c>
-      <c r="C546" t="inlineStr"/>
-      <c r="D546" t="inlineStr"/>
-      <c r="E546" t="inlineStr"/>
-    </row>
-    <row r="547">
-      <c r="A547" t="inlineStr"/>
-      <c r="B547" t="n">
-        <v>546</v>
-      </c>
-      <c r="C547" t="inlineStr"/>
-      <c r="D547" t="inlineStr"/>
-      <c r="E547" t="inlineStr"/>
-    </row>
-    <row r="548">
-      <c r="A548" t="inlineStr"/>
-      <c r="B548" t="n">
-        <v>547</v>
-      </c>
-      <c r="C548" t="inlineStr"/>
-      <c r="D548" t="inlineStr"/>
-      <c r="E548" t="inlineStr"/>
-    </row>
-    <row r="549">
-      <c r="A549" t="inlineStr"/>
-      <c r="B549" t="n">
-        <v>548</v>
-      </c>
-      <c r="C549" t="inlineStr"/>
-      <c r="D549" t="inlineStr"/>
-      <c r="E549" t="inlineStr"/>
-    </row>
-    <row r="550">
-      <c r="A550" t="inlineStr"/>
-      <c r="B550" t="n">
-        <v>549</v>
-      </c>
-      <c r="C550" t="inlineStr"/>
-      <c r="D550" t="inlineStr"/>
-      <c r="E550" t="inlineStr"/>
-    </row>
-    <row r="551">
-      <c r="A551" t="inlineStr"/>
-      <c r="B551" t="n">
-        <v>550</v>
-      </c>
-      <c r="C551" t="inlineStr"/>
-      <c r="D551" t="inlineStr"/>
-      <c r="E551" t="inlineStr"/>
-    </row>
-    <row r="552">
-      <c r="A552" t="inlineStr"/>
-      <c r="B552" t="n">
-        <v>551</v>
-      </c>
-      <c r="C552" t="inlineStr"/>
-      <c r="D552" t="inlineStr"/>
-      <c r="E552" t="inlineStr"/>
-    </row>
-    <row r="553">
-      <c r="A553" t="inlineStr"/>
-      <c r="B553" t="n">
-        <v>552</v>
-      </c>
-      <c r="C553" t="inlineStr"/>
-      <c r="D553" t="inlineStr"/>
-      <c r="E553" t="inlineStr"/>
-    </row>
-    <row r="554">
-      <c r="A554" t="inlineStr"/>
-      <c r="B554" t="n">
-        <v>553</v>
-      </c>
-      <c r="C554" t="inlineStr"/>
-      <c r="D554" t="inlineStr"/>
-      <c r="E554" t="inlineStr"/>
-    </row>
-    <row r="555">
-      <c r="A555" t="inlineStr"/>
-      <c r="B555" t="n">
-        <v>554</v>
-      </c>
-      <c r="C555" t="inlineStr"/>
-      <c r="D555" t="inlineStr"/>
-      <c r="E555" t="inlineStr"/>
-    </row>
-    <row r="556">
-      <c r="A556" t="inlineStr"/>
-      <c r="B556" t="n">
-        <v>555</v>
-      </c>
-      <c r="C556" t="inlineStr"/>
-      <c r="D556" t="inlineStr"/>
-      <c r="E556" t="inlineStr"/>
-    </row>
-    <row r="557">
-      <c r="A557" t="inlineStr"/>
-      <c r="B557" t="n">
-        <v>556</v>
-      </c>
-      <c r="C557" t="inlineStr"/>
-      <c r="D557" t="inlineStr"/>
-      <c r="E557" t="inlineStr"/>
-    </row>
-    <row r="558">
-      <c r="A558" t="inlineStr"/>
-      <c r="B558" t="n">
-        <v>557</v>
-      </c>
-      <c r="C558" t="inlineStr"/>
-      <c r="D558" t="inlineStr"/>
-      <c r="E558" t="inlineStr"/>
-    </row>
-    <row r="559">
-      <c r="A559" t="inlineStr"/>
-      <c r="B559" t="n">
-        <v>558</v>
-      </c>
-      <c r="C559" t="inlineStr"/>
-      <c r="D559" t="inlineStr"/>
-      <c r="E559" t="inlineStr"/>
-    </row>
-    <row r="560">
-      <c r="A560" t="inlineStr"/>
-      <c r="B560" t="n">
-        <v>559</v>
-      </c>
-      <c r="C560" t="inlineStr"/>
-      <c r="D560" t="inlineStr"/>
-      <c r="E560" t="inlineStr"/>
-    </row>
-    <row r="561">
-      <c r="A561" t="inlineStr"/>
-      <c r="B561" t="n">
-        <v>560</v>
-      </c>
-      <c r="C561" t="inlineStr"/>
-      <c r="D561" t="inlineStr"/>
-      <c r="E561" t="inlineStr"/>
-    </row>
-    <row r="562">
-      <c r="A562" t="inlineStr"/>
-      <c r="B562" t="n">
-        <v>561</v>
-      </c>
-      <c r="C562" t="inlineStr"/>
-      <c r="D562" t="inlineStr"/>
-      <c r="E562" t="inlineStr"/>
-    </row>
-    <row r="563">
-      <c r="A563" t="inlineStr"/>
-      <c r="B563" t="n">
-        <v>562</v>
-      </c>
-      <c r="C563" t="inlineStr"/>
-      <c r="D563" t="inlineStr"/>
-      <c r="E563" t="inlineStr"/>
-    </row>
-    <row r="564">
-      <c r="A564" t="inlineStr"/>
-      <c r="B564" t="n">
-        <v>563</v>
-      </c>
-      <c r="C564" t="inlineStr"/>
-      <c r="D564" t="inlineStr"/>
-      <c r="E564" t="inlineStr"/>
-    </row>
-    <row r="565">
-      <c r="A565" t="inlineStr"/>
-      <c r="B565" t="n">
-        <v>564</v>
-      </c>
-      <c r="C565" t="inlineStr"/>
-      <c r="D565" t="inlineStr"/>
-      <c r="E565" t="inlineStr"/>
-    </row>
-    <row r="566">
-      <c r="A566" t="inlineStr"/>
-      <c r="B566" t="n">
-        <v>565</v>
-      </c>
-      <c r="C566" t="inlineStr"/>
-      <c r="D566" t="inlineStr"/>
-      <c r="E566" t="inlineStr"/>
-    </row>
-    <row r="567">
-      <c r="A567" t="inlineStr"/>
-      <c r="B567" t="n">
-        <v>566</v>
-      </c>
-      <c r="C567" t="inlineStr"/>
-      <c r="D567" t="inlineStr"/>
-      <c r="E567" t="inlineStr"/>
-    </row>
-    <row r="568">
-      <c r="A568" t="inlineStr"/>
-      <c r="B568" t="n">
-        <v>567</v>
-      </c>
-      <c r="C568" t="inlineStr"/>
-      <c r="D568" t="inlineStr"/>
-      <c r="E568" t="inlineStr"/>
-    </row>
-    <row r="569">
-      <c r="A569" t="inlineStr"/>
-      <c r="B569" t="n">
-        <v>568</v>
-      </c>
-      <c r="C569" t="inlineStr"/>
-      <c r="D569" t="inlineStr"/>
-      <c r="E569" t="inlineStr"/>
-    </row>
-    <row r="570">
-      <c r="A570" t="inlineStr"/>
-      <c r="B570" t="n">
-        <v>569</v>
-      </c>
-      <c r="C570" t="inlineStr"/>
-      <c r="D570" t="inlineStr"/>
-      <c r="E570" t="inlineStr"/>
-    </row>
-    <row r="571">
-      <c r="A571" t="inlineStr"/>
-      <c r="B571" t="n">
-        <v>570</v>
-      </c>
-      <c r="C571" t="inlineStr"/>
-      <c r="D571" t="inlineStr"/>
-      <c r="E571" t="inlineStr"/>
-    </row>
-    <row r="572">
-      <c r="A572" t="inlineStr"/>
-      <c r="B572" t="n">
-        <v>571</v>
-      </c>
-      <c r="C572" t="inlineStr"/>
-      <c r="D572" t="inlineStr"/>
-      <c r="E572" t="inlineStr"/>
-    </row>
-    <row r="573">
-      <c r="A573" t="inlineStr"/>
-      <c r="B573" t="n">
-        <v>572</v>
-      </c>
-      <c r="C573" t="inlineStr"/>
-      <c r="D573" t="inlineStr"/>
-      <c r="E573" t="inlineStr"/>
-    </row>
-    <row r="574">
-      <c r="A574" t="inlineStr"/>
-      <c r="B574" t="n">
-        <v>573</v>
-      </c>
-      <c r="C574" t="inlineStr"/>
-      <c r="D574" t="inlineStr"/>
-      <c r="E574" t="inlineStr"/>
-    </row>
-    <row r="575">
-      <c r="A575" t="inlineStr"/>
-      <c r="B575" t="n">
-        <v>574</v>
-      </c>
-      <c r="C575" t="inlineStr"/>
-      <c r="D575" t="inlineStr"/>
-      <c r="E575" t="inlineStr"/>
-    </row>
-    <row r="576">
-      <c r="A576" t="inlineStr"/>
-      <c r="B576" t="n">
-        <v>575</v>
-      </c>
-      <c r="C576" t="inlineStr"/>
-      <c r="D576" t="inlineStr"/>
-      <c r="E576" t="inlineStr"/>
-    </row>
-    <row r="577">
-      <c r="A577" t="inlineStr"/>
-      <c r="B577" t="n">
-        <v>576</v>
-      </c>
-      <c r="C577" t="inlineStr"/>
-      <c r="D577" t="inlineStr"/>
-      <c r="E577" t="inlineStr"/>
-    </row>
-    <row r="578">
-      <c r="A578" t="inlineStr"/>
-      <c r="B578" t="n">
-        <v>577</v>
-      </c>
-      <c r="C578" t="inlineStr"/>
-      <c r="D578" t="inlineStr"/>
-      <c r="E578" t="inlineStr"/>
-    </row>
-    <row r="579">
-      <c r="A579" t="inlineStr"/>
-      <c r="B579" t="n">
-        <v>578</v>
-      </c>
-      <c r="C579" t="inlineStr"/>
-      <c r="D579" t="inlineStr"/>
-      <c r="E579" t="inlineStr"/>
-    </row>
-    <row r="580">
-      <c r="A580" t="inlineStr"/>
-      <c r="B580" t="n">
-        <v>579</v>
-      </c>
-      <c r="C580" t="inlineStr"/>
-      <c r="D580" t="inlineStr"/>
-      <c r="E580" t="inlineStr"/>
-    </row>
-    <row r="581">
-      <c r="A581" t="inlineStr"/>
-      <c r="B581" t="n">
-        <v>580</v>
-      </c>
-      <c r="C581" t="inlineStr"/>
-      <c r="D581" t="inlineStr"/>
-      <c r="E581" t="inlineStr"/>
-    </row>
-    <row r="582">
-      <c r="A582" t="inlineStr"/>
-      <c r="B582" t="n">
-        <v>581</v>
-      </c>
-      <c r="C582" t="inlineStr"/>
-      <c r="D582" t="inlineStr"/>
-      <c r="E582" t="inlineStr"/>
-    </row>
-    <row r="583">
-      <c r="A583" t="inlineStr"/>
-      <c r="B583" t="n">
-        <v>582</v>
-      </c>
-      <c r="C583" t="inlineStr"/>
-      <c r="D583" t="inlineStr"/>
-      <c r="E583" t="inlineStr"/>
-    </row>
-    <row r="584">
-      <c r="A584" t="inlineStr"/>
-      <c r="B584" t="n">
-        <v>583</v>
-      </c>
-      <c r="C584" t="inlineStr"/>
-      <c r="D584" t="inlineStr"/>
-      <c r="E584" t="inlineStr"/>
-    </row>
-    <row r="585">
-      <c r="A585" t="inlineStr"/>
-      <c r="B585" t="n">
-        <v>584</v>
-      </c>
-      <c r="C585" t="inlineStr"/>
-      <c r="D585" t="inlineStr"/>
-      <c r="E585" t="inlineStr"/>
-    </row>
-    <row r="586">
-      <c r="A586" t="inlineStr"/>
-      <c r="B586" t="n">
-        <v>585</v>
-      </c>
-      <c r="C586" t="inlineStr"/>
-      <c r="D586" t="inlineStr"/>
-      <c r="E586" t="inlineStr"/>
-    </row>
-    <row r="587">
-      <c r="A587" t="inlineStr"/>
-      <c r="B587" t="n">
-        <v>586</v>
-      </c>
-      <c r="C587" t="inlineStr"/>
-      <c r="D587" t="inlineStr"/>
-      <c r="E587" t="inlineStr"/>
-    </row>
-    <row r="588">
-      <c r="A588" t="inlineStr"/>
-      <c r="B588" t="n">
-        <v>587</v>
-      </c>
-      <c r="C588" t="inlineStr"/>
-      <c r="D588" t="inlineStr"/>
-      <c r="E588" t="inlineStr"/>
-    </row>
-    <row r="589">
-      <c r="A589" t="inlineStr"/>
-      <c r="B589" t="n">
-        <v>588</v>
-      </c>
-      <c r="C589" t="inlineStr"/>
-      <c r="D589" t="inlineStr"/>
-      <c r="E589" t="inlineStr"/>
-    </row>
-    <row r="590">
-      <c r="A590" t="inlineStr"/>
-      <c r="B590" t="n">
-        <v>589</v>
-      </c>
-      <c r="C590" t="inlineStr"/>
-      <c r="D590" t="inlineStr"/>
-      <c r="E590" t="inlineStr"/>
-    </row>
-    <row r="591">
-      <c r="A591" t="inlineStr"/>
-      <c r="B591" t="n">
-        <v>590</v>
-      </c>
-      <c r="C591" t="inlineStr"/>
-      <c r="D591" t="inlineStr"/>
-      <c r="E591" t="inlineStr"/>
-    </row>
-    <row r="592">
-      <c r="A592" t="inlineStr"/>
-      <c r="B592" t="n">
-        <v>591</v>
-      </c>
-      <c r="C592" t="inlineStr"/>
-      <c r="D592" t="inlineStr"/>
-      <c r="E592" t="inlineStr"/>
-    </row>
-    <row r="593">
-      <c r="A593" t="inlineStr"/>
-      <c r="B593" t="n">
-        <v>592</v>
-      </c>
-      <c r="C593" t="inlineStr"/>
-      <c r="D593" t="inlineStr"/>
-      <c r="E593" t="inlineStr"/>
-    </row>
-    <row r="594">
-      <c r="A594" t="inlineStr"/>
-      <c r="B594" t="n">
-        <v>593</v>
-      </c>
-      <c r="C594" t="inlineStr"/>
-      <c r="D594" t="inlineStr"/>
-      <c r="E594" t="inlineStr"/>
-    </row>
-    <row r="595">
-      <c r="A595" t="inlineStr"/>
-      <c r="B595" t="n">
-        <v>594</v>
-      </c>
-      <c r="C595" t="inlineStr"/>
-      <c r="D595" t="inlineStr"/>
-      <c r="E595" t="inlineStr"/>
-    </row>
-    <row r="596">
-      <c r="A596" t="inlineStr"/>
-      <c r="B596" t="n">
-        <v>595</v>
-      </c>
-      <c r="C596" t="inlineStr"/>
-      <c r="D596" t="inlineStr"/>
-      <c r="E596" t="inlineStr"/>
-    </row>
-    <row r="597">
-      <c r="A597" t="inlineStr"/>
-      <c r="B597" t="n">
-        <v>596</v>
-      </c>
-      <c r="C597" t="inlineStr"/>
-      <c r="D597" t="inlineStr"/>
-      <c r="E597" t="inlineStr"/>
-    </row>
-    <row r="598">
-      <c r="A598" t="inlineStr"/>
-      <c r="B598" t="n">
-        <v>597</v>
-      </c>
-      <c r="C598" t="inlineStr"/>
-      <c r="D598" t="inlineStr"/>
-      <c r="E598" t="inlineStr"/>
-    </row>
-    <row r="599">
-      <c r="A599" t="inlineStr"/>
-      <c r="B599" t="n">
-        <v>598</v>
-      </c>
-      <c r="C599" t="inlineStr"/>
-      <c r="D599" t="inlineStr"/>
-      <c r="E599" t="inlineStr"/>
-    </row>
-    <row r="600">
-      <c r="A600" t="inlineStr"/>
-      <c r="B600" t="n">
-        <v>599</v>
-      </c>
-      <c r="C600" t="inlineStr"/>
-      <c r="D600" t="inlineStr"/>
-      <c r="E600" t="inlineStr"/>
-    </row>
-    <row r="601">
-      <c r="A601" t="inlineStr"/>
-      <c r="B601" t="n">
-        <v>600</v>
-      </c>
-      <c r="C601" t="inlineStr"/>
-      <c r="D601" t="inlineStr"/>
-      <c r="E601" t="inlineStr"/>
-    </row>
-    <row r="602">
-      <c r="A602" t="inlineStr"/>
-      <c r="B602" t="n">
-        <v>601</v>
-      </c>
-      <c r="C602" t="inlineStr"/>
-      <c r="D602" t="inlineStr"/>
-      <c r="E602" t="inlineStr"/>
-    </row>
-    <row r="603">
-      <c r="A603" t="inlineStr"/>
-      <c r="B603" t="n">
-        <v>602</v>
-      </c>
-      <c r="C603" t="inlineStr"/>
-      <c r="D603" t="inlineStr"/>
-      <c r="E603" t="inlineStr"/>
-    </row>
-    <row r="604">
-      <c r="A604" t="inlineStr"/>
-      <c r="B604" t="n">
-        <v>603</v>
-      </c>
-      <c r="C604" t="inlineStr"/>
-      <c r="D604" t="inlineStr"/>
-      <c r="E604" t="inlineStr"/>
-    </row>
-    <row r="605">
-      <c r="A605" t="inlineStr"/>
-      <c r="B605" t="n">
-        <v>604</v>
-      </c>
-      <c r="C605" t="inlineStr"/>
-      <c r="D605" t="inlineStr"/>
-      <c r="E605" t="inlineStr"/>
-    </row>
-    <row r="606">
-      <c r="A606" t="inlineStr"/>
-      <c r="B606" t="n">
-        <v>605</v>
-      </c>
-      <c r="C606" t="inlineStr"/>
-      <c r="D606" t="inlineStr"/>
-      <c r="E606" t="inlineStr"/>
-    </row>
-    <row r="607">
-      <c r="A607" t="inlineStr"/>
-      <c r="B607" t="n">
-        <v>606</v>
-      </c>
-      <c r="C607" t="inlineStr"/>
-      <c r="D607" t="inlineStr"/>
-      <c r="E607" t="inlineStr"/>
-    </row>
-    <row r="608">
-      <c r="A608" t="inlineStr"/>
-      <c r="B608" t="n">
-        <v>607</v>
-      </c>
-      <c r="C608" t="inlineStr"/>
-      <c r="D608" t="inlineStr"/>
-      <c r="E608" t="inlineStr"/>
-    </row>
-    <row r="609">
-      <c r="A609" t="inlineStr"/>
-      <c r="B609" t="n">
-        <v>608</v>
-      </c>
-      <c r="C609" t="inlineStr"/>
-      <c r="D609" t="inlineStr"/>
-      <c r="E609" t="inlineStr"/>
-    </row>
-    <row r="610">
-      <c r="A610" t="inlineStr"/>
-      <c r="B610" t="n">
-        <v>609</v>
-      </c>
-      <c r="C610" t="inlineStr"/>
-      <c r="D610" t="inlineStr"/>
-      <c r="E610" t="inlineStr"/>
-    </row>
-    <row r="611">
-      <c r="A611" t="inlineStr"/>
-      <c r="B611" t="n">
-        <v>610</v>
-      </c>
-      <c r="C611" t="inlineStr"/>
-      <c r="D611" t="inlineStr"/>
-      <c r="E611" t="inlineStr"/>
-    </row>
-    <row r="612">
-      <c r="A612" t="inlineStr"/>
-      <c r="B612" t="n">
-        <v>611</v>
-      </c>
-      <c r="C612" t="inlineStr"/>
-      <c r="D612" t="inlineStr"/>
-      <c r="E612" t="inlineStr"/>
-    </row>
-    <row r="613">
-      <c r="A613" t="inlineStr"/>
-      <c r="B613" t="n">
-        <v>612</v>
-      </c>
-      <c r="C613" t="inlineStr"/>
-      <c r="D613" t="inlineStr"/>
-      <c r="E613" t="inlineStr"/>
-    </row>
-    <row r="614">
-      <c r="A614" t="inlineStr"/>
-      <c r="B614" t="n">
-        <v>613</v>
-      </c>
-      <c r="C614" t="inlineStr"/>
-      <c r="D614" t="inlineStr"/>
-      <c r="E614" t="inlineStr"/>
-    </row>
-    <row r="615">
-      <c r="A615" t="inlineStr"/>
-      <c r="B615" t="n">
-        <v>614</v>
-      </c>
-      <c r="C615" t="inlineStr"/>
-      <c r="D615" t="inlineStr"/>
-      <c r="E615" t="inlineStr"/>
-    </row>
-    <row r="616">
-      <c r="A616" t="inlineStr"/>
-      <c r="B616" t="n">
-        <v>615</v>
-      </c>
-      <c r="C616" t="inlineStr"/>
-      <c r="D616" t="inlineStr"/>
-      <c r="E616" t="inlineStr"/>
-    </row>
-    <row r="617">
-      <c r="A617" t="inlineStr"/>
-      <c r="B617" t="n">
-        <v>616</v>
-      </c>
-      <c r="C617" t="inlineStr"/>
-      <c r="D617" t="inlineStr"/>
-      <c r="E617" t="inlineStr"/>
-    </row>
-    <row r="618">
-      <c r="A618" t="inlineStr"/>
-      <c r="B618" t="n">
-        <v>617</v>
-      </c>
-      <c r="C618" t="inlineStr"/>
-      <c r="D618" t="inlineStr"/>
-      <c r="E618" t="inlineStr"/>
-    </row>
-    <row r="619">
-      <c r="A619" t="inlineStr"/>
-      <c r="B619" t="n">
-        <v>618</v>
-      </c>
-      <c r="C619" t="inlineStr"/>
-      <c r="D619" t="inlineStr"/>
-      <c r="E619" t="inlineStr"/>
-    </row>
-    <row r="620">
-      <c r="A620" t="inlineStr"/>
-      <c r="B620" t="n">
-        <v>619</v>
-      </c>
-      <c r="C620" t="inlineStr"/>
-      <c r="D620" t="inlineStr"/>
-      <c r="E620" t="inlineStr"/>
-    </row>
-    <row r="621">
-      <c r="A621" t="inlineStr"/>
-      <c r="B621" t="n">
-        <v>620</v>
-      </c>
-      <c r="C621" t="inlineStr"/>
-      <c r="D621" t="inlineStr"/>
-      <c r="E621" t="inlineStr"/>
-    </row>
-    <row r="622">
-      <c r="A622" t="inlineStr"/>
-      <c r="B622" t="n">
-        <v>621</v>
-      </c>
-      <c r="C622" t="inlineStr"/>
-      <c r="D622" t="inlineStr"/>
-      <c r="E622" t="inlineStr"/>
-    </row>
-    <row r="623">
-      <c r="A623" t="inlineStr"/>
-      <c r="B623" t="n">
-        <v>622</v>
-      </c>
-      <c r="C623" t="inlineStr"/>
-      <c r="D623" t="inlineStr"/>
-      <c r="E623" t="inlineStr"/>
-    </row>
-    <row r="624">
-      <c r="A624" t="inlineStr"/>
-      <c r="B624" t="n">
-        <v>623</v>
-      </c>
-      <c r="C624" t="inlineStr"/>
-      <c r="D624" t="inlineStr"/>
-      <c r="E624" t="inlineStr"/>
-    </row>
-    <row r="625">
-      <c r="A625" t="inlineStr"/>
-      <c r="B625" t="n">
-        <v>624</v>
-      </c>
-      <c r="C625" t="inlineStr"/>
-      <c r="D625" t="inlineStr"/>
-      <c r="E625" t="inlineStr"/>
-    </row>
-    <row r="626">
-      <c r="A626" t="inlineStr"/>
-      <c r="B626" t="n">
-        <v>625</v>
-      </c>
-      <c r="C626" t="inlineStr"/>
-      <c r="D626" t="inlineStr"/>
-      <c r="E626" t="inlineStr"/>
-    </row>
-    <row r="627">
-      <c r="A627" t="inlineStr"/>
-      <c r="B627" t="n">
-        <v>626</v>
-      </c>
-      <c r="C627" t="inlineStr"/>
-      <c r="D627" t="inlineStr"/>
-      <c r="E627" t="inlineStr"/>
-    </row>
-    <row r="628">
-      <c r="A628" t="inlineStr"/>
-      <c r="B628" t="n">
-        <v>627</v>
-      </c>
-      <c r="C628" t="inlineStr"/>
-      <c r="D628" t="inlineStr"/>
-      <c r="E628" t="inlineStr"/>
-    </row>
-    <row r="629">
-      <c r="A629" t="inlineStr"/>
-      <c r="B629" t="n">
-        <v>628</v>
-      </c>
-      <c r="C629" t="inlineStr"/>
-      <c r="D629" t="inlineStr"/>
-      <c r="E629" t="inlineStr"/>
-    </row>
-    <row r="630">
-      <c r="A630" t="inlineStr"/>
-      <c r="B630" t="n">
-        <v>629</v>
-      </c>
-      <c r="C630" t="inlineStr"/>
-      <c r="D630" t="inlineStr"/>
-      <c r="E630" t="inlineStr"/>
-    </row>
-    <row r="631">
-      <c r="A631" t="inlineStr"/>
-      <c r="B631" t="n">
-        <v>630</v>
-      </c>
-      <c r="C631" t="inlineStr"/>
-      <c r="D631" t="inlineStr"/>
-      <c r="E631" t="inlineStr"/>
-    </row>
-    <row r="632">
-      <c r="A632" t="inlineStr"/>
-      <c r="B632" t="n">
-        <v>631</v>
-      </c>
-      <c r="C632" t="inlineStr"/>
-      <c r="D632" t="inlineStr"/>
-      <c r="E632" t="inlineStr"/>
-    </row>
-    <row r="633">
-      <c r="A633" t="inlineStr"/>
-      <c r="B633" t="n">
-        <v>632</v>
-      </c>
-      <c r="C633" t="inlineStr"/>
-      <c r="D633" t="inlineStr"/>
-      <c r="E633" t="inlineStr"/>
-    </row>
-    <row r="634">
-      <c r="A634" t="inlineStr"/>
-      <c r="B634" t="n">
-        <v>633</v>
-      </c>
-      <c r="C634" t="inlineStr"/>
-      <c r="D634" t="inlineStr"/>
-      <c r="E634" t="inlineStr"/>
-    </row>
-    <row r="635">
-      <c r="A635" t="inlineStr"/>
-      <c r="B635" t="n">
-        <v>634</v>
-      </c>
-      <c r="C635" t="inlineStr"/>
-      <c r="D635" t="inlineStr"/>
-      <c r="E635" t="inlineStr"/>
-    </row>
-    <row r="636">
-      <c r="A636" t="inlineStr"/>
-      <c r="B636" t="n">
-        <v>635</v>
-      </c>
-      <c r="C636" t="inlineStr"/>
-      <c r="D636" t="inlineStr"/>
-      <c r="E636" t="inlineStr"/>
-    </row>
-    <row r="637">
-      <c r="A637" t="inlineStr"/>
-      <c r="B637" t="n">
-        <v>636</v>
-      </c>
-      <c r="C637" t="inlineStr"/>
-      <c r="D637" t="inlineStr"/>
-      <c r="E637" t="inlineStr"/>
-    </row>
-    <row r="638">
-      <c r="A638" t="inlineStr"/>
-      <c r="B638" t="n">
-        <v>637</v>
-      </c>
-      <c r="C638" t="inlineStr"/>
-      <c r="D638" t="inlineStr"/>
-      <c r="E638" t="inlineStr"/>
-    </row>
-    <row r="639">
-      <c r="A639" t="inlineStr"/>
-      <c r="B639" t="n">
-        <v>638</v>
-      </c>
-      <c r="C639" t="inlineStr"/>
-      <c r="D639" t="inlineStr"/>
-      <c r="E639" t="inlineStr"/>
-    </row>
-    <row r="640">
-      <c r="A640" t="inlineStr"/>
-      <c r="B640" t="n">
-        <v>639</v>
-      </c>
-      <c r="C640" t="inlineStr"/>
-      <c r="D640" t="inlineStr"/>
-      <c r="E640" t="inlineStr"/>
-    </row>
-    <row r="641">
-      <c r="A641" t="inlineStr"/>
-      <c r="B641" t="n">
-        <v>640</v>
-      </c>
-      <c r="C641" t="inlineStr"/>
-      <c r="D641" t="inlineStr"/>
-      <c r="E641" t="inlineStr"/>
-    </row>
-    <row r="642">
-      <c r="A642" t="inlineStr"/>
-      <c r="B642" t="n">
-        <v>641</v>
-      </c>
-      <c r="C642" t="inlineStr"/>
-      <c r="D642" t="inlineStr"/>
-      <c r="E642" t="inlineStr"/>
-    </row>
-    <row r="643">
-      <c r="A643" t="inlineStr"/>
-      <c r="B643" t="n">
-        <v>642</v>
-      </c>
-      <c r="C643" t="inlineStr"/>
-      <c r="D643" t="inlineStr"/>
-      <c r="E643" t="inlineStr"/>
-    </row>
-    <row r="644">
-      <c r="A644" t="inlineStr"/>
-      <c r="B644" t="n">
-        <v>643</v>
-      </c>
-      <c r="C644" t="inlineStr"/>
-      <c r="D644" t="inlineStr"/>
-      <c r="E644" t="inlineStr"/>
-    </row>
-    <row r="645">
-      <c r="A645" t="inlineStr"/>
-      <c r="B645" t="n">
-        <v>644</v>
-      </c>
-      <c r="C645" t="inlineStr"/>
-      <c r="D645" t="inlineStr"/>
-      <c r="E645" t="inlineStr"/>
-    </row>
-    <row r="646">
-      <c r="A646" t="inlineStr"/>
-      <c r="B646" t="n">
-        <v>645</v>
-      </c>
-      <c r="C646" t="inlineStr"/>
-      <c r="D646" t="inlineStr"/>
-      <c r="E646" t="inlineStr"/>
-    </row>
-    <row r="647">
-      <c r="A647" t="inlineStr"/>
-      <c r="B647" t="n">
-        <v>646</v>
-      </c>
-      <c r="C647" t="inlineStr"/>
-      <c r="D647" t="inlineStr"/>
-      <c r="E647" t="inlineStr"/>
-    </row>
-    <row r="648">
-      <c r="A648" t="inlineStr"/>
-      <c r="B648" t="n">
-        <v>647</v>
-      </c>
-      <c r="C648" t="inlineStr"/>
-      <c r="D648" t="inlineStr"/>
-      <c r="E648" t="inlineStr"/>
-    </row>
-    <row r="649">
-      <c r="A649" t="inlineStr"/>
-      <c r="B649" t="n">
-        <v>648</v>
-      </c>
-      <c r="C649" t="inlineStr"/>
-      <c r="D649" t="inlineStr"/>
-      <c r="E649" t="inlineStr"/>
-    </row>
-    <row r="650">
-      <c r="A650" t="inlineStr"/>
-      <c r="B650" t="n">
-        <v>649</v>
-      </c>
-      <c r="C650" t="inlineStr"/>
-      <c r="D650" t="inlineStr"/>
-      <c r="E650" t="inlineStr"/>
-    </row>
-    <row r="651">
-      <c r="A651" t="inlineStr"/>
-      <c r="B651" t="n">
-        <v>650</v>
-      </c>
-      <c r="C651" t="inlineStr"/>
-      <c r="D651" t="inlineStr"/>
-      <c r="E651" t="inlineStr"/>
-    </row>
-    <row r="652">
-      <c r="A652" t="inlineStr"/>
-      <c r="B652" t="n">
-        <v>651</v>
-      </c>
-      <c r="C652" t="inlineStr"/>
-      <c r="D652" t="inlineStr"/>
-      <c r="E652" t="inlineStr"/>
-    </row>
-    <row r="653">
-      <c r="A653" t="inlineStr"/>
-      <c r="B653" t="n">
-        <v>652</v>
-      </c>
-      <c r="C653" t="inlineStr"/>
-      <c r="D653" t="inlineStr"/>
-      <c r="E653" t="inlineStr"/>
-    </row>
-    <row r="654">
-      <c r="A654" t="inlineStr"/>
-      <c r="B654" t="n">
-        <v>653</v>
-      </c>
-      <c r="C654" t="inlineStr"/>
-      <c r="D654" t="inlineStr"/>
-      <c r="E654" t="inlineStr"/>
-    </row>
-    <row r="655">
-      <c r="A655" t="inlineStr"/>
-      <c r="B655" t="n">
-        <v>654</v>
-      </c>
-      <c r="C655" t="inlineStr"/>
-      <c r="D655" t="inlineStr"/>
-      <c r="E655" t="inlineStr"/>
-    </row>
-    <row r="656">
-      <c r="A656" t="inlineStr"/>
-      <c r="B656" t="n">
-        <v>655</v>
-      </c>
-      <c r="C656" t="inlineStr"/>
-      <c r="D656" t="inlineStr"/>
-      <c r="E656" t="inlineStr"/>
-    </row>
-    <row r="657">
-      <c r="A657" t="inlineStr"/>
-      <c r="B657" t="n">
-        <v>656</v>
-      </c>
-      <c r="C657" t="inlineStr"/>
-      <c r="D657" t="inlineStr"/>
-      <c r="E657" t="inlineStr"/>
-    </row>
-    <row r="658">
-      <c r="A658" t="inlineStr"/>
-      <c r="B658" t="n">
-        <v>657</v>
-      </c>
-      <c r="C658" t="inlineStr"/>
-      <c r="D658" t="inlineStr"/>
-      <c r="E658" t="inlineStr"/>
-    </row>
-    <row r="659">
-      <c r="A659" t="inlineStr"/>
-      <c r="B659" t="n">
-        <v>658</v>
-      </c>
-      <c r="C659" t="inlineStr"/>
-      <c r="D659" t="inlineStr"/>
-      <c r="E659" t="inlineStr"/>
-    </row>
-    <row r="660">
-      <c r="A660" t="inlineStr"/>
-      <c r="B660" t="n">
-        <v>659</v>
-      </c>
-      <c r="C660" t="inlineStr"/>
-      <c r="D660" t="inlineStr"/>
-      <c r="E660" t="inlineStr"/>
-    </row>
-    <row r="661">
-      <c r="A661" t="inlineStr"/>
-      <c r="B661" t="n">
-        <v>660</v>
-      </c>
-      <c r="C661" t="inlineStr"/>
-      <c r="D661" t="inlineStr"/>
-      <c r="E661" t="inlineStr"/>
-    </row>
-    <row r="662">
-      <c r="A662" t="inlineStr"/>
-      <c r="B662" t="n">
-        <v>661</v>
-      </c>
-      <c r="C662" t="inlineStr"/>
-      <c r="D662" t="inlineStr"/>
-      <c r="E662" t="inlineStr"/>
-    </row>
-    <row r="663">
-      <c r="A663" t="inlineStr"/>
-      <c r="B663" t="n">
-        <v>662</v>
-      </c>
-      <c r="C663" t="inlineStr"/>
-      <c r="D663" t="inlineStr"/>
-      <c r="E663" t="inlineStr"/>
-    </row>
-    <row r="664">
-      <c r="A664" t="inlineStr"/>
-      <c r="B664" t="n">
-        <v>663</v>
-      </c>
-      <c r="C664" t="inlineStr"/>
-      <c r="D664" t="inlineStr"/>
-      <c r="E664" t="inlineStr"/>
-    </row>
-    <row r="665">
-      <c r="A665" t="inlineStr"/>
-      <c r="B665" t="n">
-        <v>664</v>
-      </c>
-      <c r="C665" t="inlineStr"/>
-      <c r="D665" t="inlineStr"/>
-      <c r="E665" t="inlineStr"/>
-    </row>
-    <row r="666">
-      <c r="A666" t="inlineStr"/>
-      <c r="B666" t="n">
-        <v>665</v>
-      </c>
-      <c r="C666" t="inlineStr"/>
-      <c r="D666" t="inlineStr"/>
-      <c r="E666" t="inlineStr"/>
-    </row>
-    <row r="667">
-      <c r="A667" t="inlineStr"/>
-      <c r="B667" t="n">
-        <v>666</v>
-      </c>
-      <c r="C667" t="inlineStr"/>
-      <c r="D667" t="inlineStr"/>
-      <c r="E667" t="inlineStr"/>
-    </row>
-    <row r="668">
-      <c r="A668" t="inlineStr"/>
-      <c r="B668" t="n">
-        <v>667</v>
-      </c>
-      <c r="C668" t="inlineStr"/>
-      <c r="D668" t="inlineStr"/>
-      <c r="E668" t="inlineStr"/>
-    </row>
-    <row r="669">
-      <c r="A669" t="inlineStr"/>
-      <c r="B669" t="n">
-        <v>668</v>
-      </c>
-      <c r="C669" t="inlineStr"/>
-      <c r="D669" t="inlineStr"/>
-      <c r="E669" t="inlineStr"/>
-    </row>
-    <row r="670">
-      <c r="A670" t="inlineStr"/>
-      <c r="B670" t="n">
-        <v>669</v>
-      </c>
-      <c r="C670" t="inlineStr"/>
-      <c r="D670" t="inlineStr"/>
-      <c r="E670" t="inlineStr"/>
-    </row>
-    <row r="671">
-      <c r="A671" t="inlineStr"/>
-      <c r="B671" t="n">
-        <v>670</v>
-      </c>
-      <c r="C671" t="inlineStr"/>
-      <c r="D671" t="inlineStr"/>
-      <c r="E671" t="inlineStr"/>
-    </row>
-    <row r="672">
-      <c r="A672" t="inlineStr"/>
-      <c r="B672" t="n">
-        <v>671</v>
-      </c>
-      <c r="C672" t="inlineStr"/>
-      <c r="D672" t="inlineStr"/>
-      <c r="E672" t="inlineStr"/>
-    </row>
-    <row r="673">
-      <c r="A673" t="inlineStr"/>
-      <c r="B673" t="n">
-        <v>672</v>
-      </c>
-      <c r="C673" t="inlineStr"/>
-      <c r="D673" t="inlineStr"/>
-      <c r="E673" t="inlineStr"/>
-    </row>
-    <row r="674">
-      <c r="A674" t="inlineStr"/>
-      <c r="B674" t="n">
-        <v>673</v>
-      </c>
-      <c r="C674" t="inlineStr"/>
-      <c r="D674" t="inlineStr"/>
-      <c r="E674" t="inlineStr"/>
-    </row>
-    <row r="675">
-      <c r="A675" t="inlineStr"/>
-      <c r="B675" t="n">
-        <v>674</v>
-      </c>
-      <c r="C675" t="inlineStr"/>
-      <c r="D675" t="inlineStr"/>
-      <c r="E675" t="inlineStr"/>
-    </row>
-    <row r="676">
-      <c r="A676" t="inlineStr"/>
-      <c r="B676" t="n">
-        <v>675</v>
-      </c>
-      <c r="C676" t="inlineStr"/>
-      <c r="D676" t="inlineStr"/>
-      <c r="E676" t="inlineStr"/>
-    </row>
-    <row r="677">
-      <c r="A677" t="inlineStr"/>
-      <c r="B677" t="n">
-        <v>676</v>
-      </c>
-      <c r="C677" t="inlineStr"/>
-      <c r="D677" t="inlineStr"/>
-      <c r="E677" t="inlineStr"/>
-    </row>
-    <row r="678">
-      <c r="A678" t="inlineStr"/>
-      <c r="B678" t="n">
-        <v>677</v>
-      </c>
-      <c r="C678" t="inlineStr"/>
-      <c r="D678" t="inlineStr"/>
-      <c r="E678" t="inlineStr"/>
-    </row>
-    <row r="679">
-      <c r="A679" t="inlineStr"/>
-      <c r="B679" t="n">
-        <v>678</v>
-      </c>
-      <c r="C679" t="inlineStr"/>
-      <c r="D679" t="inlineStr"/>
-      <c r="E679" t="inlineStr"/>
-    </row>
-    <row r="680">
-      <c r="A680" t="inlineStr"/>
-      <c r="B680" t="n">
-        <v>679</v>
-      </c>
-      <c r="C680" t="inlineStr"/>
-      <c r="D680" t="inlineStr"/>
-      <c r="E680" t="inlineStr"/>
-    </row>
-    <row r="681">
-      <c r="A681" t="inlineStr"/>
-      <c r="B681" t="n">
-        <v>680</v>
-      </c>
-      <c r="C681" t="inlineStr"/>
-      <c r="D681" t="inlineStr"/>
-      <c r="E681" t="inlineStr"/>
-    </row>
-    <row r="682">
-      <c r="A682" t="inlineStr"/>
-      <c r="B682" t="n">
-        <v>681</v>
-      </c>
-      <c r="C682" t="inlineStr"/>
-      <c r="D682" t="inlineStr"/>
-      <c r="E682" t="inlineStr"/>
-    </row>
-    <row r="683">
-      <c r="A683" t="inlineStr"/>
-      <c r="B683" t="n">
-        <v>682</v>
-      </c>
-      <c r="C683" t="inlineStr"/>
-      <c r="D683" t="inlineStr"/>
-      <c r="E683" t="inlineStr"/>
-    </row>
-    <row r="684">
-      <c r="A684" t="inlineStr"/>
-      <c r="B684" t="n">
-        <v>683</v>
-      </c>
-      <c r="C684" t="inlineStr"/>
-      <c r="D684" t="inlineStr"/>
-      <c r="E684" t="inlineStr"/>
-    </row>
-    <row r="685">
-      <c r="A685" t="inlineStr"/>
-      <c r="B685" t="n">
-        <v>684</v>
-      </c>
-      <c r="C685" t="inlineStr"/>
-      <c r="D685" t="inlineStr"/>
-      <c r="E685" t="inlineStr"/>
-    </row>
-    <row r="686">
-      <c r="A686" t="inlineStr"/>
-      <c r="B686" t="n">
-        <v>685</v>
-      </c>
-      <c r="C686" t="inlineStr"/>
-      <c r="D686" t="inlineStr"/>
-      <c r="E686" t="inlineStr"/>
-    </row>
-    <row r="687">
-      <c r="A687" t="inlineStr"/>
-      <c r="B687" t="n">
-        <v>686</v>
-      </c>
-      <c r="C687" t="inlineStr"/>
-      <c r="D687" t="inlineStr"/>
-      <c r="E687" t="inlineStr"/>
-    </row>
-    <row r="688">
-      <c r="A688" t="inlineStr"/>
-      <c r="B688" t="n">
-        <v>687</v>
-      </c>
-      <c r="C688" t="inlineStr"/>
-      <c r="D688" t="inlineStr"/>
-      <c r="E688" t="inlineStr"/>
-    </row>
-    <row r="689">
-      <c r="A689" t="inlineStr"/>
-      <c r="B689" t="n">
-        <v>688</v>
-      </c>
-      <c r="C689" t="inlineStr"/>
-      <c r="D689" t="inlineStr"/>
-      <c r="E689" t="inlineStr"/>
-    </row>
-    <row r="690">
-      <c r="A690" t="inlineStr"/>
-      <c r="B690" t="n">
-        <v>689</v>
-      </c>
-      <c r="C690" t="inlineStr"/>
-      <c r="D690" t="inlineStr"/>
-      <c r="E690" t="inlineStr"/>
-    </row>
-    <row r="691">
-      <c r="A691" t="inlineStr"/>
-      <c r="B691" t="n">
-        <v>690</v>
-      </c>
-      <c r="C691" t="inlineStr"/>
-      <c r="D691" t="inlineStr"/>
-      <c r="E691" t="inlineStr"/>
-    </row>
-    <row r="692">
-      <c r="A692" t="inlineStr"/>
-      <c r="B692" t="n">
-        <v>691</v>
-      </c>
-      <c r="C692" t="inlineStr"/>
-      <c r="D692" t="inlineStr"/>
-      <c r="E692" t="inlineStr"/>
-    </row>
-    <row r="693">
-      <c r="A693" t="inlineStr"/>
-      <c r="B693" t="n">
-        <v>692</v>
-      </c>
-      <c r="C693" t="inlineStr"/>
-      <c r="D693" t="inlineStr"/>
-      <c r="E693" t="inlineStr"/>
-    </row>
-    <row r="694">
-      <c r="A694" t="inlineStr"/>
-      <c r="B694" t="n">
-        <v>693</v>
-      </c>
-      <c r="C694" t="inlineStr"/>
-      <c r="D694" t="inlineStr"/>
-      <c r="E694" t="inlineStr"/>
-    </row>
-    <row r="695">
-      <c r="A695" t="inlineStr"/>
-      <c r="B695" t="n">
-        <v>694</v>
-      </c>
-      <c r="C695" t="inlineStr"/>
-      <c r="D695" t="inlineStr"/>
-      <c r="E695" t="inlineStr"/>
-    </row>
-    <row r="696">
-      <c r="A696" t="inlineStr"/>
-      <c r="B696" t="n">
-        <v>695</v>
-      </c>
-      <c r="C696" t="inlineStr"/>
-      <c r="D696" t="inlineStr"/>
-      <c r="E696" t="inlineStr"/>
-    </row>
-    <row r="697">
-      <c r="A697" t="inlineStr"/>
-      <c r="B697" t="n">
-        <v>696</v>
-      </c>
-      <c r="C697" t="inlineStr"/>
-      <c r="D697" t="inlineStr"/>
-      <c r="E697" t="inlineStr"/>
-    </row>
-    <row r="698">
-      <c r="A698" t="inlineStr"/>
-      <c r="B698" t="n">
-        <v>697</v>
-      </c>
-      <c r="C698" t="inlineStr"/>
-      <c r="D698" t="inlineStr"/>
-      <c r="E698" t="inlineStr"/>
-    </row>
-    <row r="699">
-      <c r="A699" t="inlineStr"/>
-      <c r="B699" t="n">
-        <v>698</v>
-      </c>
-      <c r="C699" t="inlineStr"/>
-      <c r="D699" t="inlineStr"/>
-      <c r="E699" t="inlineStr"/>
-    </row>
-    <row r="700">
-      <c r="A700" t="inlineStr"/>
-      <c r="B700" t="n">
-        <v>699</v>
-      </c>
-      <c r="C700" t="inlineStr"/>
-      <c r="D700" t="inlineStr"/>
-      <c r="E700" t="inlineStr"/>
-    </row>
-    <row r="701">
-      <c r="A701" t="inlineStr"/>
-      <c r="B701" t="n">
-        <v>700</v>
-      </c>
-      <c r="C701" t="inlineStr"/>
-      <c r="D701" t="inlineStr"/>
-      <c r="E701" t="inlineStr"/>
-    </row>
-    <row r="702">
-      <c r="A702" t="inlineStr"/>
-      <c r="B702" t="n">
-        <v>701</v>
-      </c>
-      <c r="C702" t="inlineStr"/>
-      <c r="D702" t="inlineStr"/>
-      <c r="E702" t="inlineStr"/>
-    </row>
-    <row r="703">
-      <c r="A703" t="inlineStr"/>
-      <c r="B703" t="n">
-        <v>702</v>
-      </c>
-      <c r="C703" t="inlineStr"/>
-      <c r="D703" t="inlineStr"/>
-      <c r="E703" t="inlineStr"/>
-    </row>
-    <row r="704">
-      <c r="A704" t="inlineStr"/>
-      <c r="B704" t="n">
-        <v>703</v>
-      </c>
-      <c r="C704" t="inlineStr"/>
-      <c r="D704" t="inlineStr"/>
-      <c r="E704" t="inlineStr"/>
-    </row>
-    <row r="705">
-      <c r="A705" t="inlineStr"/>
-      <c r="B705" t="n">
-        <v>704</v>
-      </c>
-      <c r="C705" t="inlineStr"/>
-      <c r="D705" t="inlineStr"/>
-      <c r="E705" t="inlineStr"/>
-    </row>
-    <row r="706">
-      <c r="A706" t="inlineStr"/>
-      <c r="B706" t="n">
-        <v>705</v>
-      </c>
-      <c r="C706" t="inlineStr"/>
-      <c r="D706" t="inlineStr"/>
-      <c r="E706" t="inlineStr"/>
-    </row>
-    <row r="707">
-      <c r="A707" t="inlineStr"/>
-      <c r="B707" t="n">
-        <v>706</v>
-      </c>
-      <c r="C707" t="inlineStr"/>
-      <c r="D707" t="inlineStr"/>
-      <c r="E707" t="inlineStr"/>
-    </row>
-    <row r="708">
-      <c r="A708" t="inlineStr"/>
-      <c r="B708" t="n">
-        <v>707</v>
-      </c>
-      <c r="C708" t="inlineStr"/>
-      <c r="D708" t="inlineStr"/>
-      <c r="E708" t="inlineStr"/>
-    </row>
-    <row r="709">
-      <c r="A709" t="inlineStr"/>
-      <c r="B709" t="n">
-        <v>708</v>
-      </c>
-      <c r="C709" t="inlineStr"/>
-      <c r="D709" t="inlineStr"/>
-      <c r="E709" t="inlineStr"/>
-    </row>
-    <row r="710">
-      <c r="A710" t="inlineStr"/>
-      <c r="B710" t="n">
-        <v>709</v>
-      </c>
-      <c r="C710" t="inlineStr"/>
-      <c r="D710" t="inlineStr"/>
-      <c r="E710" t="inlineStr"/>
-    </row>
-    <row r="711">
-      <c r="A711" t="inlineStr"/>
-      <c r="B711" t="n">
-        <v>710</v>
-      </c>
-      <c r="C711" t="inlineStr"/>
-      <c r="D711" t="inlineStr"/>
-      <c r="E711" t="inlineStr"/>
-    </row>
-    <row r="712">
-      <c r="A712" t="inlineStr"/>
-      <c r="B712" t="n">
-        <v>711</v>
-      </c>
-      <c r="C712" t="inlineStr"/>
-      <c r="D712" t="inlineStr"/>
-      <c r="E712" t="inlineStr"/>
-    </row>
-    <row r="713">
-      <c r="A713" t="inlineStr"/>
-      <c r="B713" t="n">
-        <v>712</v>
-      </c>
-      <c r="C713" t="inlineStr"/>
-      <c r="D713" t="inlineStr"/>
-      <c r="E713" t="inlineStr"/>
-    </row>
-    <row r="714">
-      <c r="A714" t="inlineStr"/>
-      <c r="B714" t="n">
-        <v>713</v>
-      </c>
-      <c r="C714" t="inlineStr"/>
-      <c r="D714" t="inlineStr"/>
-      <c r="E714" t="inlineStr"/>
-    </row>
-    <row r="715">
-      <c r="A715" t="inlineStr"/>
-      <c r="B715" t="n">
-        <v>714</v>
-      </c>
-      <c r="C715" t="inlineStr"/>
-      <c r="D715" t="inlineStr"/>
-      <c r="E715" t="inlineStr"/>
-    </row>
-    <row r="716">
-      <c r="A716" t="inlineStr"/>
-      <c r="B716" t="n">
-        <v>715</v>
-      </c>
-      <c r="C716" t="inlineStr"/>
-      <c r="D716" t="inlineStr"/>
-      <c r="E716" t="inlineStr"/>
-    </row>
-    <row r="717">
-      <c r="A717" t="inlineStr"/>
-      <c r="B717" t="n">
-        <v>716</v>
-      </c>
-      <c r="C717" t="inlineStr"/>
-      <c r="D717" t="inlineStr"/>
-      <c r="E717" t="inlineStr"/>
-    </row>
-    <row r="718">
-      <c r="A718" t="inlineStr"/>
-      <c r="B718" t="n">
-        <v>717</v>
-      </c>
-      <c r="C718" t="inlineStr"/>
-      <c r="D718" t="inlineStr"/>
-      <c r="E718" t="inlineStr"/>
-    </row>
-    <row r="719">
-      <c r="A719" t="inlineStr"/>
-      <c r="B719" t="n">
-        <v>718</v>
-      </c>
-      <c r="C719" t="inlineStr"/>
-      <c r="D719" t="inlineStr"/>
-      <c r="E719" t="inlineStr"/>
-    </row>
-    <row r="720">
-      <c r="A720" t="inlineStr"/>
-      <c r="B720" t="n">
-        <v>719</v>
-      </c>
-      <c r="C720" t="inlineStr"/>
-      <c r="D720" t="inlineStr"/>
-      <c r="E720" t="inlineStr"/>
-    </row>
-    <row r="721">
-      <c r="A721" t="inlineStr"/>
-      <c r="B721" t="n">
-        <v>720</v>
-      </c>
-      <c r="C721" t="inlineStr"/>
-      <c r="D721" t="inlineStr"/>
-      <c r="E721" t="inlineStr"/>
-    </row>
-    <row r="722">
-      <c r="A722" t="inlineStr"/>
-      <c r="B722" t="n">
-        <v>721</v>
-      </c>
-      <c r="C722" t="inlineStr"/>
-      <c r="D722" t="inlineStr"/>
-      <c r="E722" t="inlineStr"/>
-    </row>
-    <row r="723">
-      <c r="A723" t="inlineStr"/>
-      <c r="B723" t="n">
-        <v>722</v>
-      </c>
-      <c r="C723" t="inlineStr"/>
-      <c r="D723" t="inlineStr"/>
-      <c r="E723" t="inlineStr"/>
-    </row>
-    <row r="724">
-      <c r="A724" t="inlineStr"/>
-      <c r="B724" t="n">
-        <v>723</v>
-      </c>
-      <c r="C724" t="inlineStr"/>
-      <c r="D724" t="inlineStr"/>
-      <c r="E724" t="inlineStr"/>
-    </row>
-    <row r="725">
-      <c r="A725" t="inlineStr"/>
-      <c r="B725" t="n">
-        <v>724</v>
-      </c>
-      <c r="C725" t="inlineStr"/>
-      <c r="D725" t="inlineStr"/>
-      <c r="E725" t="inlineStr"/>
-    </row>
-    <row r="726">
-      <c r="A726" t="inlineStr"/>
-      <c r="B726" t="n">
-        <v>725</v>
-      </c>
-      <c r="C726" t="inlineStr"/>
-      <c r="D726" t="inlineStr"/>
-      <c r="E726" t="inlineStr"/>
-    </row>
-    <row r="727">
-      <c r="A727" t="inlineStr"/>
-      <c r="B727" t="n">
-        <v>726</v>
-      </c>
-      <c r="C727" t="inlineStr"/>
-      <c r="D727" t="inlineStr"/>
-      <c r="E727" t="inlineStr"/>
-    </row>
-    <row r="728">
-      <c r="A728" t="inlineStr"/>
-      <c r="B728" t="n">
-        <v>727</v>
-      </c>
-      <c r="C728" t="inlineStr"/>
-      <c r="D728" t="inlineStr"/>
-      <c r="E728" t="inlineStr"/>
-    </row>
-    <row r="729">
-      <c r="A729" t="inlineStr"/>
-      <c r="B729" t="n">
-        <v>728</v>
-      </c>
-      <c r="C729" t="inlineStr"/>
-      <c r="D729" t="inlineStr"/>
-      <c r="E729" t="inlineStr"/>
-    </row>
-    <row r="730">
-      <c r="A730" t="inlineStr"/>
-      <c r="B730" t="n">
-        <v>729</v>
-      </c>
-      <c r="C730" t="inlineStr"/>
-      <c r="D730" t="inlineStr"/>
-      <c r="E730" t="inlineStr"/>
-    </row>
-    <row r="731">
-      <c r="A731" t="inlineStr"/>
-      <c r="B731" t="n">
-        <v>730</v>
-      </c>
-      <c r="C731" t="inlineStr"/>
-      <c r="D731" t="inlineStr"/>
-      <c r="E731" t="inlineStr"/>
-    </row>
-    <row r="732">
-      <c r="A732" t="inlineStr"/>
-      <c r="B732" t="n">
-        <v>731</v>
-      </c>
-      <c r="C732" t="inlineStr"/>
-      <c r="D732" t="inlineStr"/>
-      <c r="E732" t="inlineStr"/>
-    </row>
-    <row r="733">
-      <c r="A733" t="inlineStr"/>
-      <c r="B733" t="n">
-        <v>732</v>
-      </c>
-      <c r="C733" t="inlineStr"/>
-      <c r="D733" t="inlineStr"/>
-      <c r="E733" t="inlineStr"/>
-    </row>
-    <row r="734">
-      <c r="A734" t="inlineStr"/>
-      <c r="B734" t="n">
-        <v>733</v>
-      </c>
-      <c r="C734" t="inlineStr"/>
-      <c r="D734" t="inlineStr"/>
-      <c r="E734" t="inlineStr"/>
-    </row>
-    <row r="735">
-      <c r="A735" t="inlineStr"/>
-      <c r="B735" t="n">
-        <v>734</v>
-      </c>
-      <c r="C735" t="inlineStr"/>
-      <c r="D735" t="inlineStr"/>
-      <c r="E735" t="inlineStr"/>
-    </row>
-    <row r="736">
-      <c r="A736" t="inlineStr"/>
-      <c r="B736" t="n">
-        <v>735</v>
-      </c>
-      <c r="C736" t="inlineStr"/>
-      <c r="D736" t="inlineStr"/>
-      <c r="E736" t="inlineStr"/>
-    </row>
-    <row r="737">
-      <c r="A737" t="inlineStr"/>
-      <c r="B737" t="n">
-        <v>736</v>
-      </c>
-      <c r="C737" t="inlineStr"/>
-      <c r="D737" t="inlineStr"/>
-      <c r="E737" t="inlineStr"/>
-    </row>
-    <row r="738">
-      <c r="A738" t="inlineStr"/>
-      <c r="B738" t="n">
-        <v>737</v>
-      </c>
-      <c r="C738" t="inlineStr"/>
-      <c r="D738" t="inlineStr"/>
-      <c r="E738" t="inlineStr"/>
-    </row>
-    <row r="739">
-      <c r="A739" t="inlineStr"/>
-      <c r="B739" t="n">
-        <v>738</v>
-      </c>
-      <c r="C739" t="inlineStr"/>
-      <c r="D739" t="inlineStr"/>
-      <c r="E739" t="inlineStr"/>
-    </row>
-    <row r="740">
-      <c r="A740" t="inlineStr"/>
-      <c r="B740" t="n">
-        <v>739</v>
-      </c>
-      <c r="C740" t="inlineStr"/>
-      <c r="D740" t="inlineStr"/>
-      <c r="E740" t="inlineStr"/>
-    </row>
-    <row r="741">
-      <c r="A741" t="inlineStr"/>
-      <c r="B741" t="n">
-        <v>740</v>
-      </c>
-      <c r="C741" t="inlineStr"/>
-      <c r="D741" t="inlineStr"/>
-      <c r="E741" t="inlineStr"/>
-    </row>
-    <row r="742">
-      <c r="A742" t="inlineStr"/>
-      <c r="B742" t="n">
-        <v>741</v>
-      </c>
-      <c r="C742" t="inlineStr"/>
-      <c r="D742" t="inlineStr"/>
-      <c r="E742" t="inlineStr"/>
-    </row>
-    <row r="743">
-      <c r="A743" t="inlineStr"/>
-      <c r="B743" t="n">
-        <v>742</v>
-      </c>
-      <c r="C743" t="inlineStr"/>
-      <c r="D743" t="inlineStr"/>
-      <c r="E743" t="inlineStr"/>
-    </row>
-    <row r="744">
-      <c r="A744" t="inlineStr"/>
-      <c r="B744" t="n">
-        <v>743</v>
-      </c>
-      <c r="C744" t="inlineStr"/>
-      <c r="D744" t="inlineStr"/>
-      <c r="E744" t="inlineStr"/>
-    </row>
-    <row r="745">
-      <c r="A745" t="inlineStr"/>
-      <c r="B745" t="n">
-        <v>744</v>
-      </c>
-      <c r="C745" t="inlineStr"/>
-      <c r="D745" t="inlineStr"/>
-      <c r="E745" t="inlineStr"/>
-    </row>
-    <row r="746">
-      <c r="A746" t="inlineStr"/>
-      <c r="B746" t="n">
-        <v>745</v>
-      </c>
-      <c r="C746" t="inlineStr"/>
-      <c r="D746" t="inlineStr"/>
-      <c r="E746" t="inlineStr"/>
-    </row>
-    <row r="747">
-      <c r="A747" t="inlineStr"/>
-      <c r="B747" t="n">
-        <v>746</v>
-      </c>
-      <c r="C747" t="inlineStr"/>
-      <c r="D747" t="inlineStr"/>
-      <c r="E747" t="inlineStr"/>
-    </row>
-    <row r="748">
-      <c r="A748" t="inlineStr"/>
-      <c r="B748" t="n">
-        <v>747</v>
-      </c>
-      <c r="C748" t="inlineStr"/>
-      <c r="D748" t="inlineStr"/>
-      <c r="E748" t="inlineStr"/>
-    </row>
-    <row r="749">
-      <c r="A749" t="inlineStr"/>
-      <c r="B749" t="n">
-        <v>748</v>
-      </c>
-      <c r="C749" t="inlineStr"/>
-      <c r="D749" t="inlineStr"/>
-      <c r="E749" t="inlineStr"/>
-    </row>
-    <row r="750">
-      <c r="A750" t="inlineStr"/>
-      <c r="B750" t="n">
-        <v>749</v>
-      </c>
-      <c r="C750" t="inlineStr"/>
-      <c r="D750" t="inlineStr"/>
-      <c r="E750" t="inlineStr"/>
-    </row>
-    <row r="751">
-      <c r="A751" t="inlineStr"/>
-      <c r="B751" t="n">
-        <v>750</v>
-      </c>
-      <c r="C751" t="inlineStr"/>
-      <c r="D751" t="inlineStr"/>
-      <c r="E751" t="inlineStr"/>
-    </row>
-    <row r="752">
-      <c r="A752" t="inlineStr"/>
-      <c r="B752" t="n">
-        <v>751</v>
-      </c>
-      <c r="C752" t="inlineStr"/>
-      <c r="D752" t="inlineStr"/>
-      <c r="E752" t="inlineStr"/>
-    </row>
-    <row r="753">
-      <c r="A753" t="inlineStr"/>
-      <c r="B753" t="n">
-        <v>752</v>
-      </c>
-      <c r="C753" t="inlineStr"/>
-      <c r="D753" t="inlineStr"/>
-      <c r="E753" t="inlineStr"/>
-    </row>
-    <row r="754">
-      <c r="A754" t="inlineStr"/>
-      <c r="B754" t="n">
-        <v>753</v>
-      </c>
-      <c r="C754" t="inlineStr"/>
-      <c r="D754" t="inlineStr"/>
-      <c r="E754" t="inlineStr"/>
-    </row>
-    <row r="755">
-      <c r="A755" t="inlineStr"/>
-      <c r="B755" t="n">
-        <v>754</v>
-      </c>
-      <c r="C755" t="inlineStr"/>
-      <c r="D755" t="inlineStr"/>
-      <c r="E755" t="inlineStr"/>
-    </row>
-    <row r="756">
-      <c r="A756" t="inlineStr"/>
-      <c r="B756" t="n">
-        <v>755</v>
-      </c>
-      <c r="C756" t="inlineStr"/>
-      <c r="D756" t="inlineStr"/>
-      <c r="E756" t="inlineStr"/>
-    </row>
-    <row r="757">
-      <c r="A757" t="inlineStr"/>
-      <c r="B757" t="n">
-        <v>756</v>
-      </c>
-      <c r="C757" t="inlineStr"/>
-      <c r="D757" t="inlineStr"/>
-      <c r="E757" t="inlineStr"/>
-    </row>
-    <row r="758">
-      <c r="A758" t="inlineStr"/>
-      <c r="B758" t="n">
-        <v>757</v>
-      </c>
-      <c r="C758" t="inlineStr"/>
-      <c r="D758" t="inlineStr"/>
-      <c r="E758" t="inlineStr"/>
-    </row>
-    <row r="759">
-      <c r="A759" t="inlineStr"/>
-      <c r="B759" t="n">
-        <v>758</v>
-      </c>
-      <c r="C759" t="inlineStr"/>
-      <c r="D759" t="inlineStr"/>
-      <c r="E759" t="inlineStr"/>
-    </row>
-    <row r="760">
-      <c r="A760" t="inlineStr"/>
-      <c r="B760" t="n">
-        <v>759</v>
-      </c>
-      <c r="C760" t="inlineStr"/>
-      <c r="D760" t="inlineStr"/>
-      <c r="E760" t="inlineStr"/>
-    </row>
-    <row r="761">
-      <c r="A761" t="inlineStr"/>
-      <c r="B761" t="n">
-        <v>760</v>
-      </c>
-      <c r="C761" t="inlineStr"/>
-      <c r="D761" t="inlineStr"/>
-      <c r="E761" t="inlineStr"/>
-    </row>
-    <row r="762">
-      <c r="A762" t="inlineStr"/>
-      <c r="B762" t="n">
-        <v>761</v>
-      </c>
-      <c r="C762" t="inlineStr"/>
-      <c r="D762" t="inlineStr"/>
-      <c r="E762" t="inlineStr"/>
-    </row>
-    <row r="763">
-      <c r="A763" t="inlineStr"/>
-      <c r="B763" t="n">
-        <v>762</v>
-      </c>
-      <c r="C763" t="inlineStr"/>
-      <c r="D763" t="inlineStr"/>
-      <c r="E763" t="inlineStr"/>
-    </row>
-    <row r="764">
-      <c r="A764" t="inlineStr"/>
-      <c r="B764" t="n">
-        <v>763</v>
-      </c>
-      <c r="C764" t="inlineStr"/>
-      <c r="D764" t="inlineStr"/>
-      <c r="E764" t="inlineStr"/>
-    </row>
-    <row r="765">
-      <c r="A765" t="inlineStr"/>
-      <c r="B765" t="n">
-        <v>764</v>
-      </c>
-      <c r="C765" t="inlineStr"/>
-      <c r="D765" t="inlineStr"/>
-      <c r="E765" t="inlineStr"/>
-    </row>
-    <row r="766">
-      <c r="A766" t="inlineStr"/>
-      <c r="B766" t="n">
-        <v>765</v>
-      </c>
-      <c r="C766" t="inlineStr"/>
-      <c r="D766" t="inlineStr"/>
-      <c r="E766" t="inlineStr"/>
-    </row>
-    <row r="767">
-      <c r="A767" t="inlineStr"/>
-      <c r="B767" t="n">
-        <v>766</v>
-      </c>
-      <c r="C767" t="inlineStr"/>
-      <c r="D767" t="inlineStr"/>
-      <c r="E767" t="inlineStr"/>
-    </row>
-    <row r="768">
-      <c r="A768" t="inlineStr"/>
-      <c r="B768" t="n">
-        <v>767</v>
-      </c>
-      <c r="C768" t="inlineStr"/>
-      <c r="D768" t="inlineStr"/>
-      <c r="E768" t="inlineStr"/>
-    </row>
-    <row r="769">
-      <c r="A769" t="inlineStr"/>
-      <c r="B769" t="n">
-        <v>768</v>
-      </c>
-      <c r="C769" t="inlineStr"/>
-      <c r="D769" t="inlineStr"/>
-      <c r="E769" t="inlineStr"/>
-    </row>
-    <row r="770">
-      <c r="A770" t="inlineStr"/>
-      <c r="B770" t="n">
-        <v>769</v>
-      </c>
-      <c r="C770" t="inlineStr"/>
-      <c r="D770" t="inlineStr"/>
-      <c r="E770" t="inlineStr"/>
-    </row>
-    <row r="771">
-      <c r="A771" t="inlineStr"/>
-      <c r="B771" t="n">
-        <v>770</v>
-      </c>
-      <c r="C771" t="inlineStr"/>
-      <c r="D771" t="inlineStr"/>
-      <c r="E771" t="inlineStr"/>
-    </row>
-    <row r="772">
-      <c r="A772" t="inlineStr"/>
-      <c r="B772" t="n">
-        <v>771</v>
-      </c>
-      <c r="C772" t="inlineStr"/>
-      <c r="D772" t="inlineStr"/>
-      <c r="E772" t="inlineStr"/>
-    </row>
-    <row r="773">
-      <c r="A773" t="inlineStr"/>
-      <c r="B773" t="n">
-        <v>772</v>
-      </c>
-      <c r="C773" t="inlineStr"/>
-      <c r="D773" t="inlineStr"/>
-      <c r="E773" t="inlineStr"/>
-    </row>
-    <row r="774">
-      <c r="A774" t="inlineStr"/>
-      <c r="B774" t="n">
-        <v>773</v>
-      </c>
-      <c r="C774" t="inlineStr"/>
-      <c r="D774" t="inlineStr"/>
-      <c r="E774" t="inlineStr"/>
-    </row>
-    <row r="775">
-      <c r="A775" t="inlineStr"/>
-      <c r="B775" t="n">
-        <v>774</v>
-      </c>
-      <c r="C775" t="inlineStr"/>
-      <c r="D775" t="inlineStr"/>
-      <c r="E775" t="inlineStr"/>
-    </row>
-    <row r="776">
-      <c r="A776" t="inlineStr"/>
-      <c r="B776" t="n">
-        <v>775</v>
-      </c>
-      <c r="C776" t="inlineStr"/>
-      <c r="D776" t="inlineStr"/>
-      <c r="E776" t="inlineStr"/>
-    </row>
-    <row r="777">
-      <c r="A777" t="inlineStr"/>
-      <c r="B777" t="n">
-        <v>776</v>
-      </c>
-      <c r="C777" t="inlineStr"/>
-      <c r="D777" t="inlineStr"/>
-      <c r="E777" t="inlineStr"/>
-    </row>
-    <row r="778">
-      <c r="A778" t="inlineStr"/>
-      <c r="B778" t="n">
-        <v>777</v>
-      </c>
-      <c r="C778" t="inlineStr"/>
-      <c r="D778" t="inlineStr"/>
-      <c r="E778" t="inlineStr"/>
-    </row>
-    <row r="779">
-      <c r="A779" t="inlineStr"/>
-      <c r="B779" t="n">
-        <v>778</v>
-      </c>
-      <c r="C779" t="inlineStr"/>
-      <c r="D779" t="inlineStr"/>
-      <c r="E779" t="inlineStr"/>
-    </row>
-    <row r="780">
-      <c r="A780" t="inlineStr"/>
-      <c r="B780" t="n">
-        <v>779</v>
-      </c>
-      <c r="C780" t="inlineStr"/>
-      <c r="D780" t="inlineStr"/>
-      <c r="E780" t="inlineStr"/>
-    </row>
-    <row r="781">
-      <c r="A781" t="inlineStr"/>
-      <c r="B781" t="n">
-        <v>780</v>
-      </c>
-      <c r="C781" t="inlineStr"/>
-      <c r="D781" t="inlineStr"/>
-      <c r="E781" t="inlineStr"/>
-    </row>
-    <row r="782">
-      <c r="A782" t="inlineStr"/>
-      <c r="B782" t="n">
-        <v>781</v>
-      </c>
-      <c r="C782" t="inlineStr"/>
-      <c r="D782" t="inlineStr"/>
-      <c r="E782" t="inlineStr"/>
-    </row>
-    <row r="783">
-      <c r="A783" t="inlineStr"/>
-      <c r="B783" t="n">
-        <v>782</v>
-      </c>
-      <c r="C783" t="inlineStr"/>
-      <c r="D783" t="inlineStr"/>
-      <c r="E783" t="inlineStr"/>
-    </row>
-    <row r="784">
-      <c r="A784" t="inlineStr"/>
-      <c r="B784" t="n">
-        <v>783</v>
-      </c>
-      <c r="C784" t="inlineStr"/>
-      <c r="D784" t="inlineStr"/>
-      <c r="E784" t="inlineStr"/>
-    </row>
-    <row r="785">
-      <c r="A785" t="inlineStr"/>
-      <c r="B785" t="n">
-        <v>784</v>
-      </c>
-      <c r="C785" t="inlineStr"/>
-      <c r="D785" t="inlineStr"/>
-      <c r="E785" t="inlineStr"/>
-    </row>
-    <row r="786">
-      <c r="A786" t="inlineStr"/>
-      <c r="B786" t="n">
-        <v>785</v>
-      </c>
-      <c r="C786" t="inlineStr"/>
-      <c r="D786" t="inlineStr"/>
-      <c r="E786" t="inlineStr"/>
-    </row>
-    <row r="787">
-      <c r="A787" t="inlineStr"/>
-      <c r="B787" t="n">
-        <v>786</v>
-      </c>
-      <c r="C787" t="inlineStr"/>
-      <c r="D787" t="inlineStr"/>
-      <c r="E787" t="inlineStr"/>
-    </row>
-    <row r="788">
-      <c r="A788" t="inlineStr"/>
-      <c r="B788" t="n">
-        <v>787</v>
-      </c>
-      <c r="C788" t="inlineStr"/>
-      <c r="D788" t="inlineStr"/>
-      <c r="E788" t="inlineStr"/>
-    </row>
-    <row r="789">
-      <c r="A789" t="inlineStr"/>
-      <c r="B789" t="n">
-        <v>788</v>
-      </c>
-      <c r="C789" t="inlineStr"/>
-      <c r="D789" t="inlineStr"/>
-      <c r="E789" t="inlineStr"/>
-    </row>
-    <row r="790">
-      <c r="A790" t="inlineStr"/>
-      <c r="B790" t="n">
-        <v>789</v>
-      </c>
-      <c r="C790" t="inlineStr"/>
-      <c r="D790" t="inlineStr"/>
-      <c r="E790" t="inlineStr"/>
-    </row>
-    <row r="791">
-      <c r="A791" t="inlineStr"/>
-      <c r="B791" t="n">
-        <v>790</v>
-      </c>
-      <c r="C791" t="inlineStr"/>
-      <c r="D791" t="inlineStr"/>
-      <c r="E791" t="inlineStr"/>
-    </row>
-    <row r="792">
-      <c r="A792" t="inlineStr"/>
-      <c r="B792" t="n">
-        <v>791</v>
-      </c>
-      <c r="C792" t="inlineStr"/>
-      <c r="D792" t="inlineStr"/>
-      <c r="E792" t="inlineStr"/>
-    </row>
-    <row r="793">
-      <c r="A793" t="inlineStr"/>
-      <c r="B793" t="n">
-        <v>792</v>
-      </c>
-      <c r="C793" t="inlineStr"/>
-      <c r="D793" t="inlineStr"/>
-      <c r="E793" t="inlineStr"/>
-    </row>
-    <row r="794">
-      <c r="A794" t="inlineStr"/>
-      <c r="B794" t="n">
-        <v>793</v>
-      </c>
-      <c r="C794" t="inlineStr"/>
-      <c r="D794" t="inlineStr"/>
-      <c r="E794" t="inlineStr"/>
-    </row>
-    <row r="795">
-      <c r="A795" t="inlineStr"/>
-      <c r="B795" t="n">
-        <v>794</v>
-      </c>
-      <c r="C795" t="inlineStr"/>
-      <c r="D795" t="inlineStr"/>
-      <c r="E795" t="inlineStr"/>
-    </row>
-    <row r="796">
-      <c r="A796" t="inlineStr"/>
-      <c r="B796" t="n">
-        <v>795</v>
-      </c>
-      <c r="C796" t="inlineStr"/>
-      <c r="D796" t="inlineStr"/>
-      <c r="E796" t="inlineStr"/>
-    </row>
-    <row r="797">
-      <c r="A797" t="inlineStr"/>
-      <c r="B797" t="n">
-        <v>796</v>
-      </c>
-      <c r="C797" t="inlineStr"/>
-      <c r="D797" t="inlineStr"/>
-      <c r="E797" t="inlineStr"/>
-    </row>
-    <row r="798">
-      <c r="A798" t="inlineStr"/>
-      <c r="B798" t="n">
-        <v>797</v>
-      </c>
-      <c r="C798" t="inlineStr"/>
-      <c r="D798" t="inlineStr"/>
-      <c r="E798" t="inlineStr"/>
-    </row>
-    <row r="799">
-      <c r="A799" t="inlineStr"/>
-      <c r="B799" t="n">
-        <v>798</v>
-      </c>
-      <c r="C799" t="inlineStr"/>
-      <c r="D799" t="inlineStr"/>
-      <c r="E799" t="inlineStr"/>
-    </row>
-    <row r="800">
-      <c r="A800" t="inlineStr"/>
-      <c r="B800" t="n">
-        <v>799</v>
-      </c>
-      <c r="C800" t="inlineStr"/>
-      <c r="D800" t="inlineStr"/>
-      <c r="E800" t="inlineStr"/>
-    </row>
-    <row r="801">
-      <c r="A801" t="inlineStr"/>
-      <c r="B801" t="n">
-        <v>800</v>
-      </c>
-      <c r="C801" t="inlineStr"/>
-      <c r="D801" t="inlineStr"/>
-      <c r="E801" t="inlineStr"/>
-    </row>
-    <row r="802">
-      <c r="A802" t="inlineStr"/>
-      <c r="B802" t="n">
-        <v>801</v>
-      </c>
-      <c r="C802" t="inlineStr"/>
-      <c r="D802" t="inlineStr"/>
-      <c r="E802" t="inlineStr"/>
-    </row>
-    <row r="803">
-      <c r="A803" t="inlineStr"/>
-      <c r="B803" t="n">
-        <v>802</v>
-      </c>
-      <c r="C803" t="inlineStr"/>
-      <c r="D803" t="inlineStr"/>
-      <c r="E803" t="inlineStr"/>
-    </row>
-    <row r="804">
-      <c r="A804" t="inlineStr"/>
-      <c r="B804" t="n">
-        <v>803</v>
-      </c>
-      <c r="C804" t="inlineStr"/>
-      <c r="D804" t="inlineStr"/>
-      <c r="E804" t="inlineStr"/>
-    </row>
-    <row r="805">
-      <c r="A805" t="inlineStr"/>
-      <c r="B805" t="n">
-        <v>804</v>
-      </c>
-      <c r="C805" t="inlineStr"/>
-      <c r="D805" t="inlineStr"/>
-      <c r="E805" t="inlineStr"/>
-    </row>
-    <row r="806">
-      <c r="A806" t="inlineStr"/>
-      <c r="B806" t="n">
-        <v>805</v>
-      </c>
-      <c r="C806" t="inlineStr"/>
-      <c r="D806" t="inlineStr"/>
-      <c r="E806" t="inlineStr"/>
-    </row>
-    <row r="807">
-      <c r="A807" t="inlineStr"/>
-      <c r="B807" t="n">
-        <v>806</v>
-      </c>
-      <c r="C807" t="inlineStr"/>
-      <c r="D807" t="inlineStr"/>
-      <c r="E807" t="inlineStr"/>
-    </row>
-    <row r="808">
-      <c r="A808" t="inlineStr"/>
-      <c r="B808" t="n">
-        <v>807</v>
-      </c>
-      <c r="C808" t="inlineStr"/>
-      <c r="D808" t="inlineStr"/>
-      <c r="E808" t="inlineStr"/>
-    </row>
-    <row r="809">
-      <c r="A809" t="inlineStr"/>
-      <c r="B809" t="n">
-        <v>808</v>
-      </c>
-      <c r="C809" t="inlineStr"/>
-      <c r="D809" t="inlineStr"/>
-      <c r="E809" t="inlineStr"/>
-    </row>
-    <row r="810">
-      <c r="A810" t="inlineStr"/>
-      <c r="B810" t="n">
-        <v>809</v>
-      </c>
-      <c r="C810" t="inlineStr"/>
-      <c r="D810" t="inlineStr"/>
-      <c r="E810" t="inlineStr"/>
-    </row>
-    <row r="811">
-      <c r="A811" t="inlineStr"/>
-      <c r="B811" t="n">
-        <v>810</v>
-      </c>
-      <c r="C811" t="inlineStr"/>
-      <c r="D811" t="inlineStr"/>
-      <c r="E811" t="inlineStr"/>
-    </row>
-    <row r="812">
-      <c r="A812" t="inlineStr"/>
-      <c r="B812" t="n">
-        <v>811</v>
-      </c>
-      <c r="C812" t="inlineStr"/>
-      <c r="D812" t="inlineStr"/>
-      <c r="E812" t="inlineStr"/>
-    </row>
-    <row r="813">
-      <c r="A813" t="inlineStr"/>
-      <c r="B813" t="n">
-        <v>812</v>
-      </c>
-      <c r="C813" t="inlineStr"/>
-      <c r="D813" t="inlineStr"/>
-      <c r="E813" t="inlineStr"/>
-    </row>
-    <row r="814">
-      <c r="A814" t="inlineStr"/>
-      <c r="B814" t="n">
-        <v>813</v>
-      </c>
-      <c r="C814" t="inlineStr"/>
-      <c r="D814" t="inlineStr"/>
-      <c r="E814" t="inlineStr"/>
-    </row>
-    <row r="815">
-      <c r="A815" t="inlineStr"/>
-      <c r="B815" t="n">
-        <v>814</v>
-      </c>
-      <c r="C815" t="inlineStr"/>
-      <c r="D815" t="inlineStr"/>
-      <c r="E815" t="inlineStr"/>
-    </row>
-    <row r="816">
-      <c r="A816" t="inlineStr"/>
-      <c r="B816" t="n">
-        <v>815</v>
-      </c>
-      <c r="C816" t="inlineStr"/>
-      <c r="D816" t="inlineStr"/>
-      <c r="E816" t="inlineStr"/>
-    </row>
-    <row r="817">
-      <c r="A817" t="inlineStr"/>
-      <c r="B817" t="n">
-        <v>816</v>
-      </c>
-      <c r="C817" t="inlineStr"/>
-      <c r="D817" t="inlineStr"/>
-      <c r="E817" t="inlineStr"/>
-    </row>
-    <row r="818">
-      <c r="A818" t="inlineStr"/>
-      <c r="B818" t="n">
-        <v>817</v>
-      </c>
-      <c r="C818" t="inlineStr"/>
-      <c r="D818" t="inlineStr"/>
-      <c r="E818" t="inlineStr"/>
-    </row>
-    <row r="819">
-      <c r="A819" t="inlineStr"/>
-      <c r="B819" t="n">
-        <v>818</v>
-      </c>
-      <c r="C819" t="inlineStr"/>
-      <c r="D819" t="inlineStr"/>
-      <c r="E819" t="inlineStr"/>
-    </row>
-    <row r="820">
-      <c r="A820" t="inlineStr"/>
-      <c r="B820" t="n">
-        <v>819</v>
-      </c>
-      <c r="C820" t="inlineStr"/>
-      <c r="D820" t="inlineStr"/>
-      <c r="E820" t="inlineStr"/>
-    </row>
-    <row r="821">
-      <c r="A821" t="inlineStr"/>
-      <c r="B821" t="n">
-        <v>820</v>
-      </c>
-      <c r="C821" t="inlineStr"/>
-      <c r="D821" t="inlineStr"/>
-      <c r="E821" t="inlineStr"/>
-    </row>
-    <row r="822">
-      <c r="A822" t="inlineStr"/>
-      <c r="B822" t="n">
-        <v>821</v>
-      </c>
-      <c r="C822" t="inlineStr"/>
-      <c r="D822" t="inlineStr"/>
-      <c r="E822" t="inlineStr"/>
-    </row>
-    <row r="823">
-      <c r="A823" t="inlineStr"/>
-      <c r="B823" t="n">
-        <v>822</v>
-      </c>
-      <c r="C823" t="inlineStr"/>
-      <c r="D823" t="inlineStr"/>
-      <c r="E823" t="inlineStr"/>
-    </row>
-    <row r="824">
-      <c r="A824" t="inlineStr"/>
-      <c r="B824" t="n">
-        <v>823</v>
-      </c>
-      <c r="C824" t="inlineStr"/>
-      <c r="D824" t="inlineStr"/>
-      <c r="E824" t="inlineStr"/>
-    </row>
-    <row r="825">
-      <c r="A825" t="inlineStr"/>
-      <c r="B825" t="n">
-        <v>824</v>
-      </c>
-      <c r="C825" t="inlineStr"/>
-      <c r="D825" t="inlineStr"/>
-      <c r="E825" t="inlineStr"/>
-    </row>
-    <row r="826">
-      <c r="A826" t="inlineStr"/>
-      <c r="B826" t="n">
-        <v>825</v>
-      </c>
-      <c r="C826" t="inlineStr"/>
-      <c r="D826" t="inlineStr"/>
-      <c r="E826" t="inlineStr"/>
-    </row>
-    <row r="827">
-      <c r="A827" t="inlineStr"/>
-      <c r="B827" t="n">
-        <v>826</v>
-      </c>
-      <c r="C827" t="inlineStr"/>
-      <c r="D827" t="inlineStr"/>
-      <c r="E827" t="inlineStr"/>
-    </row>
-    <row r="828">
-      <c r="A828" t="inlineStr"/>
-      <c r="B828" t="n">
-        <v>827</v>
-      </c>
-      <c r="C828" t="inlineStr"/>
-      <c r="D828" t="inlineStr"/>
-      <c r="E828" t="inlineStr"/>
-    </row>
-    <row r="829">
-      <c r="A829" t="inlineStr"/>
-      <c r="B829" t="n">
-        <v>828</v>
-      </c>
-      <c r="C829" t="inlineStr"/>
-      <c r="D829" t="inlineStr"/>
-      <c r="E829" t="inlineStr"/>
-    </row>
-    <row r="830">
-      <c r="A830" t="inlineStr"/>
-      <c r="B830" t="n">
-        <v>829</v>
-      </c>
-      <c r="C830" t="inlineStr"/>
-      <c r="D830" t="inlineStr"/>
-      <c r="E830" t="inlineStr"/>
-    </row>
-    <row r="831">
-      <c r="A831" t="inlineStr"/>
-      <c r="B831" t="n">
-        <v>830</v>
-      </c>
-      <c r="C831" t="inlineStr"/>
-      <c r="D831" t="inlineStr"/>
-      <c r="E831" t="inlineStr"/>
-    </row>
-    <row r="832">
-      <c r="A832" t="inlineStr"/>
-      <c r="B832" t="n">
-        <v>831</v>
-      </c>
-      <c r="C832" t="inlineStr"/>
-      <c r="D832" t="inlineStr"/>
-      <c r="E832" t="inlineStr"/>
-    </row>
-    <row r="833">
-      <c r="A833" t="inlineStr"/>
-      <c r="B833" t="n">
-        <v>832</v>
-      </c>
-      <c r="C833" t="inlineStr"/>
-      <c r="D833" t="inlineStr"/>
-      <c r="E833" t="inlineStr"/>
-    </row>
-    <row r="834">
-      <c r="A834" t="inlineStr"/>
-      <c r="B834" t="n">
-        <v>833</v>
-      </c>
-      <c r="C834" t="inlineStr"/>
-      <c r="D834" t="inlineStr"/>
-      <c r="E834" t="inlineStr"/>
-    </row>
-    <row r="835">
-      <c r="A835" t="inlineStr"/>
-      <c r="B835" t="n">
-        <v>834</v>
-      </c>
-      <c r="C835" t="inlineStr"/>
-      <c r="D835" t="inlineStr"/>
-      <c r="E835" t="inlineStr"/>
-    </row>
-    <row r="836">
-      <c r="A836" t="inlineStr"/>
-      <c r="B836" t="n">
-        <v>835</v>
-      </c>
-      <c r="C836" t="inlineStr"/>
-      <c r="D836" t="inlineStr"/>
-      <c r="E836" t="inlineStr"/>
-    </row>
-    <row r="837">
-      <c r="A837" t="inlineStr"/>
-      <c r="B837" t="n">
-        <v>836</v>
-      </c>
-      <c r="C837" t="inlineStr"/>
-      <c r="D837" t="inlineStr"/>
-      <c r="E837" t="inlineStr"/>
-    </row>
-    <row r="838">
-      <c r="A838" t="inlineStr"/>
-      <c r="B838" t="n">
-        <v>837</v>
-      </c>
-      <c r="C838" t="inlineStr"/>
-      <c r="D838" t="inlineStr"/>
-      <c r="E838" t="inlineStr"/>
-    </row>
-    <row r="839">
-      <c r="A839" t="inlineStr"/>
-      <c r="B839" t="n">
-        <v>838</v>
-      </c>
-      <c r="C839" t="inlineStr"/>
-      <c r="D839" t="inlineStr"/>
-      <c r="E839" t="inlineStr"/>
-    </row>
-    <row r="840">
-      <c r="A840" t="inlineStr"/>
-      <c r="B840" t="n">
-        <v>839</v>
-      </c>
-      <c r="C840" t="inlineStr"/>
-      <c r="D840" t="inlineStr"/>
-      <c r="E840" t="inlineStr"/>
-    </row>
-    <row r="841">
-      <c r="A841" t="inlineStr"/>
-      <c r="B841" t="n">
-        <v>840</v>
-      </c>
-      <c r="C841" t="inlineStr"/>
-      <c r="D841" t="inlineStr"/>
-      <c r="E841" t="inlineStr"/>
-    </row>
-    <row r="842">
-      <c r="A842" t="inlineStr"/>
-      <c r="B842" t="n">
-        <v>841</v>
-      </c>
-      <c r="C842" t="inlineStr"/>
-      <c r="D842" t="inlineStr"/>
-      <c r="E842" t="inlineStr"/>
-    </row>
-    <row r="843">
-      <c r="A843" t="inlineStr"/>
-      <c r="B843" t="n">
-        <v>842</v>
-      </c>
-      <c r="C843" t="inlineStr"/>
-      <c r="D843" t="inlineStr"/>
-      <c r="E843" t="inlineStr"/>
-    </row>
-    <row r="844">
-      <c r="A844" t="inlineStr"/>
-      <c r="B844" t="n">
-        <v>843</v>
-      </c>
-      <c r="C844" t="inlineStr"/>
-      <c r="D844" t="inlineStr"/>
-      <c r="E844" t="inlineStr"/>
-    </row>
-    <row r="845">
-      <c r="A845" t="inlineStr"/>
-      <c r="B845" t="n">
-        <v>844</v>
-      </c>
-      <c r="C845" t="inlineStr"/>
-      <c r="D845" t="inlineStr"/>
-      <c r="E845" t="inlineStr"/>
-    </row>
-    <row r="846">
-      <c r="A846" t="inlineStr"/>
-      <c r="B846" t="n">
-        <v>845</v>
-      </c>
-      <c r="C846" t="inlineStr"/>
-      <c r="D846" t="inlineStr"/>
-      <c r="E846" t="inlineStr"/>
-    </row>
-    <row r="847">
-      <c r="A847" t="inlineStr"/>
-      <c r="B847" t="n">
-        <v>846</v>
-      </c>
-      <c r="C847" t="inlineStr"/>
-      <c r="D847" t="inlineStr"/>
-      <c r="E847" t="inlineStr"/>
-    </row>
-    <row r="848">
-      <c r="A848" t="inlineStr"/>
-      <c r="B848" t="n">
-        <v>847</v>
-      </c>
-      <c r="C848" t="inlineStr"/>
-      <c r="D848" t="inlineStr"/>
-      <c r="E848" t="inlineStr"/>
-    </row>
-    <row r="849">
-      <c r="A849" t="inlineStr"/>
-      <c r="B849" t="n">
-        <v>848</v>
-      </c>
-      <c r="C849" t="inlineStr"/>
-      <c r="D849" t="inlineStr"/>
-      <c r="E849" t="inlineStr"/>
-    </row>
-    <row r="850">
-      <c r="A850" t="inlineStr"/>
-      <c r="B850" t="n">
-        <v>849</v>
-      </c>
-      <c r="C850" t="inlineStr"/>
-      <c r="D850" t="inlineStr"/>
-      <c r="E850" t="inlineStr"/>
-    </row>
-    <row r="851">
-      <c r="A851" t="inlineStr"/>
-      <c r="B851" t="n">
-        <v>850</v>
-      </c>
-      <c r="C851" t="inlineStr"/>
-      <c r="D851" t="inlineStr"/>
-      <c r="E851" t="inlineStr"/>
-    </row>
-    <row r="852">
-      <c r="A852" t="inlineStr"/>
-      <c r="B852" t="n">
-        <v>851</v>
-      </c>
-      <c r="C852" t="inlineStr"/>
-      <c r="D852" t="inlineStr"/>
-      <c r="E852" t="inlineStr"/>
-    </row>
-    <row r="853">
-      <c r="A853" t="inlineStr"/>
-      <c r="B853" t="n">
-        <v>852</v>
-      </c>
-      <c r="C853" t="inlineStr"/>
-      <c r="D853" t="inlineStr"/>
-      <c r="E853" t="inlineStr"/>
-    </row>
-    <row r="854">
-      <c r="A854" t="inlineStr"/>
-      <c r="B854" t="n">
-        <v>853</v>
-      </c>
-      <c r="C854" t="inlineStr"/>
-      <c r="D854" t="inlineStr"/>
-      <c r="E854" t="inlineStr"/>
-    </row>
-    <row r="855">
-      <c r="A855" t="inlineStr"/>
-      <c r="B855" t="n">
-        <v>854</v>
-      </c>
-      <c r="C855" t="inlineStr"/>
-      <c r="D855" t="inlineStr"/>
-      <c r="E855" t="inlineStr"/>
-    </row>
-    <row r="856">
-      <c r="A856" t="inlineStr"/>
-      <c r="B856" t="n">
-        <v>855</v>
-      </c>
-      <c r="C856" t="inlineStr"/>
-      <c r="D856" t="inlineStr"/>
-      <c r="E856" t="inlineStr"/>
-    </row>
-    <row r="857">
-      <c r="A857" t="inlineStr"/>
-      <c r="B857" t="n">
-        <v>856</v>
-      </c>
-      <c r="C857" t="inlineStr"/>
-      <c r="D857" t="inlineStr"/>
-      <c r="E857" t="inlineStr"/>
-    </row>
-    <row r="858">
-      <c r="A858" t="inlineStr"/>
-      <c r="B858" t="n">
-        <v>857</v>
-      </c>
-      <c r="C858" t="inlineStr"/>
-      <c r="D858" t="inlineStr"/>
-      <c r="E858" t="inlineStr"/>
-    </row>
-    <row r="859">
-      <c r="A859" t="inlineStr"/>
-      <c r="B859" t="n">
-        <v>858</v>
-      </c>
-      <c r="C859" t="inlineStr"/>
-      <c r="D859" t="inlineStr"/>
-      <c r="E859" t="inlineStr"/>
-    </row>
-    <row r="860">
-      <c r="A860" t="inlineStr"/>
-      <c r="B860" t="n">
-        <v>859</v>
-      </c>
-      <c r="C860" t="inlineStr"/>
-      <c r="D860" t="inlineStr"/>
-      <c r="E860" t="inlineStr"/>
-    </row>
-    <row r="861">
-      <c r="A861" t="inlineStr"/>
-      <c r="B861" t="n">
-        <v>860</v>
-      </c>
-      <c r="C861" t="inlineStr"/>
-      <c r="D861" t="inlineStr"/>
-      <c r="E861" t="inlineStr"/>
-    </row>
-    <row r="862">
-      <c r="A862" t="inlineStr"/>
-      <c r="B862" t="n">
-        <v>861</v>
-      </c>
-      <c r="C862" t="inlineStr"/>
-      <c r="D862" t="inlineStr"/>
-      <c r="E862" t="inlineStr"/>
-    </row>
-    <row r="863">
-      <c r="A863" t="inlineStr"/>
-      <c r="B863" t="n">
-        <v>862</v>
-      </c>
-      <c r="C863" t="inlineStr"/>
-      <c r="D863" t="inlineStr"/>
-      <c r="E863" t="inlineStr"/>
-    </row>
-    <row r="864">
-      <c r="A864" t="inlineStr"/>
-      <c r="B864" t="n">
-        <v>863</v>
-      </c>
-      <c r="C864" t="inlineStr"/>
-      <c r="D864" t="inlineStr"/>
-      <c r="E864" t="inlineStr"/>
-    </row>
-    <row r="865">
-      <c r="A865" t="inlineStr"/>
-      <c r="B865" t="n">
-        <v>864</v>
-      </c>
-      <c r="C865" t="inlineStr"/>
-      <c r="D865" t="inlineStr"/>
-      <c r="E865" t="inlineStr"/>
-    </row>
-    <row r="866">
-      <c r="A866" t="inlineStr"/>
-      <c r="B866" t="n">
-        <v>865</v>
-      </c>
-      <c r="C866" t="inlineStr"/>
-      <c r="D866" t="inlineStr"/>
-      <c r="E866" t="inlineStr"/>
-    </row>
-    <row r="867">
-      <c r="A867" t="inlineStr"/>
-      <c r="B867" t="n">
-        <v>866</v>
-      </c>
-      <c r="C867" t="inlineStr"/>
-      <c r="D867" t="inlineStr"/>
-      <c r="E867" t="inlineStr"/>
-    </row>
-    <row r="868">
-      <c r="A868" t="inlineStr"/>
-      <c r="B868" t="n">
-        <v>867</v>
-      </c>
-      <c r="C868" t="inlineStr"/>
-      <c r="D868" t="inlineStr"/>
-      <c r="E868" t="inlineStr"/>
-    </row>
-    <row r="869">
-      <c r="A869" t="inlineStr"/>
-      <c r="B869" t="n">
-        <v>868</v>
-      </c>
-      <c r="C869" t="inlineStr"/>
-      <c r="D869" t="inlineStr"/>
-      <c r="E869" t="inlineStr"/>
-    </row>
-    <row r="870">
-      <c r="A870" t="inlineStr"/>
-      <c r="B870" t="n">
-        <v>869</v>
-      </c>
-      <c r="C870" t="inlineStr"/>
-      <c r="D870" t="inlineStr"/>
-      <c r="E870" t="inlineStr"/>
-    </row>
-    <row r="871">
-      <c r="A871" t="inlineStr"/>
-      <c r="B871" t="n">
-        <v>870</v>
-      </c>
-      <c r="C871" t="inlineStr"/>
-      <c r="D871" t="inlineStr"/>
-      <c r="E871" t="inlineStr"/>
-    </row>
-    <row r="872">
-      <c r="A872" t="inlineStr"/>
-      <c r="B872" t="n">
-        <v>871</v>
-      </c>
-      <c r="C872" t="inlineStr"/>
-      <c r="D872" t="inlineStr"/>
-      <c r="E872" t="inlineStr"/>
-    </row>
-    <row r="873">
-      <c r="A873" t="inlineStr"/>
-      <c r="B873" t="n">
-        <v>872</v>
-      </c>
-      <c r="C873" t="inlineStr"/>
-      <c r="D873" t="inlineStr"/>
-      <c r="E873" t="inlineStr"/>
-    </row>
-    <row r="874">
-      <c r="A874" t="inlineStr"/>
-      <c r="B874" t="n">
-        <v>873</v>
-      </c>
-      <c r="C874" t="inlineStr"/>
-      <c r="D874" t="inlineStr"/>
-      <c r="E874" t="inlineStr"/>
-    </row>
-    <row r="875">
-      <c r="A875" t="inlineStr"/>
-      <c r="B875" t="n">
-        <v>874</v>
-      </c>
-      <c r="C875" t="inlineStr"/>
-      <c r="D875" t="inlineStr"/>
-      <c r="E875" t="inlineStr"/>
-    </row>
-    <row r="876">
-      <c r="A876" t="inlineStr"/>
-      <c r="B876" t="n">
-        <v>875</v>
-      </c>
-      <c r="C876" t="inlineStr"/>
-      <c r="D876" t="inlineStr"/>
-      <c r="E876" t="inlineStr"/>
-    </row>
-    <row r="877">
-      <c r="A877" t="inlineStr"/>
-      <c r="B877" t="n">
-        <v>876</v>
-      </c>
-      <c r="C877" t="inlineStr"/>
-      <c r="D877" t="inlineStr"/>
-      <c r="E877" t="inlineStr"/>
-    </row>
-    <row r="878">
-      <c r="A878" t="inlineStr"/>
-      <c r="B878" t="n">
-        <v>877</v>
-      </c>
-      <c r="C878" t="inlineStr"/>
-      <c r="D878" t="inlineStr"/>
-      <c r="E878" t="inlineStr"/>
-    </row>
-    <row r="879">
-      <c r="A879" t="inlineStr"/>
-      <c r="B879" t="n">
-        <v>878</v>
-      </c>
-      <c r="C879" t="inlineStr"/>
-      <c r="D879" t="inlineStr"/>
-      <c r="E879" t="inlineStr"/>
-    </row>
-    <row r="880">
-      <c r="A880" t="inlineStr"/>
-      <c r="B880" t="n">
-        <v>879</v>
-      </c>
-      <c r="C880" t="inlineStr"/>
-      <c r="D880" t="inlineStr"/>
-      <c r="E880" t="inlineStr"/>
-    </row>
-    <row r="881">
-      <c r="A881" t="inlineStr"/>
-      <c r="B881" t="n">
-        <v>880</v>
-      </c>
-      <c r="C881" t="inlineStr"/>
-      <c r="D881" t="inlineStr"/>
-      <c r="E881" t="inlineStr"/>
-    </row>
-    <row r="882">
-      <c r="A882" t="inlineStr"/>
-      <c r="B882" t="n">
-        <v>881</v>
-      </c>
-      <c r="C882" t="inlineStr"/>
-      <c r="D882" t="inlineStr"/>
-      <c r="E882" t="inlineStr"/>
-    </row>
-    <row r="883">
-      <c r="A883" t="inlineStr"/>
-      <c r="B883" t="n">
-        <v>882</v>
-      </c>
-      <c r="C883" t="inlineStr"/>
-      <c r="D883" t="inlineStr"/>
-      <c r="E883" t="inlineStr"/>
-    </row>
-    <row r="884">
-      <c r="A884" t="inlineStr"/>
-      <c r="B884" t="n">
-        <v>883</v>
-      </c>
-      <c r="C884" t="inlineStr"/>
-      <c r="D884" t="inlineStr"/>
-      <c r="E884" t="inlineStr"/>
-    </row>
-    <row r="885">
-      <c r="A885" t="inlineStr"/>
-      <c r="B885" t="n">
-        <v>884</v>
-      </c>
-      <c r="C885" t="inlineStr"/>
-      <c r="D885" t="inlineStr"/>
-      <c r="E885" t="inlineStr"/>
-    </row>
-    <row r="886">
-      <c r="A886" t="inlineStr"/>
-      <c r="B886" t="n">
-        <v>885</v>
-      </c>
-      <c r="C886" t="inlineStr"/>
-      <c r="D886" t="inlineStr"/>
-      <c r="E886" t="inlineStr"/>
-    </row>
-    <row r="887">
-      <c r="A887" t="inlineStr"/>
-      <c r="B887" t="n">
-        <v>886</v>
-      </c>
-      <c r="C887" t="inlineStr"/>
-      <c r="D887" t="inlineStr"/>
-      <c r="E887" t="inlineStr"/>
-    </row>
-    <row r="888">
-      <c r="A888" t="inlineStr"/>
-      <c r="B888" t="n">
-        <v>887</v>
-      </c>
-      <c r="C888" t="inlineStr"/>
-      <c r="D888" t="inlineStr"/>
-      <c r="E888" t="inlineStr"/>
-    </row>
-    <row r="889">
-      <c r="A889" t="inlineStr"/>
-      <c r="B889" t="n">
-        <v>888</v>
-      </c>
-      <c r="C889" t="inlineStr"/>
-      <c r="D889" t="inlineStr"/>
-      <c r="E889" t="inlineStr"/>
-    </row>
-    <row r="890">
-      <c r="A890" t="inlineStr"/>
-      <c r="B890" t="n">
-        <v>889</v>
-      </c>
-      <c r="C890" t="inlineStr"/>
-      <c r="D890" t="inlineStr"/>
-      <c r="E890" t="inlineStr"/>
-    </row>
-    <row r="891">
-      <c r="A891" t="inlineStr"/>
-      <c r="B891" t="n">
-        <v>890</v>
-      </c>
-      <c r="C891" t="inlineStr"/>
-      <c r="D891" t="inlineStr"/>
-      <c r="E891" t="inlineStr"/>
-    </row>
-    <row r="892">
-      <c r="A892" t="inlineStr"/>
-      <c r="B892" t="n">
-        <v>891</v>
-      </c>
-      <c r="C892" t="inlineStr"/>
-      <c r="D892" t="inlineStr"/>
-      <c r="E892" t="inlineStr"/>
-    </row>
-    <row r="893">
-      <c r="A893" t="inlineStr"/>
-      <c r="B893" t="n">
-        <v>892</v>
-      </c>
-      <c r="C893" t="inlineStr"/>
-      <c r="D893" t="inlineStr"/>
-      <c r="E893" t="inlineStr"/>
-    </row>
-    <row r="894">
-      <c r="A894" t="inlineStr"/>
-      <c r="B894" t="n">
-        <v>893</v>
-      </c>
-      <c r="C894" t="inlineStr"/>
-      <c r="D894" t="inlineStr"/>
-      <c r="E894" t="inlineStr"/>
-    </row>
-    <row r="895">
-      <c r="A895" t="inlineStr"/>
-      <c r="B895" t="n">
-        <v>894</v>
-      </c>
-      <c r="C895" t="inlineStr"/>
-      <c r="D895" t="inlineStr"/>
-      <c r="E895" t="inlineStr"/>
-    </row>
-    <row r="896">
-      <c r="A896" t="inlineStr"/>
-      <c r="B896" t="n">
-        <v>895</v>
-      </c>
-      <c r="C896" t="inlineStr"/>
-      <c r="D896" t="inlineStr"/>
-      <c r="E896" t="inlineStr"/>
-    </row>
-    <row r="897">
-      <c r="A897" t="inlineStr"/>
-      <c r="B897" t="n">
-        <v>896</v>
-      </c>
-      <c r="C897" t="inlineStr"/>
-      <c r="D897" t="inlineStr"/>
-      <c r="E897" t="inlineStr"/>
-    </row>
-    <row r="898">
-      <c r="A898" t="inlineStr"/>
-      <c r="B898" t="n">
-        <v>897</v>
-      </c>
-      <c r="C898" t="inlineStr"/>
-      <c r="D898" t="inlineStr"/>
-      <c r="E898" t="inlineStr"/>
-    </row>
-    <row r="899">
-      <c r="A899" t="inlineStr"/>
-      <c r="B899" t="n">
-        <v>898</v>
-      </c>
-      <c r="C899" t="inlineStr"/>
-      <c r="D899" t="inlineStr"/>
-      <c r="E899" t="inlineStr"/>
-    </row>
-    <row r="900">
-      <c r="A900" t="inlineStr"/>
-      <c r="B900" t="n">
-        <v>899</v>
-      </c>
-      <c r="C900" t="inlineStr"/>
-      <c r="D900" t="inlineStr"/>
-      <c r="E900" t="inlineStr"/>
-    </row>
-    <row r="901">
-      <c r="A901" t="inlineStr"/>
-      <c r="B901" t="n">
-        <v>900</v>
-      </c>
-      <c r="C901" t="inlineStr"/>
-      <c r="D901" t="inlineStr"/>
-      <c r="E901" t="inlineStr"/>
-    </row>
-    <row r="902">
-      <c r="A902" t="inlineStr"/>
-      <c r="B902" t="n">
-        <v>901</v>
-      </c>
-      <c r="C902" t="inlineStr"/>
-      <c r="D902" t="inlineStr"/>
-      <c r="E902" t="inlineStr"/>
-    </row>
-    <row r="903">
-      <c r="A903" t="inlineStr"/>
-      <c r="B903" t="n">
-        <v>902</v>
-      </c>
-      <c r="C903" t="inlineStr"/>
-      <c r="D903" t="inlineStr"/>
-      <c r="E903" t="inlineStr"/>
-    </row>
-    <row r="904">
-      <c r="A904" t="inlineStr"/>
-      <c r="B904" t="n">
-        <v>903</v>
-      </c>
-      <c r="C904" t="inlineStr"/>
-      <c r="D904" t="inlineStr"/>
-      <c r="E904" t="inlineStr"/>
-    </row>
-    <row r="905">
-      <c r="A905" t="inlineStr"/>
-      <c r="B905" t="n">
-        <v>904</v>
-      </c>
-      <c r="C905" t="inlineStr"/>
-      <c r="D905" t="inlineStr"/>
-      <c r="E905" t="inlineStr"/>
-    </row>
-    <row r="906">
-      <c r="A906" t="inlineStr"/>
-      <c r="B906" t="n">
-        <v>905</v>
-      </c>
-      <c r="C906" t="inlineStr"/>
-      <c r="D906" t="inlineStr"/>
-      <c r="E906" t="inlineStr"/>
-    </row>
-    <row r="907">
-      <c r="A907" t="inlineStr"/>
-      <c r="B907" t="n">
-        <v>906</v>
-      </c>
-      <c r="C907" t="inlineStr"/>
-      <c r="D907" t="inlineStr"/>
-      <c r="E907" t="inlineStr"/>
-    </row>
-    <row r="908">
-      <c r="A908" t="inlineStr"/>
-      <c r="B908" t="n">
-        <v>907</v>
-      </c>
-      <c r="C908" t="inlineStr"/>
-      <c r="D908" t="inlineStr"/>
-      <c r="E908" t="inlineStr"/>
-    </row>
-    <row r="909">
-      <c r="A909" t="inlineStr"/>
-      <c r="B909" t="n">
-        <v>908</v>
-      </c>
-      <c r="C909" t="inlineStr"/>
-      <c r="D909" t="inlineStr"/>
-      <c r="E909" t="inlineStr"/>
-    </row>
-    <row r="910">
-      <c r="A910" t="inlineStr"/>
-      <c r="B910" t="n">
-        <v>909</v>
-      </c>
-      <c r="C910" t="inlineStr"/>
-      <c r="D910" t="inlineStr"/>
-      <c r="E910" t="inlineStr"/>
-    </row>
-    <row r="911">
-      <c r="A911" t="inlineStr"/>
-      <c r="B911" t="n">
-        <v>910</v>
-      </c>
-      <c r="C911" t="inlineStr"/>
-      <c r="D911" t="inlineStr"/>
-      <c r="E911" t="inlineStr"/>
-    </row>
-    <row r="912">
-      <c r="A912" t="inlineStr"/>
-      <c r="B912" t="n">
-        <v>911</v>
-      </c>
-      <c r="C912" t="inlineStr"/>
-      <c r="D912" t="inlineStr"/>
-      <c r="E912" t="inlineStr"/>
-    </row>
-    <row r="913">
-      <c r="A913" t="inlineStr"/>
-      <c r="B913" t="n">
-        <v>912</v>
-      </c>
-      <c r="C913" t="inlineStr"/>
-      <c r="D913" t="inlineStr"/>
-      <c r="E913" t="inlineStr"/>
-    </row>
-    <row r="914">
-      <c r="A914" t="inlineStr"/>
-      <c r="B914" t="n">
-        <v>913</v>
-      </c>
-      <c r="C914" t="inlineStr"/>
-      <c r="D914" t="inlineStr"/>
-      <c r="E914" t="inlineStr"/>
-    </row>
-    <row r="915">
-      <c r="A915" t="inlineStr"/>
-      <c r="B915" t="n">
-        <v>914</v>
-      </c>
-      <c r="C915" t="inlineStr"/>
-      <c r="D915" t="inlineStr"/>
-      <c r="E915" t="inlineStr"/>
-    </row>
-    <row r="916">
-      <c r="A916" t="inlineStr"/>
-      <c r="B916" t="n">
-        <v>915</v>
-      </c>
-      <c r="C916" t="inlineStr"/>
-      <c r="D916" t="inlineStr"/>
-      <c r="E916" t="inlineStr"/>
-    </row>
-    <row r="917">
-      <c r="A917" t="inlineStr"/>
-      <c r="B917" t="n">
-        <v>916</v>
-      </c>
-      <c r="C917" t="inlineStr"/>
-      <c r="D917" t="inlineStr"/>
-      <c r="E917" t="inlineStr"/>
-    </row>
-    <row r="918">
-      <c r="A918" t="inlineStr"/>
-      <c r="B918" t="n">
-        <v>917</v>
-      </c>
-      <c r="C918" t="inlineStr"/>
-      <c r="D918" t="inlineStr"/>
-      <c r="E918" t="inlineStr"/>
-    </row>
-    <row r="919">
-      <c r="A919" t="inlineStr"/>
-      <c r="B919" t="n">
-        <v>918</v>
-      </c>
-      <c r="C919" t="inlineStr"/>
-      <c r="D919" t="inlineStr"/>
-      <c r="E919" t="inlineStr"/>
-    </row>
-    <row r="920">
-      <c r="A920" t="inlineStr"/>
-      <c r="B920" t="n">
-        <v>919</v>
-      </c>
-      <c r="C920" t="inlineStr"/>
-      <c r="D920" t="inlineStr"/>
-      <c r="E920" t="inlineStr"/>
-    </row>
-    <row r="921">
-      <c r="A921" t="inlineStr"/>
-      <c r="B921" t="n">
-        <v>920</v>
-      </c>
-      <c r="C921" t="inlineStr"/>
-      <c r="D921" t="inlineStr"/>
-      <c r="E921" t="inlineStr"/>
-    </row>
-    <row r="922">
-      <c r="A922" t="inlineStr"/>
-      <c r="B922" t="n">
-        <v>921</v>
-      </c>
-      <c r="C922" t="inlineStr"/>
-      <c r="D922" t="inlineStr"/>
-      <c r="E922" t="inlineStr"/>
-    </row>
-    <row r="923">
-      <c r="A923" t="inlineStr"/>
-      <c r="B923" t="n">
-        <v>922</v>
-      </c>
-      <c r="C923" t="inlineStr"/>
-      <c r="D923" t="inlineStr"/>
-      <c r="E923" t="inlineStr"/>
-    </row>
-    <row r="924">
-      <c r="A924" t="inlineStr"/>
-      <c r="B924" t="n">
-        <v>923</v>
-      </c>
-      <c r="C924" t="inlineStr"/>
-      <c r="D924" t="inlineStr"/>
-      <c r="E924" t="inlineStr"/>
-    </row>
-    <row r="925">
-      <c r="A925" t="inlineStr"/>
-      <c r="B925" t="n">
-        <v>924</v>
-      </c>
-      <c r="C925" t="inlineStr"/>
-      <c r="D925" t="inlineStr"/>
-      <c r="E925" t="inlineStr"/>
-    </row>
-    <row r="926">
-      <c r="A926" t="inlineStr"/>
-      <c r="B926" t="n">
-        <v>925</v>
-      </c>
-      <c r="C926" t="inlineStr"/>
-      <c r="D926" t="inlineStr"/>
-      <c r="E926" t="inlineStr"/>
-    </row>
-    <row r="927">
-      <c r="A927" t="inlineStr"/>
-      <c r="B927" t="n">
-        <v>926</v>
-      </c>
-      <c r="C927" t="inlineStr"/>
-      <c r="D927" t="inlineStr"/>
-      <c r="E927" t="inlineStr"/>
-    </row>
-    <row r="928">
-      <c r="A928" t="inlineStr"/>
-      <c r="B928" t="n">
-        <v>927</v>
-      </c>
-      <c r="C928" t="inlineStr"/>
-      <c r="D928" t="inlineStr"/>
-      <c r="E928" t="inlineStr"/>
-    </row>
-    <row r="929">
-      <c r="A929" t="inlineStr"/>
-      <c r="B929" t="n">
-        <v>928</v>
-      </c>
-      <c r="C929" t="inlineStr"/>
-      <c r="D929" t="inlineStr"/>
-      <c r="E929" t="inlineStr"/>
-    </row>
-    <row r="930">
-      <c r="A930" t="inlineStr"/>
-      <c r="B930" t="n">
-        <v>929</v>
-      </c>
-      <c r="C930" t="inlineStr"/>
-      <c r="D930" t="inlineStr"/>
-      <c r="E930" t="inlineStr"/>
-    </row>
-    <row r="931">
-      <c r="A931" t="inlineStr"/>
-      <c r="B931" t="n">
-        <v>930</v>
-      </c>
-      <c r="C931" t="inlineStr"/>
-      <c r="D931" t="inlineStr"/>
-      <c r="E931" t="inlineStr"/>
-    </row>
-    <row r="932">
-      <c r="A932" t="inlineStr"/>
-      <c r="B932" t="n">
-        <v>931</v>
-      </c>
-      <c r="C932" t="inlineStr"/>
-      <c r="D932" t="inlineStr"/>
-      <c r="E932" t="inlineStr"/>
-    </row>
-    <row r="933">
-      <c r="A933" t="inlineStr"/>
-      <c r="B933" t="n">
-        <v>932</v>
-      </c>
-      <c r="C933" t="inlineStr"/>
-      <c r="D933" t="inlineStr"/>
-      <c r="E933" t="inlineStr"/>
-    </row>
-    <row r="934">
-      <c r="A934" t="inlineStr"/>
-      <c r="B934" t="n">
-        <v>933</v>
-      </c>
-      <c r="C934" t="inlineStr"/>
-      <c r="D934" t="inlineStr"/>
-      <c r="E934" t="inlineStr"/>
-    </row>
-    <row r="935">
-      <c r="A935" t="inlineStr"/>
-      <c r="B935" t="n">
-        <v>934</v>
-      </c>
-      <c r="C935" t="inlineStr"/>
-      <c r="D935" t="inlineStr"/>
-      <c r="E935" t="inlineStr"/>
-    </row>
-    <row r="936">
-      <c r="A936" t="inlineStr"/>
-      <c r="B936" t="n">
-        <v>935</v>
-      </c>
-      <c r="C936" t="inlineStr"/>
-      <c r="D936" t="inlineStr"/>
-      <c r="E936" t="inlineStr"/>
-    </row>
-    <row r="937">
-      <c r="A937" t="inlineStr"/>
-      <c r="B937" t="n">
-        <v>936</v>
-      </c>
-      <c r="C937" t="inlineStr"/>
-      <c r="D937" t="inlineStr"/>
-      <c r="E937" t="inlineStr"/>
-    </row>
-    <row r="938">
-      <c r="A938" t="inlineStr"/>
-      <c r="B938" t="n">
-        <v>937</v>
-      </c>
-      <c r="C938" t="inlineStr"/>
-      <c r="D938" t="inlineStr"/>
-      <c r="E938" t="inlineStr"/>
-    </row>
-    <row r="939">
-      <c r="A939" t="inlineStr"/>
-      <c r="B939" t="n">
-        <v>938</v>
-      </c>
-      <c r="C939" t="inlineStr"/>
-      <c r="D939" t="inlineStr"/>
-      <c r="E939" t="inlineStr"/>
-    </row>
-    <row r="940">
-      <c r="A940" t="inlineStr"/>
-      <c r="B940" t="n">
-        <v>939</v>
-      </c>
-      <c r="C940" t="inlineStr"/>
-      <c r="D940" t="inlineStr"/>
-      <c r="E940" t="inlineStr"/>
-    </row>
-    <row r="941">
-      <c r="A941" t="inlineStr"/>
-      <c r="B941" t="n">
-        <v>940</v>
-      </c>
-      <c r="C941" t="inlineStr"/>
-      <c r="D941" t="inlineStr"/>
-      <c r="E941" t="inlineStr"/>
-    </row>
-    <row r="942">
-      <c r="A942" t="inlineStr"/>
-      <c r="B942" t="n">
-        <v>941</v>
-      </c>
-      <c r="C942" t="inlineStr"/>
-      <c r="D942" t="inlineStr"/>
-      <c r="E942" t="inlineStr"/>
-    </row>
-    <row r="943">
-      <c r="A943" t="inlineStr"/>
-      <c r="B943" t="n">
-        <v>942</v>
-      </c>
-      <c r="C943" t="inlineStr"/>
-      <c r="D943" t="inlineStr"/>
-      <c r="E943" t="inlineStr"/>
-    </row>
-    <row r="944">
-      <c r="A944" t="inlineStr"/>
-      <c r="B944" t="n">
-        <v>943</v>
-      </c>
-      <c r="C944" t="inlineStr"/>
-      <c r="D944" t="inlineStr"/>
-      <c r="E944" t="inlineStr"/>
-    </row>
-    <row r="945">
-      <c r="A945" t="inlineStr"/>
-      <c r="B945" t="n">
-        <v>944</v>
-      </c>
-      <c r="C945" t="inlineStr"/>
-      <c r="D945" t="inlineStr"/>
-      <c r="E945" t="inlineStr"/>
-    </row>
-    <row r="946">
-      <c r="A946" t="inlineStr"/>
-      <c r="B946" t="n">
-        <v>945</v>
-      </c>
-      <c r="C946" t="inlineStr"/>
-      <c r="D946" t="inlineStr"/>
-      <c r="E946" t="inlineStr"/>
-    </row>
-    <row r="947">
-      <c r="A947" t="inlineStr"/>
-      <c r="B947" t="n">
-        <v>946</v>
-      </c>
-      <c r="C947" t="inlineStr"/>
-      <c r="D947" t="inlineStr"/>
-      <c r="E947" t="inlineStr"/>
-    </row>
-    <row r="948">
-      <c r="A948" t="inlineStr"/>
-      <c r="B948" t="n">
-        <v>947</v>
-      </c>
-      <c r="C948" t="inlineStr"/>
-      <c r="D948" t="inlineStr"/>
-      <c r="E948" t="inlineStr"/>
-    </row>
-    <row r="949">
-      <c r="A949" t="inlineStr"/>
-      <c r="B949" t="n">
-        <v>948</v>
-      </c>
-      <c r="C949" t="inlineStr"/>
-      <c r="D949" t="inlineStr"/>
-      <c r="E949" t="inlineStr"/>
-    </row>
-    <row r="950">
-      <c r="A950" t="inlineStr"/>
-      <c r="B950" t="n">
-        <v>949</v>
-      </c>
-      <c r="C950" t="inlineStr"/>
-      <c r="D950" t="inlineStr"/>
-      <c r="E950" t="inlineStr"/>
-    </row>
-    <row r="951">
-      <c r="A951" t="inlineStr"/>
-      <c r="B951" t="n">
-        <v>950</v>
-      </c>
-      <c r="C951" t="inlineStr"/>
-      <c r="D951" t="inlineStr"/>
-      <c r="E951" t="inlineStr"/>
-    </row>
-    <row r="952">
-      <c r="A952" t="inlineStr"/>
-      <c r="B952" t="n">
-        <v>951</v>
-      </c>
-      <c r="C952" t="inlineStr"/>
-      <c r="D952" t="inlineStr"/>
-      <c r="E952" t="inlineStr"/>
-    </row>
-    <row r="953">
-      <c r="A953" t="inlineStr"/>
-      <c r="B953" t="n">
-        <v>952</v>
-      </c>
-      <c r="C953" t="inlineStr"/>
-      <c r="D953" t="inlineStr"/>
-      <c r="E953" t="inlineStr"/>
-    </row>
-    <row r="954">
-      <c r="A954" t="inlineStr"/>
-      <c r="B954" t="n">
-        <v>953</v>
-      </c>
-      <c r="C954" t="inlineStr"/>
-      <c r="D954" t="inlineStr"/>
-      <c r="E954" t="inlineStr"/>
-    </row>
-    <row r="955">
-      <c r="A955" t="inlineStr"/>
-      <c r="B955" t="n">
-        <v>954</v>
-      </c>
-      <c r="C955" t="inlineStr"/>
-      <c r="D955" t="inlineStr"/>
-      <c r="E955" t="inlineStr"/>
-    </row>
-    <row r="956">
-      <c r="A956" t="inlineStr"/>
-      <c r="B956" t="n">
-        <v>955</v>
-      </c>
-      <c r="C956" t="inlineStr"/>
-      <c r="D956" t="inlineStr"/>
-      <c r="E956" t="inlineStr"/>
-    </row>
-    <row r="957">
-      <c r="A957" t="inlineStr"/>
-      <c r="B957" t="n">
-        <v>956</v>
-      </c>
-      <c r="C957" t="inlineStr"/>
-      <c r="D957" t="inlineStr"/>
-      <c r="E957" t="inlineStr"/>
-    </row>
-    <row r="958">
-      <c r="A958" t="inlineStr"/>
-      <c r="B958" t="n">
-        <v>957</v>
-      </c>
-      <c r="C958" t="inlineStr"/>
-      <c r="D958" t="inlineStr"/>
-      <c r="E958" t="inlineStr"/>
-    </row>
-    <row r="959">
-      <c r="A959" t="inlineStr"/>
-      <c r="B959" t="n">
-        <v>958</v>
-      </c>
-      <c r="C959" t="inlineStr"/>
-      <c r="D959" t="inlineStr"/>
-      <c r="E959" t="inlineStr"/>
-    </row>
-    <row r="960">
-      <c r="A960" t="inlineStr"/>
-      <c r="B960" t="n">
-        <v>959</v>
-      </c>
-      <c r="C960" t="inlineStr"/>
-      <c r="D960" t="inlineStr"/>
-      <c r="E960" t="inlineStr"/>
-    </row>
-    <row r="961">
-      <c r="A961" t="inlineStr"/>
-      <c r="B961" t="n">
-        <v>960</v>
-      </c>
-      <c r="C961" t="inlineStr"/>
-      <c r="D961" t="inlineStr"/>
-      <c r="E961" t="inlineStr"/>
-    </row>
-    <row r="962">
-      <c r="A962" t="inlineStr"/>
-      <c r="B962" t="n">
-        <v>961</v>
-      </c>
-      <c r="C962" t="inlineStr"/>
-      <c r="D962" t="inlineStr"/>
-      <c r="E962" t="inlineStr"/>
-    </row>
-    <row r="963">
-      <c r="A963" t="inlineStr"/>
-      <c r="B963" t="n">
-        <v>962</v>
-      </c>
-      <c r="C963" t="inlineStr"/>
-      <c r="D963" t="inlineStr"/>
-      <c r="E963" t="inlineStr"/>
-    </row>
-    <row r="964">
-      <c r="A964" t="inlineStr"/>
-      <c r="B964" t="n">
-        <v>963</v>
-      </c>
-      <c r="C964" t="inlineStr"/>
-      <c r="D964" t="inlineStr"/>
-      <c r="E964" t="inlineStr"/>
-    </row>
-    <row r="965">
-      <c r="A965" t="inlineStr"/>
-      <c r="B965" t="n">
-        <v>964</v>
-      </c>
-      <c r="C965" t="inlineStr"/>
-      <c r="D965" t="inlineStr"/>
-      <c r="E965" t="inlineStr"/>
-    </row>
-    <row r="966">
-      <c r="A966" t="inlineStr"/>
-      <c r="B966" t="n">
-        <v>965</v>
-      </c>
-      <c r="C966" t="inlineStr"/>
-      <c r="D966" t="inlineStr"/>
-      <c r="E966" t="inlineStr"/>
-    </row>
-    <row r="967">
-      <c r="A967" t="inlineStr"/>
-      <c r="B967" t="n">
-        <v>966</v>
-      </c>
-      <c r="C967" t="inlineStr"/>
-      <c r="D967" t="inlineStr"/>
-      <c r="E967" t="inlineStr"/>
-    </row>
-    <row r="968">
-      <c r="A968" t="inlineStr"/>
-      <c r="B968" t="n">
-        <v>967</v>
-      </c>
-      <c r="C968" t="inlineStr"/>
-      <c r="D968" t="inlineStr"/>
-      <c r="E968" t="inlineStr"/>
-    </row>
-    <row r="969">
-      <c r="A969" t="inlineStr"/>
-      <c r="B969" t="n">
-        <v>968</v>
-      </c>
-      <c r="C969" t="inlineStr"/>
-      <c r="D969" t="inlineStr"/>
-      <c r="E969" t="inlineStr"/>
-    </row>
-    <row r="970">
-      <c r="A970" t="inlineStr"/>
-      <c r="B970" t="n">
-        <v>969</v>
-      </c>
-      <c r="C970" t="inlineStr"/>
-      <c r="D970" t="inlineStr"/>
-      <c r="E970" t="inlineStr"/>
-    </row>
-    <row r="971">
-      <c r="A971" t="inlineStr"/>
-      <c r="B971" t="n">
-        <v>970</v>
-      </c>
-      <c r="C971" t="inlineStr"/>
-      <c r="D971" t="inlineStr"/>
-      <c r="E971" t="inlineStr"/>
-    </row>
-    <row r="972">
-      <c r="A972" t="inlineStr"/>
-      <c r="B972" t="n">
-        <v>971</v>
-      </c>
-      <c r="C972" t="inlineStr"/>
-      <c r="D972" t="inlineStr"/>
-      <c r="E972" t="inlineStr"/>
-    </row>
-    <row r="973">
-      <c r="A973" t="inlineStr"/>
-      <c r="B973" t="n">
-        <v>972</v>
-      </c>
-      <c r="C973" t="inlineStr"/>
-      <c r="D973" t="inlineStr"/>
-      <c r="E973" t="inlineStr"/>
-    </row>
-    <row r="974">
-      <c r="A974" t="inlineStr"/>
-      <c r="B974" t="n">
-        <v>973</v>
-      </c>
-      <c r="C974" t="inlineStr"/>
-      <c r="D974" t="inlineStr"/>
-      <c r="E974" t="inlineStr"/>
-    </row>
-    <row r="975">
-      <c r="A975" t="inlineStr"/>
-      <c r="B975" t="n">
-        <v>974</v>
-      </c>
-      <c r="C975" t="inlineStr"/>
-      <c r="D975" t="inlineStr"/>
-      <c r="E975" t="inlineStr"/>
-    </row>
-    <row r="976">
-      <c r="A976" t="inlineStr"/>
-      <c r="B976" t="n">
-        <v>975</v>
-      </c>
-      <c r="C976" t="inlineStr"/>
-      <c r="D976" t="inlineStr"/>
-      <c r="E976" t="inlineStr"/>
-    </row>
-    <row r="977">
-      <c r="A977" t="inlineStr"/>
-      <c r="B977" t="n">
-        <v>976</v>
-      </c>
-      <c r="C977" t="inlineStr"/>
-      <c r="D977" t="inlineStr"/>
-      <c r="E977" t="inlineStr"/>
-    </row>
-    <row r="978">
-      <c r="A978" t="inlineStr"/>
-      <c r="B978" t="n">
-        <v>977</v>
-      </c>
-      <c r="C978" t="inlineStr"/>
-      <c r="D978" t="inlineStr"/>
-      <c r="E978" t="inlineStr"/>
-    </row>
-    <row r="979">
-      <c r="A979" t="inlineStr"/>
-      <c r="B979" t="n">
-        <v>978</v>
-      </c>
-      <c r="C979" t="inlineStr"/>
-      <c r="D979" t="inlineStr"/>
-      <c r="E979" t="inlineStr"/>
-    </row>
-    <row r="980">
-      <c r="A980" t="inlineStr"/>
-      <c r="B980" t="n">
-        <v>979</v>
-      </c>
-      <c r="C980" t="inlineStr"/>
-      <c r="D980" t="inlineStr"/>
-      <c r="E980" t="inlineStr"/>
-    </row>
-    <row r="981">
-      <c r="A981" t="inlineStr"/>
-      <c r="B981" t="n">
-        <v>980</v>
-      </c>
-      <c r="C981" t="inlineStr"/>
-      <c r="D981" t="inlineStr"/>
-      <c r="E981" t="inlineStr"/>
-    </row>
-    <row r="982">
-      <c r="A982" t="inlineStr"/>
-      <c r="B982" t="n">
-        <v>981</v>
-      </c>
-      <c r="C982" t="inlineStr"/>
-      <c r="D982" t="inlineStr"/>
-      <c r="E982" t="inlineStr"/>
-    </row>
-    <row r="983">
-      <c r="A983" t="inlineStr"/>
-      <c r="B983" t="n">
-        <v>982</v>
-      </c>
-      <c r="C983" t="inlineStr"/>
-      <c r="D983" t="inlineStr"/>
-      <c r="E983" t="inlineStr"/>
-    </row>
-    <row r="984">
-      <c r="A984" t="inlineStr"/>
-      <c r="B984" t="n">
-        <v>983</v>
-      </c>
-      <c r="C984" t="inlineStr"/>
-      <c r="D984" t="inlineStr"/>
-      <c r="E984" t="inlineStr"/>
-    </row>
-    <row r="985">
-      <c r="A985" t="inlineStr"/>
-      <c r="B985" t="n">
-        <v>984</v>
-      </c>
-      <c r="C985" t="inlineStr"/>
-      <c r="D985" t="inlineStr"/>
-      <c r="E985" t="inlineStr"/>
-    </row>
-    <row r="986">
-      <c r="A986" t="inlineStr"/>
-      <c r="B986" t="n">
-        <v>985</v>
-      </c>
-      <c r="C986" t="inlineStr"/>
-      <c r="D986" t="inlineStr"/>
-      <c r="E986" t="inlineStr"/>
-    </row>
-    <row r="987">
-      <c r="A987" t="inlineStr"/>
-      <c r="B987" t="n">
-        <v>986</v>
-      </c>
-      <c r="C987" t="inlineStr"/>
-      <c r="D987" t="inlineStr"/>
-      <c r="E987" t="inlineStr"/>
-    </row>
-    <row r="988">
-      <c r="A988" t="inlineStr"/>
-      <c r="B988" t="n">
-        <v>987</v>
-      </c>
-      <c r="C988" t="inlineStr"/>
-      <c r="D988" t="inlineStr"/>
-      <c r="E988" t="inlineStr"/>
-    </row>
-    <row r="989">
-      <c r="A989" t="inlineStr"/>
-      <c r="B989" t="n">
-        <v>988</v>
-      </c>
-      <c r="C989" t="inlineStr"/>
-      <c r="D989" t="inlineStr"/>
-      <c r="E989" t="inlineStr"/>
-    </row>
-    <row r="990">
-      <c r="A990" t="inlineStr"/>
-      <c r="B990" t="n">
-        <v>989</v>
-      </c>
-      <c r="C990" t="inlineStr"/>
-      <c r="D990" t="inlineStr"/>
-      <c r="E990" t="inlineStr"/>
-    </row>
-    <row r="991">
-      <c r="A991" t="inlineStr"/>
-      <c r="B991" t="n">
-        <v>990</v>
-      </c>
-      <c r="C991" t="inlineStr"/>
-      <c r="D991" t="inlineStr"/>
-      <c r="E991" t="inlineStr"/>
-    </row>
-    <row r="992">
-      <c r="A992" t="inlineStr"/>
-      <c r="B992" t="n">
-        <v>991</v>
-      </c>
-      <c r="C992" t="inlineStr"/>
-      <c r="D992" t="inlineStr"/>
-      <c r="E992" t="inlineStr"/>
-    </row>
-    <row r="993">
-      <c r="A993" t="inlineStr"/>
-      <c r="B993" t="n">
-        <v>992</v>
-      </c>
-      <c r="C993" t="inlineStr"/>
-      <c r="D993" t="inlineStr"/>
-      <c r="E993" t="inlineStr"/>
-    </row>
-    <row r="994">
-      <c r="A994" t="inlineStr"/>
-      <c r="B994" t="n">
-        <v>993</v>
-      </c>
-      <c r="C994" t="inlineStr"/>
-      <c r="D994" t="inlineStr"/>
-      <c r="E994" t="inlineStr"/>
-    </row>
-    <row r="995">
-      <c r="A995" t="inlineStr"/>
-      <c r="B995" t="n">
-        <v>994</v>
-      </c>
-      <c r="C995" t="inlineStr"/>
-      <c r="D995" t="inlineStr"/>
-      <c r="E995" t="inlineStr"/>
-    </row>
-    <row r="996">
-      <c r="A996" t="inlineStr"/>
-      <c r="B996" t="n">
-        <v>995</v>
-      </c>
-      <c r="C996" t="inlineStr"/>
-      <c r="D996" t="inlineStr"/>
-      <c r="E996" t="inlineStr"/>
-    </row>
-    <row r="997">
-      <c r="A997" t="inlineStr"/>
-      <c r="B997" t="n">
-        <v>996</v>
-      </c>
-      <c r="C997" t="inlineStr"/>
-      <c r="D997" t="inlineStr"/>
-      <c r="E997" t="inlineStr"/>
-    </row>
-    <row r="998">
-      <c r="A998" t="inlineStr"/>
-      <c r="B998" t="n">
-        <v>997</v>
-      </c>
-      <c r="C998" t="inlineStr"/>
-      <c r="D998" t="inlineStr"/>
-      <c r="E998" t="inlineStr"/>
-    </row>
-    <row r="999">
-      <c r="A999" t="inlineStr"/>
-      <c r="B999" t="n">
-        <v>998</v>
-      </c>
-      <c r="C999" t="inlineStr"/>
-      <c r="D999" t="inlineStr"/>
-      <c r="E999" t="inlineStr"/>
-    </row>
-    <row r="1000">
-      <c r="A1000" t="inlineStr"/>
-      <c r="B1000" t="n">
-        <v>999</v>
-      </c>
-      <c r="C1000" t="inlineStr"/>
-      <c r="D1000" t="inlineStr"/>
-      <c r="E1000" t="inlineStr"/>
-    </row>
-    <row r="1001">
-      <c r="A1001" t="inlineStr"/>
-      <c r="B1001" t="n">
-        <v>1000</v>
-      </c>
-      <c r="C1001" t="inlineStr"/>
-      <c r="D1001" t="inlineStr"/>
-      <c r="E1001" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
